--- a/LTE_Spectrum_Coordination.xlsx
+++ b/LTE_Spectrum_Coordination.xlsx
@@ -80,7 +80,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill/>
     </fill>
@@ -135,6 +135,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C9A227"/>
       </patternFill>
     </fill>
   </fills>
@@ -208,7 +213,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -302,6 +307,10 @@
     <xf numFmtId="0" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -698,7 +707,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J189"/>
+  <dimension ref="A1:J186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -732,7 +741,7 @@
     <row r="2" ht="28" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Huawei eRAN LTE Spectrum Coordination Feature Parameter Description, eRAN21.1 Issue 01 (2025-03-10).  Applies to FDD/TDD (no FDD↔TDD principle difference, §2.4).  MML, counter IDs, license models, and Figure 4-1 are taken from this FPD.  Doc example uses downlink 3CC (LocalCellId=0/1/2).  Where the FPD does not print a factory default, Default = “See Parameter Reference”; Recommended = Table 4-1/4-2 setting or the MML sample.</t>
+          <t>Huawei eRAN LTE Spectrum Coordination Feature Parameter Description, eRAN21.1 Issue 01 (2025-03-10).  Applies to FDD/TDD (no FDD↔TDD principle difference, §2.4).  MML, counter IDs, license models, and Figure 4-1 are taken from this FPD.  Cell-level MML in this sheet uses LocalCellId=1 only (repeat on the partner cell in live network).  Where the FPD does not print a factory default, Default = “See Parameter Reference”; Recommended = Table 4-1/4-2 setting or the MML sample.</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -1119,7 +1128,7 @@
       <c r="A36" s="20" t="inlineStr">
         <is>
           <t>Worked example (sample values from the document or typical live-network settings):
-Doc MML: MOD CAMGTCFG: LocalCellId=0/1/2, SpectrumCoordSinrThld=-2;
+Doc MML (this sheet: LocalCellId=1): MOD CAMGTCFG: LocalCellId=1, SpectrumCoordSinrThld=-2;
 Sample UE at high-frequency PCell: UL SINR used in scheduling = −3 dB, threshold = −2 dB.
 Compare: −3 &lt; −2  → TRUE.
 Result: LTE Spectrum Coordination evaluation STARTS. If UL SINR = 0 dB: 0 &lt; −2 is FALSE → no SC handover from this trigger.</t>
@@ -1589,7 +1598,7 @@
     <row r="61" ht="33" customHeight="1">
       <c r="A61" s="7" t="inlineStr">
         <is>
-          <t>MOD CAMGTCFG: LocalCellId=0/1/2, CellCaAlgoSwitch=SpectrumCoordinationSwitch-0;  stops UL-SINR-triggered PCell swaps. CA itself is unchanged. Doc example is the 3CC set of three cells.</t>
+          <t>MOD CAMGTCFG: LocalCellId=1, CellCaAlgoSwitch=SpectrumCoordinationSwitch-0;  stops UL-SINR-triggered PCell swaps. CA itself is unchanged. Repeat on every participating cell in live network.</t>
         </is>
       </c>
       <c r="B61" s="8" t="n"/>
@@ -2420,7 +2429,7 @@
       </c>
       <c r="G84" s="16" t="inlineStr">
         <is>
-          <t>Doc MML: CellCaAlgoSwitch=SpectrumCoordinationSwitch-1 on LocalCellId=0,1,2 (3CC example).</t>
+          <t>Doc MML in this sheet: CellCaAlgoSwitch=SpectrumCoordinationSwitch-1 on LocalCellId=1.</t>
         </is>
       </c>
       <c r="H84" s="14" t="n"/>
@@ -2610,7 +2619,7 @@
       </c>
       <c r="G89" s="33" t="inlineStr">
         <is>
-          <t>Doc MML on LocalCellId=0,1,2.</t>
+          <t>Doc MML in this sheet: LocalCellId=1.</t>
         </is>
       </c>
       <c r="H89" s="14" t="n"/>
@@ -3000,7 +3009,7 @@
     <row r="100" ht="22" customHeight="1">
       <c r="A100" s="5" t="inlineStr">
         <is>
-          <t>F.  MML  (verbatim from Ch.4.4.1.2 and Ch.5.4.1.2)</t>
+          <t>F.  MML  (from Ch.4.4.1.2 and Ch.5.4.1.2  —  LocalCellId=1 only)</t>
         </is>
       </c>
       <c r="B100" s="6" t="n"/>
@@ -3016,7 +3025,7 @@
     <row r="101" ht="28" customHeight="1">
       <c r="A101" s="3" t="inlineStr">
         <is>
-          <t>Ch.4 example is downlink 3CC (LocalCellId=0,1,2; EARFCN 123/567/890). Ch.5 example: low-frequency LocalCellId=0 as MBBSERCELL, EARFCN 123 PCC + 456 SCC. Replace IDs with live-network values.</t>
+          <t>FPD sample used three cells (0/1/2). This sheet keeps one cell: LocalCellId=1. Repeat the same cell-level command on every participating high/low cell in the live network. eNodeB-level commands have no LocalCellId. EARFCN 123/567 are FPD examples — replace with live EARFCNs.</t>
         </is>
       </c>
       <c r="B101" s="4" t="n"/>
@@ -3095,12 +3104,12 @@
       </c>
       <c r="F103" s="29" t="inlineStr">
         <is>
-          <t>MOD CELLMLBHO: LocalCellId=0, MlbMatchOtherFeatureMode=HoAdmitSwitch-0;</t>
+          <t>MOD CELLMLBHO: LocalCellId=1, MlbMatchOtherFeatureMode=HoAdmitSwitch-0;</t>
         </is>
       </c>
       <c r="G103" s="16" t="inlineStr">
         <is>
-          <t>Doc: Enabling LTE spectrum coordination (taking downlink 3CC as an example). Repeat 0,1,2.</t>
+          <t>Deselect MLB unnecessary-HO admission on the cell (original PCell/SCell). Repeat on partner cell in live network.</t>
         </is>
       </c>
       <c r="H103" s="14" t="n"/>
@@ -3133,19 +3142,19 @@
       </c>
       <c r="F104" s="28" t="inlineStr">
         <is>
-          <t>MOD CELLMLBHO: LocalCellId=1, MlbMatchOtherFeatureMode=HoAdmitSwitch-0;</t>
+          <t>MOD CELLALGOSWITCH: LocalCellId=1, PucchAlgoSwitch=Dl2CCAckResShareSw-1;</t>
         </is>
       </c>
       <c r="G104" s="13" t="inlineStr">
         <is>
-          <t>Original PCell/SCell set.</t>
+          <t>With CaEnhancedPreAllocSwitch, prevents low-frequency cell traffic from increasing.</t>
         </is>
       </c>
       <c r="H104" s="14" t="n"/>
       <c r="I104" s="14" t="n"/>
       <c r="J104" s="15" t="n"/>
     </row>
-    <row r="105" ht="24" customHeight="1">
+    <row r="105" ht="36" customHeight="1">
       <c r="A105" s="30" t="n">
         <v>3</v>
       </c>
@@ -3171,12 +3180,12 @@
       </c>
       <c r="F105" s="29" t="inlineStr">
         <is>
-          <t>MOD CELLMLBHO: LocalCellId=2, MlbMatchOtherFeatureMode=HoAdmitSwitch-0;</t>
+          <t>MOD ENODEBALGOSWITCH: CaAlgoSwitch=HoWithSccCfgSwitch-1&amp;SccA2RmvSwitch-1, CaAlgoExtSwitch=CaEnhancedPreAllocSwitch-1;</t>
         </is>
       </c>
       <c r="G105" s="16" t="inlineStr">
         <is>
-          <t>Original PCell/SCell set.</t>
+          <t>eNodeB-level (no LocalCellId): SCell-during-HO + A2 remove + enhanced pre-alloc.</t>
         </is>
       </c>
       <c r="H105" s="14" t="n"/>
@@ -3209,12 +3218,12 @@
       </c>
       <c r="F106" s="28" t="inlineStr">
         <is>
-          <t>MOD CELLALGOSWITCH: LocalCellId=0, PucchAlgoSwitch=Dl2CCAckResShareSw-1;</t>
+          <t>MOD CAMGTCFG: LocalCellId=1, CellCaAlgoSwitch=SpectrumCoordinationSwitch-1;</t>
         </is>
       </c>
       <c r="G106" s="13" t="inlineStr">
         <is>
-          <t>Prevents low-frequency traffic increase (with CaEnhancedPreAllocSwitch).</t>
+          <t>Master switch. Repeat on every participating cell.</t>
         </is>
       </c>
       <c r="H106" s="14" t="n"/>
@@ -3242,15 +3251,19 @@
       </c>
       <c r="E107" s="16" t="inlineStr">
         <is>
-          <t>Activate SC</t>
+          <t>Optimize SC</t>
         </is>
       </c>
       <c r="F107" s="29" t="inlineStr">
         <is>
-          <t>MOD CELLALGOSWITCH: LocalCellId=1, PucchAlgoSwitch=Dl2CCAckResShareSw-1;</t>
-        </is>
-      </c>
-      <c r="G107" s="16" t="inlineStr"/>
+          <t>MOD CAMGTCFG: LocalCellId=1, SpectrumCoordSinrThld=-2;</t>
+        </is>
+      </c>
+      <c r="G107" s="16" t="inlineStr">
+        <is>
+          <t>Doc recommended SINR threshold on original PCells.</t>
+        </is>
+      </c>
       <c r="H107" s="14" t="n"/>
       <c r="I107" s="14" t="n"/>
       <c r="J107" s="15" t="n"/>
@@ -3266,7 +3279,7 @@
       </c>
       <c r="C108" s="13" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Adaptive</t>
         </is>
       </c>
       <c r="D108" s="13" t="inlineStr">
@@ -3276,20 +3289,24 @@
       </c>
       <c r="E108" s="13" t="inlineStr">
         <is>
-          <t>Activate SC</t>
+          <t>Optimize SC</t>
         </is>
       </c>
       <c r="F108" s="28" t="inlineStr">
         <is>
-          <t>MOD CELLALGOSWITCH: LocalCellId=2, PucchAlgoSwitch=Dl2CCAckResShareSw-1;</t>
-        </is>
-      </c>
-      <c r="G108" s="13" t="inlineStr"/>
+          <t>MOD SCCFREQCFG: PccDlEarfcn=123, SccDlEarfcn=567, SccA2RsrpThldExtendedOfs=-10;</t>
+        </is>
+      </c>
+      <c r="G108" s="13" t="inlineStr">
+        <is>
+          <t>Doc A2 extended offset. One PCC↔SCC pair shown; apply to each live pair.</t>
+        </is>
+      </c>
       <c r="H108" s="14" t="n"/>
       <c r="I108" s="14" t="n"/>
       <c r="J108" s="15" t="n"/>
     </row>
-    <row r="109" ht="36" customHeight="1">
+    <row r="109" ht="24" customHeight="1">
       <c r="A109" s="30" t="n">
         <v>7</v>
       </c>
@@ -3310,17 +3327,17 @@
       </c>
       <c r="E109" s="16" t="inlineStr">
         <is>
-          <t>Activate SC</t>
+          <t>Deactivate SC</t>
         </is>
       </c>
       <c r="F109" s="29" t="inlineStr">
         <is>
-          <t>MOD ENODEBALGOSWITCH: CaAlgoSwitch=HoWithSccCfgSwitch-1&amp;SccA2RmvSwitch-1, CaAlgoExtSwitch=CaEnhancedPreAllocSwitch-1;</t>
+          <t>MOD CAMGTCFG: LocalCellId=1, CellCaAlgoSwitch=SpectrumCoordinationSwitch-0;</t>
         </is>
       </c>
       <c r="G109" s="16" t="inlineStr">
         <is>
-          <t>Doc single eNodeB-level command (HO-with-SCell + A2 remove + enhanced pre-alloc).</t>
+          <t>Stops UL-SINR PCell swaps. CA stays as configured.</t>
         </is>
       </c>
       <c r="H109" s="14" t="n"/>
@@ -3348,17 +3365,17 @@
       </c>
       <c r="E110" s="13" t="inlineStr">
         <is>
-          <t>Activate SC</t>
+          <t>Activate enhancement</t>
         </is>
       </c>
       <c r="F110" s="28" t="inlineStr">
         <is>
-          <t>MOD CAMGTCFG: LocalCellId=0, CellCaAlgoSwitch=SpectrumCoordinationSwitch-1;</t>
+          <t>MOD ENODEBALGOSWITCH: CaAlgoSwitch=HoWithSccCfgSwitch-1;</t>
         </is>
       </c>
       <c r="G110" s="13" t="inlineStr">
         <is>
-          <t>Master bit on each of the three cells.</t>
+          <t>Ch.5 WBB/RRN enhancement. eNodeB-level.</t>
         </is>
       </c>
       <c r="H110" s="14" t="n"/>
@@ -3386,15 +3403,19 @@
       </c>
       <c r="E111" s="16" t="inlineStr">
         <is>
-          <t>Activate SC</t>
+          <t>Activate enhancement</t>
         </is>
       </c>
       <c r="F111" s="29" t="inlineStr">
         <is>
-          <t>MOD CAMGTCFG: LocalCellId=1, CellCaAlgoSwitch=SpectrumCoordinationSwitch-1;</t>
-        </is>
-      </c>
-      <c r="G111" s="16" t="inlineStr"/>
+          <t>MOD CELL: LocalCellId=1, SpecifiedCellFlag=MBBSERCELL;</t>
+        </is>
+      </c>
+      <c r="G111" s="16" t="inlineStr">
+        <is>
+          <t>Mark the low-frequency cell as MBB service cell.</t>
+        </is>
+      </c>
       <c r="H111" s="14" t="n"/>
       <c r="I111" s="14" t="n"/>
       <c r="J111" s="15" t="n"/>
@@ -3420,15 +3441,19 @@
       </c>
       <c r="E112" s="13" t="inlineStr">
         <is>
-          <t>Activate SC</t>
+          <t>Activate enhancement</t>
         </is>
       </c>
       <c r="F112" s="28" t="inlineStr">
         <is>
-          <t>MOD CAMGTCFG: LocalCellId=2, CellCaAlgoSwitch=SpectrumCoordinationSwitch-1;</t>
-        </is>
-      </c>
-      <c r="G112" s="13" t="inlineStr"/>
+          <t>MOD CAMGTCFG: LocalCellId=1, CellCaAlgoSwitch=WbbCaMultiCarrierCoordSw-1;</t>
+        </is>
+      </c>
+      <c r="G112" s="13" t="inlineStr">
+        <is>
+          <t>Enhancement bit on the participating cell.</t>
+        </is>
+      </c>
       <c r="H112" s="14" t="n"/>
       <c r="I112" s="14" t="n"/>
       <c r="J112" s="15" t="n"/>
@@ -3454,17 +3479,17 @@
       </c>
       <c r="E113" s="16" t="inlineStr">
         <is>
-          <t>Optimize SC</t>
+          <t>Optimize enhancement</t>
         </is>
       </c>
       <c r="F113" s="29" t="inlineStr">
         <is>
-          <t>MOD CAMGTCFG: LocalCellId=0, SpectrumCoordSinrThld=-2;</t>
+          <t>MOD CELLWTTXPARACFG: LocalCellId=1, WbbMultiCarrierCoordA2Ofs=2;</t>
         </is>
       </c>
       <c r="G113" s="16" t="inlineStr">
         <is>
-          <t>Doc: Setting the SINR threshold (3CC example). Repeat 0,1,2.</t>
+          <t>Doc WBB A2 offset (low-frequency cells).</t>
         </is>
       </c>
       <c r="H113" s="14" t="n"/>
@@ -3482,7 +3507,7 @@
       </c>
       <c r="C114" s="13" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Adaptive</t>
         </is>
       </c>
       <c r="D114" s="13" t="inlineStr">
@@ -3492,15 +3517,19 @@
       </c>
       <c r="E114" s="13" t="inlineStr">
         <is>
-          <t>Optimize SC</t>
+          <t>Optimize enhancement</t>
         </is>
       </c>
       <c r="F114" s="28" t="inlineStr">
         <is>
-          <t>MOD CAMGTCFG: LocalCellId=1, SpectrumCoordSinrThld=-2;</t>
-        </is>
-      </c>
-      <c r="G114" s="13" t="inlineStr"/>
+          <t>MOD SCCFREQCFG: PccDlEarfcn=123, SccDlEarfcn=456, SccA2RsrpThldExtendedOfs=-10;</t>
+        </is>
+      </c>
+      <c r="G114" s="13" t="inlineStr">
+        <is>
+          <t>Doc: low-freq PCC 123 + high-freq WBB SCC 456.</t>
+        </is>
+      </c>
       <c r="H114" s="14" t="n"/>
       <c r="I114" s="14" t="n"/>
       <c r="J114" s="15" t="n"/>
@@ -3526,733 +3555,633 @@
       </c>
       <c r="E115" s="16" t="inlineStr">
         <is>
-          <t>Optimize SC</t>
+          <t>Deactivate enhancement</t>
         </is>
       </c>
       <c r="F115" s="29" t="inlineStr">
         <is>
-          <t>MOD CAMGTCFG: LocalCellId=2, SpectrumCoordSinrThld=-2;</t>
-        </is>
-      </c>
-      <c r="G115" s="16" t="inlineStr"/>
+          <t>MOD CAMGTCFG: LocalCellId=1, CellCaAlgoSwitch=WbbCaMultiCarrierCoordSw-0;</t>
+        </is>
+      </c>
+      <c r="G115" s="16" t="inlineStr">
+        <is>
+          <t>Turns off WBB/RRN enhancement only.</t>
+        </is>
+      </c>
       <c r="H115" s="14" t="n"/>
       <c r="I115" s="14" t="n"/>
       <c r="J115" s="15" t="n"/>
     </row>
-    <row r="116" ht="24" customHeight="1">
-      <c r="A116" s="34" t="n">
-        <v>14</v>
-      </c>
-      <c r="B116" s="34" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="C116" s="13" t="inlineStr">
-        <is>
-          <t>Adaptive</t>
-        </is>
-      </c>
-      <c r="D116" s="13" t="inlineStr">
-        <is>
-          <t>FDD/TDD</t>
-        </is>
-      </c>
-      <c r="E116" s="13" t="inlineStr">
-        <is>
-          <t>Optimize SC</t>
-        </is>
-      </c>
-      <c r="F116" s="28" t="inlineStr">
-        <is>
-          <t>MOD SCCFREQCFG: PccDlEarfcn=123, SccDlEarfcn=567, SccA2RsrpThldExtendedOfs=-10;</t>
-        </is>
-      </c>
-      <c r="G116" s="13" t="inlineStr">
-        <is>
-          <t>Doc: extended A2 offset on every PCC↔SCC pair of {123,567,890}.</t>
-        </is>
-      </c>
-      <c r="H116" s="14" t="n"/>
-      <c r="I116" s="14" t="n"/>
-      <c r="J116" s="15" t="n"/>
-    </row>
-    <row r="117" ht="24" customHeight="1">
-      <c r="A117" s="30" t="n">
-        <v>15</v>
-      </c>
-      <c r="B117" s="30" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="C117" s="16" t="inlineStr">
-        <is>
-          <t>Adaptive</t>
-        </is>
-      </c>
-      <c r="D117" s="16" t="inlineStr">
-        <is>
-          <t>FDD/TDD</t>
-        </is>
-      </c>
-      <c r="E117" s="16" t="inlineStr">
-        <is>
-          <t>Optimize SC</t>
-        </is>
-      </c>
-      <c r="F117" s="29" t="inlineStr">
-        <is>
-          <t>MOD SCCFREQCFG: PccDlEarfcn=123, SccDlEarfcn=890, SccA2RsrpThldExtendedOfs=-10;</t>
-        </is>
-      </c>
-      <c r="G117" s="16" t="inlineStr"/>
-      <c r="H117" s="14" t="n"/>
-      <c r="I117" s="14" t="n"/>
-      <c r="J117" s="15" t="n"/>
-    </row>
-    <row r="118" ht="24" customHeight="1">
-      <c r="A118" s="34" t="n">
-        <v>16</v>
-      </c>
-      <c r="B118" s="34" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="C118" s="13" t="inlineStr">
-        <is>
-          <t>Adaptive</t>
-        </is>
-      </c>
-      <c r="D118" s="13" t="inlineStr">
-        <is>
-          <t>FDD/TDD</t>
-        </is>
-      </c>
-      <c r="E118" s="13" t="inlineStr">
-        <is>
-          <t>Optimize SC</t>
-        </is>
-      </c>
-      <c r="F118" s="28" t="inlineStr">
-        <is>
-          <t>MOD SCCFREQCFG: PccDlEarfcn=567, SccDlEarfcn=123, SccA2RsrpThldExtendedOfs=-10;</t>
-        </is>
-      </c>
-      <c r="G118" s="13" t="inlineStr"/>
+    <row r="116" ht="22" customHeight="1">
+      <c r="A116" s="5" t="inlineStr">
+        <is>
+          <t>G.  Counters  (Tables 4-3, 4-4, 5-4–5-8, 5.4.2)</t>
+        </is>
+      </c>
+      <c r="B116" s="6" t="n"/>
+      <c r="C116" s="6" t="n"/>
+      <c r="D116" s="6" t="n"/>
+      <c r="E116" s="6" t="n"/>
+      <c r="F116" s="6" t="n"/>
+      <c r="G116" s="6" t="n"/>
+      <c r="H116" s="6" t="n"/>
+      <c r="I116" s="6" t="n"/>
+      <c r="J116" s="6" t="n"/>
+    </row>
+    <row r="117" ht="22" customHeight="1">
+      <c r="A117" s="12" t="inlineStr">
+        <is>
+          <t>SN</t>
+        </is>
+      </c>
+      <c r="B117" s="12" t="inlineStr">
+        <is>
+          <t>Counter ID</t>
+        </is>
+      </c>
+      <c r="C117" s="12" t="inlineStr">
+        <is>
+          <t>Counter Name</t>
+        </is>
+      </c>
+      <c r="D117" s="12" t="inlineStr">
+        <is>
+          <t>Function / what it measures</t>
+        </is>
+      </c>
+      <c r="E117" s="12" t="inlineStr">
+        <is>
+          <t>Use</t>
+        </is>
+      </c>
+      <c r="F117" s="12" t="inlineStr"/>
+      <c r="G117" s="12" t="inlineStr"/>
+      <c r="H117" s="12" t="inlineStr"/>
+      <c r="I117" s="12" t="inlineStr"/>
+      <c r="J117" s="12" t="inlineStr"/>
+    </row>
+    <row r="118" ht="32" customHeight="1">
+      <c r="A118" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="B118" s="16" t="inlineStr">
+        <is>
+          <t>1526729994</t>
+        </is>
+      </c>
+      <c r="C118" s="29" t="inlineStr">
+        <is>
+          <t>L.HHO.InterFreq.ULquality.PrepAttOut</t>
+        </is>
+      </c>
+      <c r="D118" s="16" t="inlineStr">
+        <is>
+          <t>UL-quality inter-freq HO preparations</t>
+        </is>
+      </c>
+      <c r="E118" s="16" t="inlineStr">
+        <is>
+          <t>Table 4-3 activation: values increase ⇒ SC has taken effect</t>
+        </is>
+      </c>
+      <c r="F118" s="14" t="n"/>
+      <c r="G118" s="14" t="n"/>
       <c r="H118" s="14" t="n"/>
       <c r="I118" s="14" t="n"/>
       <c r="J118" s="15" t="n"/>
     </row>
-    <row r="119" ht="24" customHeight="1">
-      <c r="A119" s="30" t="n">
-        <v>17</v>
-      </c>
-      <c r="B119" s="30" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="C119" s="16" t="inlineStr">
-        <is>
-          <t>Adaptive</t>
-        </is>
-      </c>
-      <c r="D119" s="16" t="inlineStr">
-        <is>
-          <t>FDD/TDD</t>
-        </is>
-      </c>
-      <c r="E119" s="16" t="inlineStr">
-        <is>
-          <t>Optimize SC</t>
-        </is>
-      </c>
-      <c r="F119" s="29" t="inlineStr">
-        <is>
-          <t>MOD SCCFREQCFG: PccDlEarfcn=567, SccDlEarfcn=890, SccA2RsrpThldExtendedOfs=-10;</t>
-        </is>
-      </c>
-      <c r="G119" s="16" t="inlineStr"/>
+    <row r="119" ht="32" customHeight="1">
+      <c r="A119" s="34" t="n">
+        <v>2</v>
+      </c>
+      <c r="B119" s="13" t="inlineStr">
+        <is>
+          <t>1526729996</t>
+        </is>
+      </c>
+      <c r="C119" s="28" t="inlineStr">
+        <is>
+          <t>L.HHO.InterFreq.ULquality.ExecAttOut</t>
+        </is>
+      </c>
+      <c r="D119" s="13" t="inlineStr">
+        <is>
+          <t>UL-quality inter-freq HO executions</t>
+        </is>
+      </c>
+      <c r="E119" s="13" t="inlineStr">
+        <is>
+          <t>Table 4-3</t>
+        </is>
+      </c>
+      <c r="F119" s="14" t="n"/>
+      <c r="G119" s="14" t="n"/>
       <c r="H119" s="14" t="n"/>
       <c r="I119" s="14" t="n"/>
       <c r="J119" s="15" t="n"/>
     </row>
-    <row r="120" ht="24" customHeight="1">
-      <c r="A120" s="34" t="n">
-        <v>18</v>
-      </c>
-      <c r="B120" s="34" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="C120" s="13" t="inlineStr">
-        <is>
-          <t>Adaptive</t>
-        </is>
-      </c>
-      <c r="D120" s="13" t="inlineStr">
-        <is>
-          <t>FDD/TDD</t>
-        </is>
-      </c>
-      <c r="E120" s="13" t="inlineStr">
-        <is>
-          <t>Optimize SC</t>
-        </is>
-      </c>
-      <c r="F120" s="28" t="inlineStr">
-        <is>
-          <t>MOD SCCFREQCFG: PccDlEarfcn=890, SccDlEarfcn=123, SccA2RsrpThldExtendedOfs=-10;</t>
-        </is>
-      </c>
-      <c r="G120" s="13" t="inlineStr"/>
+    <row r="120" ht="32" customHeight="1">
+      <c r="A120" s="30" t="n">
+        <v>3</v>
+      </c>
+      <c r="B120" s="16" t="inlineStr">
+        <is>
+          <t>1526729998</t>
+        </is>
+      </c>
+      <c r="C120" s="29" t="inlineStr">
+        <is>
+          <t>L.HHO.InterFreq.ULquality.ExecSuccOut</t>
+        </is>
+      </c>
+      <c r="D120" s="16" t="inlineStr">
+        <is>
+          <t>UL-quality inter-freq HO success</t>
+        </is>
+      </c>
+      <c r="E120" s="16" t="inlineStr">
+        <is>
+          <t>Table 4-3; success rate KPI</t>
+        </is>
+      </c>
+      <c r="F120" s="14" t="n"/>
+      <c r="G120" s="14" t="n"/>
       <c r="H120" s="14" t="n"/>
       <c r="I120" s="14" t="n"/>
       <c r="J120" s="15" t="n"/>
     </row>
-    <row r="121" ht="24" customHeight="1">
-      <c r="A121" s="30" t="n">
-        <v>19</v>
-      </c>
-      <c r="B121" s="30" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="C121" s="16" t="inlineStr">
-        <is>
-          <t>Adaptive</t>
-        </is>
-      </c>
-      <c r="D121" s="16" t="inlineStr">
-        <is>
-          <t>FDD/TDD</t>
-        </is>
-      </c>
-      <c r="E121" s="16" t="inlineStr">
-        <is>
-          <t>Optimize SC</t>
-        </is>
-      </c>
-      <c r="F121" s="29" t="inlineStr">
-        <is>
-          <t>MOD SCCFREQCFG: PccDlEarfcn=890, SccDlEarfcn=567, SccA2RsrpThldExtendedOfs=-10;</t>
-        </is>
-      </c>
-      <c r="G121" s="16" t="inlineStr"/>
+    <row r="121" ht="32" customHeight="1">
+      <c r="A121" s="34" t="n">
+        <v>4</v>
+      </c>
+      <c r="B121" s="13" t="inlineStr">
+        <is>
+          <t>1526729995</t>
+        </is>
+      </c>
+      <c r="C121" s="28" t="inlineStr">
+        <is>
+          <t>L.HHO.InterFddTdd.ULquality.PrepAttOut</t>
+        </is>
+      </c>
+      <c r="D121" s="13" t="inlineStr">
+        <is>
+          <t>UL-quality FDD↔TDD HO preparations</t>
+        </is>
+      </c>
+      <c r="E121" s="13" t="inlineStr">
+        <is>
+          <t>Table 4-3</t>
+        </is>
+      </c>
+      <c r="F121" s="14" t="n"/>
+      <c r="G121" s="14" t="n"/>
       <c r="H121" s="14" t="n"/>
       <c r="I121" s="14" t="n"/>
       <c r="J121" s="15" t="n"/>
     </row>
-    <row r="122" ht="24" customHeight="1">
-      <c r="A122" s="34" t="n">
-        <v>20</v>
-      </c>
-      <c r="B122" s="34" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="C122" s="13" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="D122" s="13" t="inlineStr">
-        <is>
-          <t>FDD/TDD</t>
-        </is>
-      </c>
-      <c r="E122" s="13" t="inlineStr">
-        <is>
-          <t>Deactivate SC</t>
-        </is>
-      </c>
-      <c r="F122" s="28" t="inlineStr">
-        <is>
-          <t>MOD CAMGTCFG: LocalCellId=0, CellCaAlgoSwitch=SpectrumCoordinationSwitch-0;</t>
-        </is>
-      </c>
-      <c r="G122" s="13" t="inlineStr">
-        <is>
-          <t>Doc deactivation (3CC). Repeat 1 and 2.</t>
-        </is>
-      </c>
+    <row r="122" ht="32" customHeight="1">
+      <c r="A122" s="30" t="n">
+        <v>5</v>
+      </c>
+      <c r="B122" s="16" t="inlineStr">
+        <is>
+          <t>1526729997</t>
+        </is>
+      </c>
+      <c r="C122" s="29" t="inlineStr">
+        <is>
+          <t>L.HHO.InterFddTdd.ULquality.ExecAttOut</t>
+        </is>
+      </c>
+      <c r="D122" s="16" t="inlineStr">
+        <is>
+          <t>UL-quality FDD↔TDD HO executions</t>
+        </is>
+      </c>
+      <c r="E122" s="16" t="inlineStr">
+        <is>
+          <t>Table 4-3</t>
+        </is>
+      </c>
+      <c r="F122" s="14" t="n"/>
+      <c r="G122" s="14" t="n"/>
       <c r="H122" s="14" t="n"/>
       <c r="I122" s="14" t="n"/>
       <c r="J122" s="15" t="n"/>
     </row>
-    <row r="123" ht="24" customHeight="1">
-      <c r="A123" s="30" t="n">
-        <v>21</v>
-      </c>
-      <c r="B123" s="30" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="C123" s="16" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="D123" s="16" t="inlineStr">
-        <is>
-          <t>FDD/TDD</t>
-        </is>
-      </c>
-      <c r="E123" s="16" t="inlineStr">
-        <is>
-          <t>Deactivate SC</t>
-        </is>
-      </c>
-      <c r="F123" s="29" t="inlineStr">
-        <is>
-          <t>MOD CAMGTCFG: LocalCellId=1, CellCaAlgoSwitch=SpectrumCoordinationSwitch-0;</t>
-        </is>
-      </c>
-      <c r="G123" s="16" t="inlineStr"/>
+    <row r="123" ht="32" customHeight="1">
+      <c r="A123" s="34" t="n">
+        <v>6</v>
+      </c>
+      <c r="B123" s="13" t="inlineStr">
+        <is>
+          <t>1526729999</t>
+        </is>
+      </c>
+      <c r="C123" s="28" t="inlineStr">
+        <is>
+          <t>L.HHO.InterFddTdd.ULquality.ExecSuccOut</t>
+        </is>
+      </c>
+      <c r="D123" s="13" t="inlineStr">
+        <is>
+          <t>UL-quality FDD↔TDD HO success</t>
+        </is>
+      </c>
+      <c r="E123" s="13" t="inlineStr">
+        <is>
+          <t>Table 4-3</t>
+        </is>
+      </c>
+      <c r="F123" s="14" t="n"/>
+      <c r="G123" s="14" t="n"/>
       <c r="H123" s="14" t="n"/>
       <c r="I123" s="14" t="n"/>
       <c r="J123" s="15" t="n"/>
     </row>
-    <row r="124" ht="24" customHeight="1">
-      <c r="A124" s="34" t="n">
-        <v>22</v>
-      </c>
-      <c r="B124" s="34" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="C124" s="13" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="D124" s="13" t="inlineStr">
-        <is>
-          <t>FDD/TDD</t>
-        </is>
-      </c>
-      <c r="E124" s="13" t="inlineStr">
-        <is>
-          <t>Deactivate SC</t>
-        </is>
-      </c>
-      <c r="F124" s="28" t="inlineStr">
-        <is>
-          <t>MOD CAMGTCFG: LocalCellId=2, CellCaAlgoSwitch=SpectrumCoordinationSwitch-0;</t>
-        </is>
-      </c>
-      <c r="G124" s="13" t="inlineStr"/>
+    <row r="124" ht="32" customHeight="1">
+      <c r="A124" s="30" t="n">
+        <v>7</v>
+      </c>
+      <c r="B124" s="16" t="inlineStr">
+        <is>
+          <t>1526728426</t>
+        </is>
+      </c>
+      <c r="C124" s="29" t="inlineStr">
+        <is>
+          <t>L.Traffic.User.PCell.DL.Avg</t>
+        </is>
+      </c>
+      <c r="D124" s="16" t="inlineStr">
+        <is>
+          <t>Avg CA UEs using this cell as PCell</t>
+        </is>
+      </c>
+      <c r="E124" s="16" t="inlineStr">
+        <is>
+          <t>Table 4-4 / 5-8; Ch.4.2.2 says this moves after PCell swap</t>
+        </is>
+      </c>
+      <c r="F124" s="14" t="n"/>
+      <c r="G124" s="14" t="n"/>
       <c r="H124" s="14" t="n"/>
       <c r="I124" s="14" t="n"/>
       <c r="J124" s="15" t="n"/>
     </row>
-    <row r="125" ht="24" customHeight="1">
-      <c r="A125" s="30" t="n">
-        <v>23</v>
-      </c>
-      <c r="B125" s="30" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="C125" s="16" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="D125" s="16" t="inlineStr">
-        <is>
-          <t>FDD/TDD</t>
-        </is>
-      </c>
-      <c r="E125" s="16" t="inlineStr">
-        <is>
-          <t>Activate enhancement</t>
-        </is>
-      </c>
-      <c r="F125" s="29" t="inlineStr">
-        <is>
-          <t>MOD ENODEBALGOSWITCH: CaAlgoSwitch=HoWithSccCfgSwitch-1;</t>
-        </is>
-      </c>
-      <c r="G125" s="16" t="inlineStr">
-        <is>
-          <t>Ch.5.4.1.2 Activating LTE spectrum coordination enhancement.</t>
-        </is>
-      </c>
+    <row r="125" ht="32" customHeight="1">
+      <c r="A125" s="34" t="n">
+        <v>8</v>
+      </c>
+      <c r="B125" s="13" t="inlineStr">
+        <is>
+          <t>1526728427</t>
+        </is>
+      </c>
+      <c r="C125" s="28" t="inlineStr">
+        <is>
+          <t>L.Traffic.User.SCell.DL.Avg</t>
+        </is>
+      </c>
+      <c r="D125" s="13" t="inlineStr">
+        <is>
+          <t>Avg CA UEs using this cell as SCell</t>
+        </is>
+      </c>
+      <c r="E125" s="13" t="inlineStr">
+        <is>
+          <t>Table 4-4 / 5-8</t>
+        </is>
+      </c>
+      <c r="F125" s="14" t="n"/>
+      <c r="G125" s="14" t="n"/>
       <c r="H125" s="14" t="n"/>
       <c r="I125" s="14" t="n"/>
       <c r="J125" s="15" t="n"/>
     </row>
-    <row r="126" ht="24" customHeight="1">
-      <c r="A126" s="34" t="n">
-        <v>24</v>
-      </c>
-      <c r="B126" s="34" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="C126" s="13" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="D126" s="13" t="inlineStr">
-        <is>
-          <t>FDD/TDD</t>
-        </is>
-      </c>
-      <c r="E126" s="13" t="inlineStr">
-        <is>
-          <t>Activate enhancement</t>
-        </is>
-      </c>
-      <c r="F126" s="28" t="inlineStr">
-        <is>
-          <t>MOD CELL: LocalCellId=0, SpecifiedCellFlag=MBBSERCELL;</t>
-        </is>
-      </c>
-      <c r="G126" s="13" t="inlineStr">
-        <is>
-          <t>Low-frequency cell as MBB service cell.</t>
-        </is>
-      </c>
+    <row r="126" ht="32" customHeight="1">
+      <c r="A126" s="30" t="n">
+        <v>9</v>
+      </c>
+      <c r="B126" s="16" t="inlineStr">
+        <is>
+          <t>1526732658</t>
+        </is>
+      </c>
+      <c r="C126" s="29" t="inlineStr">
+        <is>
+          <t>L.CA.Traffic.bits.DL.PCell</t>
+        </is>
+      </c>
+      <c r="D126" s="16" t="inlineStr">
+        <is>
+          <t>DL bits on PCell of CA UEs</t>
+        </is>
+      </c>
+      <c r="E126" s="16" t="inlineStr">
+        <is>
+          <t>Table 4-4 / 5-8</t>
+        </is>
+      </c>
+      <c r="F126" s="14" t="n"/>
+      <c r="G126" s="14" t="n"/>
       <c r="H126" s="14" t="n"/>
       <c r="I126" s="14" t="n"/>
       <c r="J126" s="15" t="n"/>
     </row>
-    <row r="127" ht="24" customHeight="1">
-      <c r="A127" s="30" t="n">
-        <v>25</v>
-      </c>
-      <c r="B127" s="30" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="C127" s="16" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="D127" s="16" t="inlineStr">
-        <is>
-          <t>FDD/TDD</t>
-        </is>
-      </c>
-      <c r="E127" s="16" t="inlineStr">
-        <is>
-          <t>Activate enhancement</t>
-        </is>
-      </c>
-      <c r="F127" s="29" t="inlineStr">
-        <is>
-          <t>MOD CAMGTCFG: LocalCellId=0, CellCaAlgoSwitch=WbbCaMultiCarrierCoordSw-1;</t>
-        </is>
-      </c>
-      <c r="G127" s="16" t="inlineStr">
-        <is>
-          <t>Low- and high-frequency cells (doc 0 and 1).</t>
-        </is>
-      </c>
+    <row r="127" ht="32" customHeight="1">
+      <c r="A127" s="34" t="n">
+        <v>10</v>
+      </c>
+      <c r="B127" s="13" t="inlineStr">
+        <is>
+          <t>1526729259</t>
+        </is>
+      </c>
+      <c r="C127" s="28" t="inlineStr">
+        <is>
+          <t>L.CA.Traffic.bits.DL.SCell</t>
+        </is>
+      </c>
+      <c r="D127" s="13" t="inlineStr">
+        <is>
+          <t>DL bits on SCell of CA UEs</t>
+        </is>
+      </c>
+      <c r="E127" s="13" t="inlineStr">
+        <is>
+          <t>Table 4-4 / 5-8</t>
+        </is>
+      </c>
+      <c r="F127" s="14" t="n"/>
+      <c r="G127" s="14" t="n"/>
       <c r="H127" s="14" t="n"/>
       <c r="I127" s="14" t="n"/>
       <c r="J127" s="15" t="n"/>
     </row>
-    <row r="128" ht="24" customHeight="1">
-      <c r="A128" s="34" t="n">
-        <v>26</v>
-      </c>
-      <c r="B128" s="34" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="C128" s="13" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="D128" s="13" t="inlineStr">
-        <is>
-          <t>FDD/TDD</t>
-        </is>
-      </c>
-      <c r="E128" s="13" t="inlineStr">
-        <is>
-          <t>Activate enhancement</t>
-        </is>
-      </c>
-      <c r="F128" s="28" t="inlineStr">
-        <is>
-          <t>MOD CAMGTCFG: LocalCellId=1, CellCaAlgoSwitch=WbbCaMultiCarrierCoordSw-1;</t>
-        </is>
-      </c>
-      <c r="G128" s="13" t="inlineStr"/>
+    <row r="128" ht="32" customHeight="1">
+      <c r="A128" s="30" t="n">
+        <v>11</v>
+      </c>
+      <c r="B128" s="16" t="inlineStr">
+        <is>
+          <t>1526728564</t>
+        </is>
+      </c>
+      <c r="C128" s="29" t="inlineStr">
+        <is>
+          <t>L.Thrp.bits.DL.CAUser</t>
+        </is>
+      </c>
+      <c r="D128" s="16" t="inlineStr">
+        <is>
+          <t>CA UE DL bits</t>
+        </is>
+      </c>
+      <c r="E128" s="16" t="inlineStr">
+        <is>
+          <t>Table 4-4 / 5-5 / 5-8; CA UE rate KPI</t>
+        </is>
+      </c>
+      <c r="F128" s="14" t="n"/>
+      <c r="G128" s="14" t="n"/>
       <c r="H128" s="14" t="n"/>
       <c r="I128" s="14" t="n"/>
       <c r="J128" s="15" t="n"/>
     </row>
-    <row r="129" ht="24" customHeight="1">
-      <c r="A129" s="30" t="n">
-        <v>27</v>
-      </c>
-      <c r="B129" s="30" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="C129" s="16" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="D129" s="16" t="inlineStr">
-        <is>
-          <t>FDD/TDD</t>
-        </is>
-      </c>
-      <c r="E129" s="16" t="inlineStr">
-        <is>
-          <t>Optimize enhancement</t>
-        </is>
-      </c>
-      <c r="F129" s="29" t="inlineStr">
-        <is>
-          <t>MOD CELLWTTXPARACFG: LocalCellId=0, WbbMultiCarrierCoordA2Ofs=2;</t>
-        </is>
-      </c>
-      <c r="G129" s="16" t="inlineStr">
-        <is>
-          <t>Doc: Setting WbbMultiCarrierCoordA2Ofs (repeat 0,1).</t>
-        </is>
-      </c>
+    <row r="129" ht="32" customHeight="1">
+      <c r="A129" s="34" t="n">
+        <v>12</v>
+      </c>
+      <c r="B129" s="13" t="inlineStr">
+        <is>
+          <t>1526740440</t>
+        </is>
+      </c>
+      <c r="C129" s="28" t="inlineStr">
+        <is>
+          <t>L.Thrp.bits.DL.LastTTI.CAUser</t>
+        </is>
+      </c>
+      <c r="D129" s="13" t="inlineStr">
+        <is>
+          <t>CA UE last-TTI DL bits</t>
+        </is>
+      </c>
+      <c r="E129" s="13" t="inlineStr">
+        <is>
+          <t>Table 4-4 / 5-5</t>
+        </is>
+      </c>
+      <c r="F129" s="14" t="n"/>
+      <c r="G129" s="14" t="n"/>
       <c r="H129" s="14" t="n"/>
       <c r="I129" s="14" t="n"/>
       <c r="J129" s="15" t="n"/>
     </row>
-    <row r="130" ht="24" customHeight="1">
-      <c r="A130" s="34" t="n">
-        <v>28</v>
-      </c>
-      <c r="B130" s="34" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="C130" s="13" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="D130" s="13" t="inlineStr">
-        <is>
-          <t>FDD/TDD</t>
-        </is>
-      </c>
-      <c r="E130" s="13" t="inlineStr">
-        <is>
-          <t>Optimize enhancement</t>
-        </is>
-      </c>
-      <c r="F130" s="28" t="inlineStr">
-        <is>
-          <t>MOD CELLWTTXPARACFG: LocalCellId=1, WbbMultiCarrierCoordA2Ofs=2;</t>
-        </is>
-      </c>
-      <c r="G130" s="13" t="inlineStr"/>
+    <row r="130" ht="32" customHeight="1">
+      <c r="A130" s="30" t="n">
+        <v>13</v>
+      </c>
+      <c r="B130" s="16" t="inlineStr">
+        <is>
+          <t>1526740441</t>
+        </is>
+      </c>
+      <c r="C130" s="29" t="inlineStr">
+        <is>
+          <t>L.Thrp.Time.DL.RmvLastTTI.CAUser</t>
+        </is>
+      </c>
+      <c r="D130" s="16" t="inlineStr">
+        <is>
+          <t>CA UE DL time last-TTI removed</t>
+        </is>
+      </c>
+      <c r="E130" s="16" t="inlineStr">
+        <is>
+          <t>Table 4-4 / 5-5</t>
+        </is>
+      </c>
+      <c r="F130" s="14" t="n"/>
+      <c r="G130" s="14" t="n"/>
       <c r="H130" s="14" t="n"/>
       <c r="I130" s="14" t="n"/>
       <c r="J130" s="15" t="n"/>
     </row>
-    <row r="131" ht="24" customHeight="1">
-      <c r="A131" s="30" t="n">
-        <v>29</v>
-      </c>
-      <c r="B131" s="30" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="C131" s="16" t="inlineStr">
-        <is>
-          <t>Adaptive</t>
-        </is>
-      </c>
-      <c r="D131" s="16" t="inlineStr">
-        <is>
-          <t>FDD/TDD</t>
-        </is>
-      </c>
-      <c r="E131" s="16" t="inlineStr">
-        <is>
-          <t>Optimize enhancement</t>
-        </is>
-      </c>
-      <c r="F131" s="29" t="inlineStr">
-        <is>
-          <t>MOD SCCFREQCFG: PccDlEarfcn=123, SccDlEarfcn=456, SccA2RsrpThldExtendedOfs=-10;</t>
-        </is>
-      </c>
-      <c r="G131" s="16" t="inlineStr">
-        <is>
-          <t>Doc: low-frequency PCC EARFCN 123, high-frequency WBB SCC EARFCN 456.</t>
-        </is>
-      </c>
+    <row r="131" ht="32" customHeight="1">
+      <c r="A131" s="34" t="n">
+        <v>14</v>
+      </c>
+      <c r="B131" s="13" t="inlineStr">
+        <is>
+          <t>1526729045</t>
+        </is>
+      </c>
+      <c r="C131" s="28" t="inlineStr">
+        <is>
+          <t>L.CA.DLSCell.Add.Att</t>
+        </is>
+      </c>
+      <c r="D131" s="13" t="inlineStr">
+        <is>
+          <t>DL SCell add attempts</t>
+        </is>
+      </c>
+      <c r="E131" s="13" t="inlineStr">
+        <is>
+          <t>Table 4-4 / 5-8; SCell cfg success vs HO</t>
+        </is>
+      </c>
+      <c r="F131" s="14" t="n"/>
+      <c r="G131" s="14" t="n"/>
       <c r="H131" s="14" t="n"/>
       <c r="I131" s="14" t="n"/>
       <c r="J131" s="15" t="n"/>
     </row>
-    <row r="132" ht="24" customHeight="1">
-      <c r="A132" s="34" t="n">
-        <v>30</v>
-      </c>
-      <c r="B132" s="34" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="C132" s="13" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="D132" s="13" t="inlineStr">
-        <is>
-          <t>FDD/TDD</t>
-        </is>
-      </c>
-      <c r="E132" s="13" t="inlineStr">
-        <is>
-          <t>Deactivate enhancement</t>
-        </is>
-      </c>
-      <c r="F132" s="28" t="inlineStr">
-        <is>
-          <t>MOD CAMGTCFG: LocalCellId=0, CellCaAlgoSwitch=WbbCaMultiCarrierCoordSw-0;</t>
-        </is>
-      </c>
-      <c r="G132" s="13" t="inlineStr">
-        <is>
-          <t>Doc deactivation. Repeat LocalCellId=1.</t>
-        </is>
-      </c>
+    <row r="132" ht="32" customHeight="1">
+      <c r="A132" s="30" t="n">
+        <v>15</v>
+      </c>
+      <c r="B132" s="16" t="inlineStr">
+        <is>
+          <t>1526729046</t>
+        </is>
+      </c>
+      <c r="C132" s="29" t="inlineStr">
+        <is>
+          <t>L.CA.DLSCell.Add.Succ</t>
+        </is>
+      </c>
+      <c r="D132" s="16" t="inlineStr">
+        <is>
+          <t>DL SCell add success</t>
+        </is>
+      </c>
+      <c r="E132" s="16" t="inlineStr">
+        <is>
+          <t>Table 4-4 / 5-8</t>
+        </is>
+      </c>
+      <c r="F132" s="14" t="n"/>
+      <c r="G132" s="14" t="n"/>
       <c r="H132" s="14" t="n"/>
       <c r="I132" s="14" t="n"/>
       <c r="J132" s="15" t="n"/>
     </row>
-    <row r="133" ht="24" customHeight="1">
-      <c r="A133" s="30" t="n">
-        <v>31</v>
-      </c>
-      <c r="B133" s="30" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="C133" s="16" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="D133" s="16" t="inlineStr">
-        <is>
-          <t>FDD/TDD</t>
-        </is>
-      </c>
-      <c r="E133" s="16" t="inlineStr">
-        <is>
-          <t>Deactivate enhancement</t>
-        </is>
-      </c>
-      <c r="F133" s="29" t="inlineStr">
-        <is>
-          <t>MOD CAMGTCFG: LocalCellId=1, CellCaAlgoSwitch=WbbCaMultiCarrierCoordSw-0;</t>
-        </is>
-      </c>
-      <c r="G133" s="16" t="inlineStr"/>
+    <row r="133" ht="32" customHeight="1">
+      <c r="A133" s="34" t="n">
+        <v>16</v>
+      </c>
+      <c r="B133" s="13" t="inlineStr">
+        <is>
+          <t>1526746999–7008</t>
+        </is>
+      </c>
+      <c r="C133" s="28" t="inlineStr">
+        <is>
+          <t>L.Thrp.DL.BitRate.Samp.CaUe.Index0 … Index9</t>
+        </is>
+      </c>
+      <c r="D133" s="13" t="inlineStr">
+        <is>
+          <t>CA UE DL bit-rate samples (10 bins)</t>
+        </is>
+      </c>
+      <c r="E133" s="13" t="inlineStr">
+        <is>
+          <t>Table 4-4 monitoring</t>
+        </is>
+      </c>
+      <c r="F133" s="14" t="n"/>
+      <c r="G133" s="14" t="n"/>
       <c r="H133" s="14" t="n"/>
       <c r="I133" s="14" t="n"/>
       <c r="J133" s="15" t="n"/>
     </row>
-    <row r="134" ht="22" customHeight="1">
-      <c r="A134" s="5" t="inlineStr">
-        <is>
-          <t>G.  Counters  (Tables 4-3, 4-4, 5-4–5-8, 5.4.2)</t>
-        </is>
-      </c>
-      <c r="B134" s="6" t="n"/>
-      <c r="C134" s="6" t="n"/>
-      <c r="D134" s="6" t="n"/>
-      <c r="E134" s="6" t="n"/>
-      <c r="F134" s="6" t="n"/>
-      <c r="G134" s="6" t="n"/>
-      <c r="H134" s="6" t="n"/>
-      <c r="I134" s="6" t="n"/>
-      <c r="J134" s="6" t="n"/>
-    </row>
-    <row r="135" ht="22" customHeight="1">
-      <c r="A135" s="12" t="inlineStr">
-        <is>
-          <t>SN</t>
-        </is>
-      </c>
-      <c r="B135" s="12" t="inlineStr">
-        <is>
-          <t>Counter ID</t>
-        </is>
-      </c>
-      <c r="C135" s="12" t="inlineStr">
-        <is>
-          <t>Counter Name</t>
-        </is>
-      </c>
-      <c r="D135" s="12" t="inlineStr">
-        <is>
-          <t>Function / what it measures</t>
-        </is>
-      </c>
-      <c r="E135" s="12" t="inlineStr">
-        <is>
-          <t>Use</t>
-        </is>
-      </c>
-      <c r="F135" s="12" t="inlineStr"/>
-      <c r="G135" s="12" t="inlineStr"/>
-      <c r="H135" s="12" t="inlineStr"/>
-      <c r="I135" s="12" t="inlineStr"/>
-      <c r="J135" s="12" t="inlineStr"/>
+    <row r="134" ht="32" customHeight="1">
+      <c r="A134" s="30" t="n">
+        <v>17</v>
+      </c>
+      <c r="B134" s="16" t="inlineStr">
+        <is>
+          <t>1526728261</t>
+        </is>
+      </c>
+      <c r="C134" s="29" t="inlineStr">
+        <is>
+          <t>L.Thrp.bits.DL</t>
+        </is>
+      </c>
+      <c r="D134" s="16" t="inlineStr">
+        <is>
+          <t>All-UE DL bits</t>
+        </is>
+      </c>
+      <c r="E134" s="16" t="inlineStr">
+        <is>
+          <t>Table 5-4 MBB perceived rate</t>
+        </is>
+      </c>
+      <c r="F134" s="14" t="n"/>
+      <c r="G134" s="14" t="n"/>
+      <c r="H134" s="14" t="n"/>
+      <c r="I134" s="14" t="n"/>
+      <c r="J134" s="15" t="n"/>
+    </row>
+    <row r="135" ht="32" customHeight="1">
+      <c r="A135" s="34" t="n">
+        <v>18</v>
+      </c>
+      <c r="B135" s="13" t="inlineStr">
+        <is>
+          <t>1526729005</t>
+        </is>
+      </c>
+      <c r="C135" s="28" t="inlineStr">
+        <is>
+          <t>L.Thrp.bits.DL.LastTTI</t>
+        </is>
+      </c>
+      <c r="D135" s="13" t="inlineStr">
+        <is>
+          <t>All-UE last-TTI DL bits</t>
+        </is>
+      </c>
+      <c r="E135" s="13" t="inlineStr">
+        <is>
+          <t>Table 5-4</t>
+        </is>
+      </c>
+      <c r="F135" s="14" t="n"/>
+      <c r="G135" s="14" t="n"/>
+      <c r="H135" s="14" t="n"/>
+      <c r="I135" s="14" t="n"/>
+      <c r="J135" s="15" t="n"/>
     </row>
     <row r="136" ht="32" customHeight="1">
       <c r="A136" s="30" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="B136" s="16" t="inlineStr">
         <is>
-          <t>1526729994</t>
+          <t>1526745879</t>
         </is>
       </c>
       <c r="C136" s="29" t="inlineStr">
         <is>
-          <t>L.HHO.InterFreq.ULquality.PrepAttOut</t>
+          <t>L.Thrp.bits.DL.WBB</t>
         </is>
       </c>
       <c r="D136" s="16" t="inlineStr">
         <is>
-          <t>UL-quality inter-freq HO preparations</t>
+          <t>WBB DL bits</t>
         </is>
       </c>
       <c r="E136" s="16" t="inlineStr">
         <is>
-          <t>Table 4-3 activation: values increase ⇒ SC has taken effect</t>
+          <t>Tables 5-4 / 5-6</t>
         </is>
       </c>
       <c r="F136" s="14" t="n"/>
@@ -4263,26 +4192,26 @@
     </row>
     <row r="137" ht="32" customHeight="1">
       <c r="A137" s="34" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="B137" s="13" t="inlineStr">
         <is>
-          <t>1526729996</t>
+          <t>1526745880</t>
         </is>
       </c>
       <c r="C137" s="28" t="inlineStr">
         <is>
-          <t>L.HHO.InterFreq.ULquality.ExecAttOut</t>
+          <t>L.Thrp.bits.DL.LastTTI.WBB</t>
         </is>
       </c>
       <c r="D137" s="13" t="inlineStr">
         <is>
-          <t>UL-quality inter-freq HO executions</t>
+          <t>WBB last-TTI DL bits</t>
         </is>
       </c>
       <c r="E137" s="13" t="inlineStr">
         <is>
-          <t>Table 4-3</t>
+          <t>Tables 5-4 / 5-6</t>
         </is>
       </c>
       <c r="F137" s="14" t="n"/>
@@ -4293,26 +4222,26 @@
     </row>
     <row r="138" ht="32" customHeight="1">
       <c r="A138" s="30" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="B138" s="16" t="inlineStr">
         <is>
-          <t>1526729998</t>
+          <t>1526729015</t>
         </is>
       </c>
       <c r="C138" s="29" t="inlineStr">
         <is>
-          <t>L.HHO.InterFreq.ULquality.ExecSuccOut</t>
+          <t>L.Thrp.Time.DL.RmvLastTTI</t>
         </is>
       </c>
       <c r="D138" s="16" t="inlineStr">
         <is>
-          <t>UL-quality inter-freq HO success</t>
+          <t>All-UE DL time last-TTI removed</t>
         </is>
       </c>
       <c r="E138" s="16" t="inlineStr">
         <is>
-          <t>Table 4-3; success rate KPI</t>
+          <t>Table 5-4</t>
         </is>
       </c>
       <c r="F138" s="14" t="n"/>
@@ -4323,26 +4252,26 @@
     </row>
     <row r="139" ht="32" customHeight="1">
       <c r="A139" s="34" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="B139" s="13" t="inlineStr">
         <is>
-          <t>1526729995</t>
+          <t>1526745881</t>
         </is>
       </c>
       <c r="C139" s="28" t="inlineStr">
         <is>
-          <t>L.HHO.InterFddTdd.ULquality.PrepAttOut</t>
+          <t>L.Thrp.Time.DL.RmvLastTTI.WBB</t>
         </is>
       </c>
       <c r="D139" s="13" t="inlineStr">
         <is>
-          <t>UL-quality FDD↔TDD HO preparations</t>
+          <t>WBB DL time last-TTI removed</t>
         </is>
       </c>
       <c r="E139" s="13" t="inlineStr">
         <is>
-          <t>Table 4-3</t>
+          <t>Tables 5-4 / 5-6; Ch.5.2.2 may increase</t>
         </is>
       </c>
       <c r="F139" s="14" t="n"/>
@@ -4353,26 +4282,26 @@
     </row>
     <row r="140" ht="32" customHeight="1">
       <c r="A140" s="30" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="B140" s="16" t="inlineStr">
         <is>
-          <t>1526729997</t>
+          <t>1526735542</t>
         </is>
       </c>
       <c r="C140" s="29" t="inlineStr">
         <is>
-          <t>L.HHO.InterFddTdd.ULquality.ExecAttOut</t>
+          <t>L.Thrp.Relay.bits.DL</t>
         </is>
       </c>
       <c r="D140" s="16" t="inlineStr">
         <is>
-          <t>UL-quality FDD↔TDD HO executions</t>
+          <t>RRN DL bits</t>
         </is>
       </c>
       <c r="E140" s="16" t="inlineStr">
         <is>
-          <t>Table 4-3</t>
+          <t>Table 5-7</t>
         </is>
       </c>
       <c r="F140" s="14" t="n"/>
@@ -4383,26 +4312,26 @@
     </row>
     <row r="141" ht="32" customHeight="1">
       <c r="A141" s="34" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="B141" s="13" t="inlineStr">
         <is>
-          <t>1526729999</t>
+          <t>1526735543</t>
         </is>
       </c>
       <c r="C141" s="28" t="inlineStr">
         <is>
-          <t>L.HHO.InterFddTdd.ULquality.ExecSuccOut</t>
+          <t>L.Thrp.Relay.Time.DL</t>
         </is>
       </c>
       <c r="D141" s="13" t="inlineStr">
         <is>
-          <t>UL-quality FDD↔TDD HO success</t>
+          <t>RRN DL time</t>
         </is>
       </c>
       <c r="E141" s="13" t="inlineStr">
         <is>
-          <t>Table 4-3</t>
+          <t>Table 5-7; Ch.5.4.2: increase on low-freq cells ⇒ RRN enhancement took effect</t>
         </is>
       </c>
       <c r="F141" s="14" t="n"/>
@@ -4413,26 +4342,26 @@
     </row>
     <row r="142" ht="32" customHeight="1">
       <c r="A142" s="30" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="B142" s="16" t="inlineStr">
         <is>
-          <t>1526728426</t>
+          <t>1526745954</t>
         </is>
       </c>
       <c r="C142" s="29" t="inlineStr">
         <is>
-          <t>L.Traffic.User.PCell.DL.Avg</t>
+          <t>L.ChMeas.PRB.DL.PDSCH.WBBUsed.Avg</t>
         </is>
       </c>
       <c r="D142" s="16" t="inlineStr">
         <is>
-          <t>Avg CA UEs using this cell as PCell</t>
+          <t>Avg PDSCH PRBs used by WBB</t>
         </is>
       </c>
       <c r="E142" s="16" t="inlineStr">
         <is>
-          <t>Table 4-4 / 5-8; Ch.4.2.2 says this moves after PCell swap</t>
+          <t>Ch.5.2.2: decreases on low-freq, increases on high-freq</t>
         </is>
       </c>
       <c r="F142" s="14" t="n"/>
@@ -4443,26 +4372,26 @@
     </row>
     <row r="143" ht="32" customHeight="1">
       <c r="A143" s="34" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="B143" s="13" t="inlineStr">
         <is>
-          <t>1526728427</t>
+          <t>1526740478</t>
         </is>
       </c>
       <c r="C143" s="28" t="inlineStr">
         <is>
-          <t>L.Traffic.User.SCell.DL.Avg</t>
+          <t>L.Traffic.SpecSerUser.Avg</t>
         </is>
       </c>
       <c r="D143" s="13" t="inlineStr">
         <is>
-          <t>Avg CA UEs using this cell as SCell</t>
+          <t>Specified-service (MBB) users</t>
         </is>
       </c>
       <c r="E143" s="13" t="inlineStr">
         <is>
-          <t>Table 4-4 / 5-8</t>
+          <t>Ch.5.4.2: decrease to a non-zero value on low-freq cells ⇒ WBB enhancement took effect</t>
         </is>
       </c>
       <c r="F143" s="14" t="n"/>
@@ -4471,88 +4400,78 @@
       <c r="I143" s="14" t="n"/>
       <c r="J143" s="15" t="n"/>
     </row>
-    <row r="144" ht="32" customHeight="1">
-      <c r="A144" s="30" t="n">
-        <v>9</v>
-      </c>
-      <c r="B144" s="16" t="inlineStr">
-        <is>
-          <t>1526732658</t>
-        </is>
-      </c>
-      <c r="C144" s="29" t="inlineStr">
-        <is>
-          <t>L.CA.Traffic.bits.DL.PCell</t>
-        </is>
-      </c>
-      <c r="D144" s="16" t="inlineStr">
-        <is>
-          <t>DL bits on PCell of CA UEs</t>
-        </is>
-      </c>
-      <c r="E144" s="16" t="inlineStr">
-        <is>
-          <t>Table 4-4 / 5-8</t>
-        </is>
-      </c>
-      <c r="F144" s="14" t="n"/>
-      <c r="G144" s="14" t="n"/>
-      <c r="H144" s="14" t="n"/>
-      <c r="I144" s="14" t="n"/>
-      <c r="J144" s="15" t="n"/>
-    </row>
-    <row r="145" ht="32" customHeight="1">
-      <c r="A145" s="34" t="n">
-        <v>10</v>
-      </c>
-      <c r="B145" s="13" t="inlineStr">
-        <is>
-          <t>1526729259</t>
-        </is>
-      </c>
-      <c r="C145" s="28" t="inlineStr">
-        <is>
-          <t>L.CA.Traffic.bits.DL.SCell</t>
-        </is>
-      </c>
-      <c r="D145" s="13" t="inlineStr">
-        <is>
-          <t>DL bits on SCell of CA UEs</t>
-        </is>
-      </c>
-      <c r="E145" s="13" t="inlineStr">
-        <is>
-          <t>Table 4-4 / 5-8</t>
-        </is>
-      </c>
-      <c r="F145" s="14" t="n"/>
-      <c r="G145" s="14" t="n"/>
-      <c r="H145" s="14" t="n"/>
-      <c r="I145" s="14" t="n"/>
-      <c r="J145" s="15" t="n"/>
-    </row>
-    <row r="146" ht="32" customHeight="1">
-      <c r="A146" s="30" t="n">
-        <v>11</v>
-      </c>
-      <c r="B146" s="16" t="inlineStr">
-        <is>
-          <t>1526728564</t>
-        </is>
-      </c>
-      <c r="C146" s="29" t="inlineStr">
-        <is>
-          <t>L.Thrp.bits.DL.CAUser</t>
-        </is>
-      </c>
-      <c r="D146" s="16" t="inlineStr">
-        <is>
-          <t>CA UE DL bits</t>
-        </is>
-      </c>
-      <c r="E146" s="16" t="inlineStr">
-        <is>
-          <t>Table 4-4 / 5-5 / 5-8; CA UE rate KPI</t>
+    <row r="144" ht="22" customHeight="1">
+      <c r="A144" s="5" t="inlineStr">
+        <is>
+          <t>H.  KPI formulas  (Ch.4.2.1, 4.2.2, 4.4.2, 5.2)</t>
+        </is>
+      </c>
+      <c r="B144" s="6" t="n"/>
+      <c r="C144" s="6" t="n"/>
+      <c r="D144" s="6" t="n"/>
+      <c r="E144" s="6" t="n"/>
+      <c r="F144" s="6" t="n"/>
+      <c r="G144" s="6" t="n"/>
+      <c r="H144" s="6" t="n"/>
+      <c r="I144" s="6" t="n"/>
+      <c r="J144" s="6" t="n"/>
+    </row>
+    <row r="145" ht="22" customHeight="1">
+      <c r="A145" s="12" t="inlineStr">
+        <is>
+          <t>SN</t>
+        </is>
+      </c>
+      <c r="B145" s="12" t="inlineStr">
+        <is>
+          <t>KPI</t>
+        </is>
+      </c>
+      <c r="C145" s="12" t="inlineStr">
+        <is>
+          <t>Formula (from document)</t>
+        </is>
+      </c>
+      <c r="D145" s="12" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="E145" s="12" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="F145" s="12" t="inlineStr"/>
+      <c r="G145" s="12" t="inlineStr"/>
+      <c r="H145" s="12" t="inlineStr"/>
+      <c r="I145" s="12" t="inlineStr"/>
+      <c r="J145" s="12" t="inlineStr"/>
+    </row>
+    <row r="146" ht="48" customHeight="1">
+      <c r="A146" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B146" s="13" t="inlineStr">
+        <is>
+          <t>UL-quality inter-freq HO success</t>
+        </is>
+      </c>
+      <c r="C146" s="13" t="inlineStr">
+        <is>
+          <t>L.HHO.InterFreq.ULquality.ExecSuccOut / L.HHO.InterFreq.ULquality.ExecAttOut × 100%</t>
+        </is>
+      </c>
+      <c r="D146" s="13" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E146" s="13" t="inlineStr">
+        <is>
+          <t>From Table 4-3 counters. Rise in Prep/Exec/Succ verifies activation.</t>
         </is>
       </c>
       <c r="F146" s="14" t="n"/>
@@ -4561,28 +4480,30 @@
       <c r="I146" s="14" t="n"/>
       <c r="J146" s="15" t="n"/>
     </row>
-    <row r="147" ht="32" customHeight="1">
-      <c r="A147" s="34" t="n">
-        <v>12</v>
-      </c>
-      <c r="B147" s="13" t="inlineStr">
-        <is>
-          <t>1526740440</t>
-        </is>
-      </c>
-      <c r="C147" s="28" t="inlineStr">
-        <is>
-          <t>L.Thrp.bits.DL.LastTTI.CAUser</t>
-        </is>
-      </c>
-      <c r="D147" s="13" t="inlineStr">
-        <is>
-          <t>CA UE last-TTI DL bits</t>
-        </is>
-      </c>
-      <c r="E147" s="13" t="inlineStr">
-        <is>
-          <t>Table 4-4 / 5-5</t>
+    <row r="147" ht="48" customHeight="1">
+      <c r="A147" s="16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B147" s="16" t="inlineStr">
+        <is>
+          <t>UL-quality FDD↔TDD HO success</t>
+        </is>
+      </c>
+      <c r="C147" s="16" t="inlineStr">
+        <is>
+          <t>L.HHO.InterFddTdd.ULquality.ExecSuccOut / L.HHO.InterFddTdd.ULquality.ExecAttOut × 100%</t>
+        </is>
+      </c>
+      <c r="D147" s="16" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E147" s="16" t="inlineStr">
+        <is>
+          <t>Table 4-3</t>
         </is>
       </c>
       <c r="F147" s="14" t="n"/>
@@ -4591,28 +4512,30 @@
       <c r="I147" s="14" t="n"/>
       <c r="J147" s="15" t="n"/>
     </row>
-    <row r="148" ht="32" customHeight="1">
-      <c r="A148" s="30" t="n">
-        <v>13</v>
-      </c>
-      <c r="B148" s="16" t="inlineStr">
-        <is>
-          <t>1526740441</t>
-        </is>
-      </c>
-      <c r="C148" s="29" t="inlineStr">
-        <is>
-          <t>L.Thrp.Time.DL.RmvLastTTI.CAUser</t>
-        </is>
-      </c>
-      <c r="D148" s="16" t="inlineStr">
-        <is>
-          <t>CA UE DL time last-TTI removed</t>
-        </is>
-      </c>
-      <c r="E148" s="16" t="inlineStr">
-        <is>
-          <t>Table 4-4 / 5-5</t>
+    <row r="148" ht="48" customHeight="1">
+      <c r="A148" s="13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B148" s="13" t="inlineStr">
+        <is>
+          <t>Average downlink throughput of CA UEs</t>
+        </is>
+      </c>
+      <c r="C148" s="13" t="inlineStr">
+        <is>
+          <t>(L.Thrp.bits.DL.CAUser − L.Thrp.bits.DL.LastTTI.CAUser) / L.Thrp.Time.DL.RmvLastTTI.CAUser</t>
+        </is>
+      </c>
+      <c r="D148" s="13" t="inlineStr">
+        <is>
+          <t>bit/s</t>
+        </is>
+      </c>
+      <c r="E148" s="13" t="inlineStr">
+        <is>
+          <t>Ch.4.2.1 Scenario 1. If CA UE proportion rises after SC, this KPI may even drop.</t>
         </is>
       </c>
       <c r="F148" s="14" t="n"/>
@@ -4621,28 +4544,30 @@
       <c r="I148" s="14" t="n"/>
       <c r="J148" s="15" t="n"/>
     </row>
-    <row r="149" ht="32" customHeight="1">
-      <c r="A149" s="34" t="n">
-        <v>14</v>
-      </c>
-      <c r="B149" s="13" t="inlineStr">
-        <is>
-          <t>1526729045</t>
-        </is>
-      </c>
-      <c r="C149" s="28" t="inlineStr">
-        <is>
-          <t>L.CA.DLSCell.Add.Att</t>
-        </is>
-      </c>
-      <c r="D149" s="13" t="inlineStr">
-        <is>
-          <t>DL SCell add attempts</t>
-        </is>
-      </c>
-      <c r="E149" s="13" t="inlineStr">
-        <is>
-          <t>Table 4-4 / 5-8; SCell cfg success vs HO</t>
+    <row r="149" ht="48" customHeight="1">
+      <c r="A149" s="16" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B149" s="16" t="inlineStr">
+        <is>
+          <t>SCell configuration success rate</t>
+        </is>
+      </c>
+      <c r="C149" s="16" t="inlineStr">
+        <is>
+          <t>L.CA.DLSCell.Add.Succ / L.CA.DLSCell.Add.Att × 100%</t>
+        </is>
+      </c>
+      <c r="D149" s="16" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E149" s="16" t="inlineStr">
+        <is>
+          <t>Ch.4.2.2 / 5.2.2: affected by HO success once HoWithSccCfgSwitch is on.</t>
         </is>
       </c>
       <c r="F149" s="14" t="n"/>
@@ -4651,28 +4576,30 @@
       <c r="I149" s="14" t="n"/>
       <c r="J149" s="15" t="n"/>
     </row>
-    <row r="150" ht="32" customHeight="1">
-      <c r="A150" s="30" t="n">
-        <v>15</v>
-      </c>
-      <c r="B150" s="16" t="inlineStr">
-        <is>
-          <t>1526729046</t>
-        </is>
-      </c>
-      <c r="C150" s="29" t="inlineStr">
-        <is>
-          <t>L.CA.DLSCell.Add.Succ</t>
-        </is>
-      </c>
-      <c r="D150" s="16" t="inlineStr">
-        <is>
-          <t>DL SCell add success</t>
-        </is>
-      </c>
-      <c r="E150" s="16" t="inlineStr">
-        <is>
-          <t>Table 4-4 / 5-8</t>
+    <row r="150" ht="48" customHeight="1">
+      <c r="A150" s="13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B150" s="13" t="inlineStr">
+        <is>
+          <t>Perceived data rate of MBB UEs (enhancement)</t>
+        </is>
+      </c>
+      <c r="C150" s="13" t="inlineStr">
+        <is>
+          <t>[(L.Thrp.bits.DL − L.Thrp.bits.DL.LastTTI) − (L.Thrp.bits.DL.WBB − L.Thrp.bits.DL.LastTTI.WBB)] / (L.Thrp.Time.DL.RmvLastTTI − L.Thrp.Time.DL.RmvLastTTI.WBB)</t>
+        </is>
+      </c>
+      <c r="D150" s="13" t="inlineStr">
+        <is>
+          <t>bit/s</t>
+        </is>
+      </c>
+      <c r="E150" s="13" t="inlineStr">
+        <is>
+          <t>Ch.5.2.1 Table 5-4. Expected to increase when enhancement is activated (low-freq were normal cells).</t>
         </is>
       </c>
       <c r="F150" s="14" t="n"/>
@@ -4681,28 +4608,30 @@
       <c r="I150" s="14" t="n"/>
       <c r="J150" s="15" t="n"/>
     </row>
-    <row r="151" ht="32" customHeight="1">
-      <c r="A151" s="34" t="n">
-        <v>16</v>
-      </c>
-      <c r="B151" s="13" t="inlineStr">
-        <is>
-          <t>1526746999–7008</t>
-        </is>
-      </c>
-      <c r="C151" s="28" t="inlineStr">
-        <is>
-          <t>L.Thrp.DL.BitRate.Samp.CaUe.Index0 … Index9</t>
-        </is>
-      </c>
-      <c r="D151" s="13" t="inlineStr">
-        <is>
-          <t>CA UE DL bit-rate samples (10 bins)</t>
-        </is>
-      </c>
-      <c r="E151" s="13" t="inlineStr">
-        <is>
-          <t>Table 4-4 monitoring</t>
+    <row r="151" ht="48" customHeight="1">
+      <c r="A151" s="16" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B151" s="16" t="inlineStr">
+        <is>
+          <t>Perceived data rate of CA UEs (enhancement impact)</t>
+        </is>
+      </c>
+      <c r="C151" s="16" t="inlineStr">
+        <is>
+          <t>(L.Thrp.bits.DL.CAUser − L.Thrp.bits.DL.LastTTI.CAUser) / L.Thrp.Time.DL.RmvLastTTI.CAUser</t>
+        </is>
+      </c>
+      <c r="D151" s="16" t="inlineStr">
+        <is>
+          <t>bit/s</t>
+        </is>
+      </c>
+      <c r="E151" s="16" t="inlineStr">
+        <is>
+          <t>Ch.5.2.2: overall average perceived CA UE rate decreases after enhancement.</t>
         </is>
       </c>
       <c r="F151" s="14" t="n"/>
@@ -4711,28 +4640,30 @@
       <c r="I151" s="14" t="n"/>
       <c r="J151" s="15" t="n"/>
     </row>
-    <row r="152" ht="32" customHeight="1">
-      <c r="A152" s="30" t="n">
-        <v>17</v>
-      </c>
-      <c r="B152" s="16" t="inlineStr">
-        <is>
-          <t>1526728261</t>
-        </is>
-      </c>
-      <c r="C152" s="29" t="inlineStr">
-        <is>
-          <t>L.Thrp.bits.DL</t>
-        </is>
-      </c>
-      <c r="D152" s="16" t="inlineStr">
-        <is>
-          <t>All-UE DL bits</t>
-        </is>
-      </c>
-      <c r="E152" s="16" t="inlineStr">
-        <is>
-          <t>Table 5-4 MBB perceived rate</t>
+    <row r="152" ht="48" customHeight="1">
+      <c r="A152" s="13" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B152" s="13" t="inlineStr">
+        <is>
+          <t>Perceived data rate of WBB UEs</t>
+        </is>
+      </c>
+      <c r="C152" s="13" t="inlineStr">
+        <is>
+          <t>(L.Thrp.bits.DL.WBB − L.Thrp.bits.DL.LastTTI.WBB) / L.Thrp.Time.DL.RmvLastTTI.WBB</t>
+        </is>
+      </c>
+      <c r="D152" s="13" t="inlineStr">
+        <is>
+          <t>bit/s</t>
+        </is>
+      </c>
+      <c r="E152" s="13" t="inlineStr">
+        <is>
+          <t>Ch.5.2.2 Table 5-6: decreases. CA takes effect for a smaller proportion of WBB UEs.</t>
         </is>
       </c>
       <c r="F152" s="14" t="n"/>
@@ -4741,28 +4672,30 @@
       <c r="I152" s="14" t="n"/>
       <c r="J152" s="15" t="n"/>
     </row>
-    <row r="153" ht="32" customHeight="1">
-      <c r="A153" s="34" t="n">
-        <v>18</v>
-      </c>
-      <c r="B153" s="13" t="inlineStr">
-        <is>
-          <t>1526729005</t>
-        </is>
-      </c>
-      <c r="C153" s="28" t="inlineStr">
-        <is>
-          <t>L.Thrp.bits.DL.LastTTI</t>
-        </is>
-      </c>
-      <c r="D153" s="13" t="inlineStr">
-        <is>
-          <t>All-UE last-TTI DL bits</t>
-        </is>
-      </c>
-      <c r="E153" s="13" t="inlineStr">
-        <is>
-          <t>Table 5-4</t>
+    <row r="153" ht="48" customHeight="1">
+      <c r="A153" s="16" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B153" s="16" t="inlineStr">
+        <is>
+          <t>Perceived data rate of RRNs</t>
+        </is>
+      </c>
+      <c r="C153" s="16" t="inlineStr">
+        <is>
+          <t>L.Thrp.Relay.bits.DL / L.Thrp.Relay.Time.DL</t>
+        </is>
+      </c>
+      <c r="D153" s="16" t="inlineStr">
+        <is>
+          <t>bit/s</t>
+        </is>
+      </c>
+      <c r="E153" s="16" t="inlineStr">
+        <is>
+          <t>Ch.5.2.2 Table 5-7: decreases.</t>
         </is>
       </c>
       <c r="F153" s="14" t="n"/>
@@ -4771,242 +4704,233 @@
       <c r="I153" s="14" t="n"/>
       <c r="J153" s="15" t="n"/>
     </row>
-    <row r="154" ht="32" customHeight="1">
-      <c r="A154" s="30" t="n">
-        <v>19</v>
-      </c>
-      <c r="B154" s="16" t="inlineStr">
-        <is>
-          <t>1526745879</t>
-        </is>
-      </c>
-      <c r="C154" s="29" t="inlineStr">
-        <is>
-          <t>L.Thrp.bits.DL.WBB</t>
-        </is>
-      </c>
-      <c r="D154" s="16" t="inlineStr">
-        <is>
-          <t>WBB DL bits</t>
-        </is>
-      </c>
-      <c r="E154" s="16" t="inlineStr">
-        <is>
-          <t>Tables 5-4 / 5-6</t>
-        </is>
-      </c>
-      <c r="F154" s="14" t="n"/>
-      <c r="G154" s="14" t="n"/>
-      <c r="H154" s="14" t="n"/>
-      <c r="I154" s="14" t="n"/>
-      <c r="J154" s="15" t="n"/>
-    </row>
-    <row r="155" ht="32" customHeight="1">
-      <c r="A155" s="34" t="n">
-        <v>20</v>
-      </c>
-      <c r="B155" s="13" t="inlineStr">
-        <is>
-          <t>1526745880</t>
-        </is>
-      </c>
-      <c r="C155" s="28" t="inlineStr">
-        <is>
-          <t>L.Thrp.bits.DL.LastTTI.WBB</t>
-        </is>
-      </c>
-      <c r="D155" s="13" t="inlineStr">
-        <is>
-          <t>WBB last-TTI DL bits</t>
-        </is>
-      </c>
-      <c r="E155" s="13" t="inlineStr">
-        <is>
-          <t>Tables 5-4 / 5-6</t>
-        </is>
-      </c>
-      <c r="F155" s="14" t="n"/>
-      <c r="G155" s="14" t="n"/>
-      <c r="H155" s="14" t="n"/>
-      <c r="I155" s="14" t="n"/>
-      <c r="J155" s="15" t="n"/>
-    </row>
-    <row r="156" ht="32" customHeight="1">
-      <c r="A156" s="30" t="n">
-        <v>21</v>
-      </c>
-      <c r="B156" s="16" t="inlineStr">
-        <is>
-          <t>1526729015</t>
-        </is>
-      </c>
-      <c r="C156" s="29" t="inlineStr">
-        <is>
-          <t>L.Thrp.Time.DL.RmvLastTTI</t>
-        </is>
-      </c>
-      <c r="D156" s="16" t="inlineStr">
-        <is>
-          <t>All-UE DL time last-TTI removed</t>
-        </is>
-      </c>
-      <c r="E156" s="16" t="inlineStr">
-        <is>
-          <t>Table 5-4</t>
-        </is>
-      </c>
-      <c r="F156" s="14" t="n"/>
-      <c r="G156" s="14" t="n"/>
-      <c r="H156" s="14" t="n"/>
-      <c r="I156" s="14" t="n"/>
-      <c r="J156" s="15" t="n"/>
-    </row>
-    <row r="157" ht="32" customHeight="1">
-      <c r="A157" s="34" t="n">
-        <v>22</v>
-      </c>
-      <c r="B157" s="13" t="inlineStr">
-        <is>
-          <t>1526745881</t>
-        </is>
-      </c>
-      <c r="C157" s="28" t="inlineStr">
-        <is>
-          <t>L.Thrp.Time.DL.RmvLastTTI.WBB</t>
-        </is>
-      </c>
-      <c r="D157" s="13" t="inlineStr">
-        <is>
-          <t>WBB DL time last-TTI removed</t>
-        </is>
-      </c>
-      <c r="E157" s="13" t="inlineStr">
-        <is>
-          <t>Tables 5-4 / 5-6; Ch.5.2.2 may increase</t>
-        </is>
-      </c>
-      <c r="F157" s="14" t="n"/>
-      <c r="G157" s="14" t="n"/>
-      <c r="H157" s="14" t="n"/>
-      <c r="I157" s="14" t="n"/>
-      <c r="J157" s="15" t="n"/>
-    </row>
-    <row r="158" ht="32" customHeight="1">
-      <c r="A158" s="30" t="n">
-        <v>23</v>
-      </c>
-      <c r="B158" s="16" t="inlineStr">
-        <is>
-          <t>1526735542</t>
-        </is>
-      </c>
-      <c r="C158" s="29" t="inlineStr">
-        <is>
-          <t>L.Thrp.Relay.bits.DL</t>
-        </is>
-      </c>
-      <c r="D158" s="16" t="inlineStr">
-        <is>
-          <t>RRN DL bits</t>
-        </is>
-      </c>
-      <c r="E158" s="16" t="inlineStr">
-        <is>
-          <t>Table 5-7</t>
-        </is>
-      </c>
-      <c r="F158" s="14" t="n"/>
-      <c r="G158" s="14" t="n"/>
-      <c r="H158" s="14" t="n"/>
-      <c r="I158" s="14" t="n"/>
-      <c r="J158" s="15" t="n"/>
-    </row>
-    <row r="159" ht="32" customHeight="1">
-      <c r="A159" s="34" t="n">
-        <v>24</v>
+    <row r="154" ht="20" customHeight="1">
+      <c r="A154" s="17" t="inlineStr">
+        <is>
+          <t>H worked example  —  CA UE average DL throughput  (Ch.4.2.1 formula + sample counts)</t>
+        </is>
+      </c>
+      <c r="B154" s="6" t="n"/>
+      <c r="C154" s="6" t="n"/>
+      <c r="D154" s="6" t="n"/>
+      <c r="E154" s="6" t="n"/>
+      <c r="F154" s="6" t="n"/>
+      <c r="G154" s="6" t="n"/>
+      <c r="H154" s="6" t="n"/>
+      <c r="I154" s="6" t="n"/>
+      <c r="J154" s="6" t="n"/>
+    </row>
+    <row r="155" ht="42" customHeight="1">
+      <c r="A155" s="18" t="inlineStr">
+        <is>
+          <t>3GPP / Huawei condition:
+R = (L.Thrp.bits.DL.CAUser − L.Thrp.bits.DL.LastTTI.CAUser) / L.Thrp.Time.DL.RmvLastTTI.CAUser</t>
+        </is>
+      </c>
+      <c r="B155" s="19" t="n"/>
+      <c r="C155" s="19" t="n"/>
+      <c r="D155" s="19" t="n"/>
+      <c r="E155" s="19" t="n"/>
+      <c r="F155" s="19" t="n"/>
+      <c r="G155" s="19" t="n"/>
+      <c r="H155" s="19" t="n"/>
+      <c r="I155" s="19" t="n"/>
+      <c r="J155" s="19" t="n"/>
+    </row>
+    <row r="156" ht="90" customHeight="1">
+      <c r="A156" s="20" t="inlineStr">
+        <is>
+          <t>Worked example (sample values from the document or typical live-network settings):
+Suppose a 15-minute bin on the high/low pair after SC:
+  L.Thrp.bits.DL.CAUser = 7.20×10^12 bit
+  L.Thrp.bits.DL.LastTTI.CAUser = 0.45×10^12 bit
+  L.Thrp.Time.DL.RmvLastTTI.CAUser = 1.50×10^8 ms
+  R = (7.20 − 0.45)×10^12 / 1.50×10^8 = 6.75×10^12 / 1.50×10^8 = 4.50×10^4 bit/ms = 45.0 Mbit/s.
+Result: Compare the same formula on cell-edge bins (PUSCH MCS 0–3 share, Ch.4.2.1 Scenario 1) before vs after SC. If CA UE proportion also rose, Ch.4.2.1 warns this average can fall even when network User DL Average Throughput rose.</t>
+        </is>
+      </c>
+      <c r="B156" s="21" t="n"/>
+      <c r="C156" s="21" t="n"/>
+      <c r="D156" s="21" t="n"/>
+      <c r="E156" s="21" t="n"/>
+      <c r="F156" s="21" t="n"/>
+      <c r="G156" s="21" t="n"/>
+      <c r="H156" s="21" t="n"/>
+      <c r="I156" s="21" t="n"/>
+      <c r="J156" s="21" t="n"/>
+    </row>
+    <row r="157" ht="22" customHeight="1">
+      <c r="A157" s="5" t="inlineStr">
+        <is>
+          <t>I.  Licenses — FDD and TDD  (Ch.4.3.1 / 5.3.1  —  same license covers enhancement)</t>
+        </is>
+      </c>
+      <c r="B157" s="6" t="n"/>
+      <c r="C157" s="6" t="n"/>
+      <c r="D157" s="6" t="n"/>
+      <c r="E157" s="6" t="n"/>
+      <c r="F157" s="6" t="n"/>
+      <c r="G157" s="6" t="n"/>
+      <c r="H157" s="6" t="n"/>
+      <c r="I157" s="6" t="n"/>
+      <c r="J157" s="6" t="n"/>
+    </row>
+    <row r="158" ht="22" customHeight="1">
+      <c r="A158" s="12" t="inlineStr">
+        <is>
+          <t>SN</t>
+        </is>
+      </c>
+      <c r="B158" s="12" t="inlineStr">
+        <is>
+          <t>RAT</t>
+        </is>
+      </c>
+      <c r="C158" s="12" t="inlineStr">
+        <is>
+          <t>Feature ID</t>
+        </is>
+      </c>
+      <c r="D158" s="12" t="inlineStr">
+        <is>
+          <t>Feature name</t>
+        </is>
+      </c>
+      <c r="E158" s="12" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="F158" s="12" t="inlineStr">
+        <is>
+          <t>Sales unit</t>
+        </is>
+      </c>
+      <c r="G158" s="12" t="inlineStr">
+        <is>
+          <t>When consumed</t>
+        </is>
+      </c>
+      <c r="H158" s="12" t="inlineStr"/>
+      <c r="I158" s="12" t="inlineStr"/>
+      <c r="J158" s="12" t="inlineStr"/>
+    </row>
+    <row r="159" ht="48" customHeight="1">
+      <c r="A159" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="B159" s="13" t="inlineStr">
         <is>
-          <t>1526735543</t>
-        </is>
-      </c>
-      <c r="C159" s="28" t="inlineStr">
-        <is>
-          <t>L.Thrp.Relay.Time.DL</t>
+          <t>FDD</t>
+        </is>
+      </c>
+      <c r="C159" s="13" t="inlineStr">
+        <is>
+          <t>LCOFD-131312</t>
         </is>
       </c>
       <c r="D159" s="13" t="inlineStr">
         <is>
-          <t>RRN DL time</t>
+          <t>LTE Spectrum Coordination (LTE FDD)</t>
         </is>
       </c>
       <c r="E159" s="13" t="inlineStr">
         <is>
-          <t>Table 5-7; Ch.5.4.2: increase on low-freq cells ⇒ RRN enhancement took effect</t>
-        </is>
-      </c>
-      <c r="F159" s="14" t="n"/>
-      <c r="G159" s="14" t="n"/>
+          <t>LT1SUNPLTE00</t>
+        </is>
+      </c>
+      <c r="F159" s="13" t="inlineStr">
+        <is>
+          <t>per cell</t>
+        </is>
+      </c>
+      <c r="G159" s="13" t="inlineStr">
+        <is>
+          <t>Ch.4.3.1 and Ch.5.3.1. Enhancement uses the same license. Insufficiency of certain items affects CELL ACTIVATION — see License Control Item Lists.</t>
+        </is>
+      </c>
       <c r="H159" s="14" t="n"/>
       <c r="I159" s="14" t="n"/>
       <c r="J159" s="15" t="n"/>
     </row>
-    <row r="160" ht="32" customHeight="1">
-      <c r="A160" s="30" t="n">
-        <v>25</v>
+    <row r="160" ht="48" customHeight="1">
+      <c r="A160" s="16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="B160" s="16" t="inlineStr">
         <is>
-          <t>1526745954</t>
-        </is>
-      </c>
-      <c r="C160" s="29" t="inlineStr">
-        <is>
-          <t>L.ChMeas.PRB.DL.PDSCH.WBBUsed.Avg</t>
+          <t>TDD</t>
+        </is>
+      </c>
+      <c r="C160" s="16" t="inlineStr">
+        <is>
+          <t>TDLCOFD-131312</t>
         </is>
       </c>
       <c r="D160" s="16" t="inlineStr">
         <is>
-          <t>Avg PDSCH PRBs used by WBB</t>
+          <t>LTE Spectrum Coordination (LTE TDD)</t>
         </is>
       </c>
       <c r="E160" s="16" t="inlineStr">
         <is>
-          <t>Ch.5.2.2: decreases on low-freq, increases on high-freq</t>
-        </is>
-      </c>
-      <c r="F160" s="14" t="n"/>
-      <c r="G160" s="14" t="n"/>
+          <t>LT1SLTESPC00</t>
+        </is>
+      </c>
+      <c r="F160" s="16" t="inlineStr">
+        <is>
+          <t>per cell</t>
+        </is>
+      </c>
+      <c r="G160" s="16" t="inlineStr">
+        <is>
+          <t>Ch.4.3.1 and Ch.5.3.1. Same note on cell activation. No FDD/TDD feature-difference in switches or principles (§2.4).</t>
+        </is>
+      </c>
       <c r="H160" s="14" t="n"/>
       <c r="I160" s="14" t="n"/>
       <c r="J160" s="15" t="n"/>
     </row>
-    <row r="161" ht="32" customHeight="1">
-      <c r="A161" s="34" t="n">
-        <v>26</v>
+    <row r="161" ht="48" customHeight="1">
+      <c r="A161" s="13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="B161" s="13" t="inlineStr">
         <is>
-          <t>1526740478</t>
-        </is>
-      </c>
-      <c r="C161" s="28" t="inlineStr">
-        <is>
-          <t>L.Traffic.SpecSerUser.Avg</t>
+          <t>FDD/TDD</t>
+        </is>
+      </c>
+      <c r="C161" s="13" t="inlineStr">
+        <is>
+          <t>(this workbook Steps 1–4)</t>
         </is>
       </c>
       <c r="D161" s="13" t="inlineStr">
         <is>
-          <t>Specified-service (MBB) users</t>
+          <t>Carrier aggregation (prerequisite)</t>
         </is>
       </c>
       <c r="E161" s="13" t="inlineStr">
         <is>
-          <t>Ch.5.4.2: decrease to a non-zero value on low-freq cells ⇒ WBB enhancement took effect</t>
-        </is>
-      </c>
-      <c r="F161" s="14" t="n"/>
-      <c r="G161" s="14" t="n"/>
+          <t>LAOFD / TDLAOFD / LEOFD as deployed</t>
+        </is>
+      </c>
+      <c r="F161" s="13" t="inlineStr">
+        <is>
+          <t>per cell</t>
+        </is>
+      </c>
+      <c r="G161" s="13" t="inlineStr">
+        <is>
+          <t>CA must already be licensed and active. SC does not replace CA licenses.</t>
+        </is>
+      </c>
       <c r="H161" s="14" t="n"/>
       <c r="I161" s="14" t="n"/>
       <c r="J161" s="15" t="n"/>
@@ -5014,7 +4938,7 @@
     <row r="162" ht="22" customHeight="1">
       <c r="A162" s="5" t="inlineStr">
         <is>
-          <t>H.  KPI formulas  (Ch.4.2.1, 4.2.2, 4.4.2, 5.2)</t>
+          <t>J.  LTE Spectrum Coordination Enhancement  (Ch.5)  —  WBB UEs and RRNs</t>
         </is>
       </c>
       <c r="B162" s="6" t="n"/>
@@ -5027,559 +4951,24 @@
       <c r="I162" s="6" t="n"/>
       <c r="J162" s="6" t="n"/>
     </row>
-    <row r="163" ht="22" customHeight="1">
-      <c r="A163" s="12" t="inlineStr">
-        <is>
-          <t>SN</t>
-        </is>
-      </c>
-      <c r="B163" s="12" t="inlineStr">
-        <is>
-          <t>KPI</t>
-        </is>
-      </c>
-      <c r="C163" s="12" t="inlineStr">
-        <is>
-          <t>Formula (from document)</t>
-        </is>
-      </c>
-      <c r="D163" s="12" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="E163" s="12" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-      <c r="F163" s="12" t="inlineStr"/>
-      <c r="G163" s="12" t="inlineStr"/>
-      <c r="H163" s="12" t="inlineStr"/>
-      <c r="I163" s="12" t="inlineStr"/>
-      <c r="J163" s="12" t="inlineStr"/>
-    </row>
-    <row r="164" ht="48" customHeight="1">
-      <c r="A164" s="13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B164" s="13" t="inlineStr">
-        <is>
-          <t>UL-quality inter-freq HO success</t>
-        </is>
-      </c>
-      <c r="C164" s="13" t="inlineStr">
-        <is>
-          <t>L.HHO.InterFreq.ULquality.ExecSuccOut / L.HHO.InterFreq.ULquality.ExecAttOut × 100%</t>
-        </is>
-      </c>
-      <c r="D164" s="13" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="E164" s="13" t="inlineStr">
-        <is>
-          <t>From Table 4-3 counters. Rise in Prep/Exec/Succ verifies activation.</t>
-        </is>
-      </c>
-      <c r="F164" s="14" t="n"/>
-      <c r="G164" s="14" t="n"/>
-      <c r="H164" s="14" t="n"/>
-      <c r="I164" s="14" t="n"/>
-      <c r="J164" s="15" t="n"/>
-    </row>
-    <row r="165" ht="48" customHeight="1">
-      <c r="A165" s="16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B165" s="16" t="inlineStr">
-        <is>
-          <t>UL-quality FDD↔TDD HO success</t>
-        </is>
-      </c>
-      <c r="C165" s="16" t="inlineStr">
-        <is>
-          <t>L.HHO.InterFddTdd.ULquality.ExecSuccOut / L.HHO.InterFddTdd.ULquality.ExecAttOut × 100%</t>
-        </is>
-      </c>
-      <c r="D165" s="16" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="E165" s="16" t="inlineStr">
-        <is>
-          <t>Table 4-3</t>
-        </is>
-      </c>
-      <c r="F165" s="14" t="n"/>
-      <c r="G165" s="14" t="n"/>
-      <c r="H165" s="14" t="n"/>
-      <c r="I165" s="14" t="n"/>
-      <c r="J165" s="15" t="n"/>
-    </row>
-    <row r="166" ht="48" customHeight="1">
-      <c r="A166" s="13" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B166" s="13" t="inlineStr">
-        <is>
-          <t>Average downlink throughput of CA UEs</t>
-        </is>
-      </c>
-      <c r="C166" s="13" t="inlineStr">
-        <is>
-          <t>(L.Thrp.bits.DL.CAUser − L.Thrp.bits.DL.LastTTI.CAUser) / L.Thrp.Time.DL.RmvLastTTI.CAUser</t>
-        </is>
-      </c>
-      <c r="D166" s="13" t="inlineStr">
-        <is>
-          <t>bit/s</t>
-        </is>
-      </c>
-      <c r="E166" s="13" t="inlineStr">
-        <is>
-          <t>Ch.4.2.1 Scenario 1. If CA UE proportion rises after SC, this KPI may even drop.</t>
-        </is>
-      </c>
-      <c r="F166" s="14" t="n"/>
-      <c r="G166" s="14" t="n"/>
-      <c r="H166" s="14" t="n"/>
-      <c r="I166" s="14" t="n"/>
-      <c r="J166" s="15" t="n"/>
-    </row>
-    <row r="167" ht="48" customHeight="1">
-      <c r="A167" s="16" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B167" s="16" t="inlineStr">
-        <is>
-          <t>SCell configuration success rate</t>
-        </is>
-      </c>
-      <c r="C167" s="16" t="inlineStr">
-        <is>
-          <t>L.CA.DLSCell.Add.Succ / L.CA.DLSCell.Add.Att × 100%</t>
-        </is>
-      </c>
-      <c r="D167" s="16" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="E167" s="16" t="inlineStr">
-        <is>
-          <t>Ch.4.2.2 / 5.2.2: affected by HO success once HoWithSccCfgSwitch is on.</t>
-        </is>
-      </c>
-      <c r="F167" s="14" t="n"/>
-      <c r="G167" s="14" t="n"/>
-      <c r="H167" s="14" t="n"/>
-      <c r="I167" s="14" t="n"/>
-      <c r="J167" s="15" t="n"/>
-    </row>
-    <row r="168" ht="48" customHeight="1">
-      <c r="A168" s="13" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B168" s="13" t="inlineStr">
-        <is>
-          <t>Perceived data rate of MBB UEs (enhancement)</t>
-        </is>
-      </c>
-      <c r="C168" s="13" t="inlineStr">
-        <is>
-          <t>[(L.Thrp.bits.DL − L.Thrp.bits.DL.LastTTI) − (L.Thrp.bits.DL.WBB − L.Thrp.bits.DL.LastTTI.WBB)] / (L.Thrp.Time.DL.RmvLastTTI − L.Thrp.Time.DL.RmvLastTTI.WBB)</t>
-        </is>
-      </c>
-      <c r="D168" s="13" t="inlineStr">
-        <is>
-          <t>bit/s</t>
-        </is>
-      </c>
-      <c r="E168" s="13" t="inlineStr">
-        <is>
-          <t>Ch.5.2.1 Table 5-4. Expected to increase when enhancement is activated (low-freq were normal cells).</t>
-        </is>
-      </c>
-      <c r="F168" s="14" t="n"/>
-      <c r="G168" s="14" t="n"/>
-      <c r="H168" s="14" t="n"/>
-      <c r="I168" s="14" t="n"/>
-      <c r="J168" s="15" t="n"/>
-    </row>
-    <row r="169" ht="48" customHeight="1">
-      <c r="A169" s="16" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B169" s="16" t="inlineStr">
-        <is>
-          <t>Perceived data rate of CA UEs (enhancement impact)</t>
-        </is>
-      </c>
-      <c r="C169" s="16" t="inlineStr">
-        <is>
-          <t>(L.Thrp.bits.DL.CAUser − L.Thrp.bits.DL.LastTTI.CAUser) / L.Thrp.Time.DL.RmvLastTTI.CAUser</t>
-        </is>
-      </c>
-      <c r="D169" s="16" t="inlineStr">
-        <is>
-          <t>bit/s</t>
-        </is>
-      </c>
-      <c r="E169" s="16" t="inlineStr">
-        <is>
-          <t>Ch.5.2.2: overall average perceived CA UE rate decreases after enhancement.</t>
-        </is>
-      </c>
-      <c r="F169" s="14" t="n"/>
-      <c r="G169" s="14" t="n"/>
-      <c r="H169" s="14" t="n"/>
-      <c r="I169" s="14" t="n"/>
-      <c r="J169" s="15" t="n"/>
-    </row>
-    <row r="170" ht="48" customHeight="1">
-      <c r="A170" s="13" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B170" s="13" t="inlineStr">
-        <is>
-          <t>Perceived data rate of WBB UEs</t>
-        </is>
-      </c>
-      <c r="C170" s="13" t="inlineStr">
-        <is>
-          <t>(L.Thrp.bits.DL.WBB − L.Thrp.bits.DL.LastTTI.WBB) / L.Thrp.Time.DL.RmvLastTTI.WBB</t>
-        </is>
-      </c>
-      <c r="D170" s="13" t="inlineStr">
-        <is>
-          <t>bit/s</t>
-        </is>
-      </c>
-      <c r="E170" s="13" t="inlineStr">
-        <is>
-          <t>Ch.5.2.2 Table 5-6: decreases. CA takes effect for a smaller proportion of WBB UEs.</t>
-        </is>
-      </c>
-      <c r="F170" s="14" t="n"/>
-      <c r="G170" s="14" t="n"/>
-      <c r="H170" s="14" t="n"/>
-      <c r="I170" s="14" t="n"/>
-      <c r="J170" s="15" t="n"/>
-    </row>
-    <row r="171" ht="48" customHeight="1">
-      <c r="A171" s="16" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="B171" s="16" t="inlineStr">
-        <is>
-          <t>Perceived data rate of RRNs</t>
-        </is>
-      </c>
-      <c r="C171" s="16" t="inlineStr">
-        <is>
-          <t>L.Thrp.Relay.bits.DL / L.Thrp.Relay.Time.DL</t>
-        </is>
-      </c>
-      <c r="D171" s="16" t="inlineStr">
-        <is>
-          <t>bit/s</t>
-        </is>
-      </c>
-      <c r="E171" s="16" t="inlineStr">
-        <is>
-          <t>Ch.5.2.2 Table 5-7: decreases.</t>
-        </is>
-      </c>
-      <c r="F171" s="14" t="n"/>
-      <c r="G171" s="14" t="n"/>
-      <c r="H171" s="14" t="n"/>
-      <c r="I171" s="14" t="n"/>
-      <c r="J171" s="15" t="n"/>
-    </row>
-    <row r="172" ht="20" customHeight="1">
-      <c r="A172" s="17" t="inlineStr">
-        <is>
-          <t>H worked example  —  CA UE average DL throughput  (Ch.4.2.1 formula + sample counts)</t>
-        </is>
-      </c>
-      <c r="B172" s="6" t="n"/>
-      <c r="C172" s="6" t="n"/>
-      <c r="D172" s="6" t="n"/>
-      <c r="E172" s="6" t="n"/>
-      <c r="F172" s="6" t="n"/>
-      <c r="G172" s="6" t="n"/>
-      <c r="H172" s="6" t="n"/>
-      <c r="I172" s="6" t="n"/>
-      <c r="J172" s="6" t="n"/>
-    </row>
-    <row r="173" ht="42" customHeight="1">
-      <c r="A173" s="18" t="inlineStr">
-        <is>
-          <t>3GPP / Huawei condition:
-R = (L.Thrp.bits.DL.CAUser − L.Thrp.bits.DL.LastTTI.CAUser) / L.Thrp.Time.DL.RmvLastTTI.CAUser</t>
-        </is>
-      </c>
-      <c r="B173" s="19" t="n"/>
-      <c r="C173" s="19" t="n"/>
-      <c r="D173" s="19" t="n"/>
-      <c r="E173" s="19" t="n"/>
-      <c r="F173" s="19" t="n"/>
-      <c r="G173" s="19" t="n"/>
-      <c r="H173" s="19" t="n"/>
-      <c r="I173" s="19" t="n"/>
-      <c r="J173" s="19" t="n"/>
-    </row>
-    <row r="174" ht="90" customHeight="1">
-      <c r="A174" s="20" t="inlineStr">
-        <is>
-          <t>Worked example (sample values from the document or typical live-network settings):
-Suppose a 15-minute bin on the high/low pair after SC:
-  L.Thrp.bits.DL.CAUser = 7.20×10^12 bit
-  L.Thrp.bits.DL.LastTTI.CAUser = 0.45×10^12 bit
-  L.Thrp.Time.DL.RmvLastTTI.CAUser = 1.50×10^8 ms
-  R = (7.20 − 0.45)×10^12 / 1.50×10^8 = 6.75×10^12 / 1.50×10^8 = 4.50×10^4 bit/ms = 45.0 Mbit/s.
-Result: Compare the same formula on cell-edge bins (PUSCH MCS 0–3 share, Ch.4.2.1 Scenario 1) before vs after SC. If CA UE proportion also rose, Ch.4.2.1 warns this average can fall even when network User DL Average Throughput rose.</t>
-        </is>
-      </c>
-      <c r="B174" s="21" t="n"/>
-      <c r="C174" s="21" t="n"/>
-      <c r="D174" s="21" t="n"/>
-      <c r="E174" s="21" t="n"/>
-      <c r="F174" s="21" t="n"/>
-      <c r="G174" s="21" t="n"/>
-      <c r="H174" s="21" t="n"/>
-      <c r="I174" s="21" t="n"/>
-      <c r="J174" s="21" t="n"/>
-    </row>
-    <row r="175" ht="22" customHeight="1">
-      <c r="A175" s="5" t="inlineStr">
-        <is>
-          <t>I.  Licenses — FDD and TDD  (Ch.4.3.1 / 5.3.1  —  same license covers enhancement)</t>
-        </is>
-      </c>
-      <c r="B175" s="6" t="n"/>
-      <c r="C175" s="6" t="n"/>
-      <c r="D175" s="6" t="n"/>
-      <c r="E175" s="6" t="n"/>
-      <c r="F175" s="6" t="n"/>
-      <c r="G175" s="6" t="n"/>
-      <c r="H175" s="6" t="n"/>
-      <c r="I175" s="6" t="n"/>
-      <c r="J175" s="6" t="n"/>
-    </row>
-    <row r="176" ht="22" customHeight="1">
-      <c r="A176" s="12" t="inlineStr">
-        <is>
-          <t>SN</t>
-        </is>
-      </c>
-      <c r="B176" s="12" t="inlineStr">
-        <is>
-          <t>RAT</t>
-        </is>
-      </c>
-      <c r="C176" s="12" t="inlineStr">
-        <is>
-          <t>Feature ID</t>
-        </is>
-      </c>
-      <c r="D176" s="12" t="inlineStr">
-        <is>
-          <t>Feature name</t>
-        </is>
-      </c>
-      <c r="E176" s="12" t="inlineStr">
-        <is>
-          <t>Model</t>
-        </is>
-      </c>
-      <c r="F176" s="12" t="inlineStr">
-        <is>
-          <t>Sales unit</t>
-        </is>
-      </c>
-      <c r="G176" s="12" t="inlineStr">
-        <is>
-          <t>When consumed</t>
-        </is>
-      </c>
-      <c r="H176" s="12" t="inlineStr"/>
-      <c r="I176" s="12" t="inlineStr"/>
-      <c r="J176" s="12" t="inlineStr"/>
-    </row>
-    <row r="177" ht="48" customHeight="1">
-      <c r="A177" s="13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B177" s="13" t="inlineStr">
-        <is>
-          <t>FDD</t>
-        </is>
-      </c>
-      <c r="C177" s="13" t="inlineStr">
-        <is>
-          <t>LCOFD-131312</t>
-        </is>
-      </c>
-      <c r="D177" s="13" t="inlineStr">
-        <is>
-          <t>LTE Spectrum Coordination (LTE FDD)</t>
-        </is>
-      </c>
-      <c r="E177" s="13" t="inlineStr">
-        <is>
-          <t>LT1SUNPLTE00</t>
-        </is>
-      </c>
-      <c r="F177" s="13" t="inlineStr">
-        <is>
-          <t>per cell</t>
-        </is>
-      </c>
-      <c r="G177" s="13" t="inlineStr">
-        <is>
-          <t>Ch.4.3.1 and Ch.5.3.1. Enhancement uses the same license. Insufficiency of certain items affects CELL ACTIVATION — see License Control Item Lists.</t>
-        </is>
-      </c>
-      <c r="H177" s="14" t="n"/>
-      <c r="I177" s="14" t="n"/>
-      <c r="J177" s="15" t="n"/>
-    </row>
-    <row r="178" ht="48" customHeight="1">
-      <c r="A178" s="16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B178" s="16" t="inlineStr">
-        <is>
-          <t>TDD</t>
-        </is>
-      </c>
-      <c r="C178" s="16" t="inlineStr">
-        <is>
-          <t>TDLCOFD-131312</t>
-        </is>
-      </c>
-      <c r="D178" s="16" t="inlineStr">
-        <is>
-          <t>LTE Spectrum Coordination (LTE TDD)</t>
-        </is>
-      </c>
-      <c r="E178" s="16" t="inlineStr">
-        <is>
-          <t>LT1SLTESPC00</t>
-        </is>
-      </c>
-      <c r="F178" s="16" t="inlineStr">
-        <is>
-          <t>per cell</t>
-        </is>
-      </c>
-      <c r="G178" s="16" t="inlineStr">
-        <is>
-          <t>Ch.4.3.1 and Ch.5.3.1. Same note on cell activation. No FDD/TDD feature-difference in switches or principles (§2.4).</t>
-        </is>
-      </c>
-      <c r="H178" s="14" t="n"/>
-      <c r="I178" s="14" t="n"/>
-      <c r="J178" s="15" t="n"/>
-    </row>
-    <row r="179" ht="48" customHeight="1">
-      <c r="A179" s="13" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B179" s="13" t="inlineStr">
-        <is>
-          <t>FDD/TDD</t>
-        </is>
-      </c>
-      <c r="C179" s="13" t="inlineStr">
-        <is>
-          <t>(this workbook Steps 1–4)</t>
-        </is>
-      </c>
-      <c r="D179" s="13" t="inlineStr">
-        <is>
-          <t>Carrier aggregation (prerequisite)</t>
-        </is>
-      </c>
-      <c r="E179" s="13" t="inlineStr">
-        <is>
-          <t>LAOFD / TDLAOFD / LEOFD as deployed</t>
-        </is>
-      </c>
-      <c r="F179" s="13" t="inlineStr">
-        <is>
-          <t>per cell</t>
-        </is>
-      </c>
-      <c r="G179" s="13" t="inlineStr">
-        <is>
-          <t>CA must already be licensed and active. SC does not replace CA licenses.</t>
-        </is>
-      </c>
-      <c r="H179" s="14" t="n"/>
-      <c r="I179" s="14" t="n"/>
-      <c r="J179" s="15" t="n"/>
-    </row>
-    <row r="180" ht="22" customHeight="1">
-      <c r="A180" s="5" t="inlineStr">
-        <is>
-          <t>J.  LTE Spectrum Coordination Enhancement  (Ch.5)  —  WBB UEs and RRNs</t>
-        </is>
-      </c>
-      <c r="B180" s="6" t="n"/>
-      <c r="C180" s="6" t="n"/>
-      <c r="D180" s="6" t="n"/>
-      <c r="E180" s="6" t="n"/>
-      <c r="F180" s="6" t="n"/>
-      <c r="G180" s="6" t="n"/>
-      <c r="H180" s="6" t="n"/>
-      <c r="I180" s="6" t="n"/>
-      <c r="J180" s="6" t="n"/>
-    </row>
-    <row r="181" ht="20" customHeight="1">
-      <c r="A181" s="10" t="inlineStr">
+    <row r="163" ht="20" customHeight="1">
+      <c r="A163" s="10" t="inlineStr">
         <is>
           <t>J1.  WBB UEs  (Ch.5.1.1)  —  trigger is downlink RSRP, not UL SINR</t>
         </is>
       </c>
-      <c r="B181" s="11" t="n"/>
-      <c r="C181" s="11" t="n"/>
-      <c r="D181" s="11" t="n"/>
-      <c r="E181" s="11" t="n"/>
-      <c r="F181" s="11" t="n"/>
-      <c r="G181" s="11" t="n"/>
-      <c r="H181" s="11" t="n"/>
-      <c r="I181" s="11" t="n"/>
-      <c r="J181" s="11" t="n"/>
-    </row>
-    <row r="182" ht="130" customHeight="1">
-      <c r="A182" s="7" t="inlineStr">
+      <c r="B163" s="11" t="n"/>
+      <c r="C163" s="11" t="n"/>
+      <c r="D163" s="11" t="n"/>
+      <c r="E163" s="11" t="n"/>
+      <c r="F163" s="11" t="n"/>
+      <c r="G163" s="11" t="n"/>
+      <c r="H163" s="11" t="n"/>
+      <c r="I163" s="11" t="n"/>
+      <c r="J163" s="11" t="n"/>
+    </row>
+    <row r="164" ht="130" customHeight="1">
+      <c r="A164" s="7" t="inlineStr">
         <is>
           <t>In addition to Ch.4, enhancement applies to CA-capable WBB UEs. When the UE is at the coverage edge of its high-frequency serving cell and has low downlink RSRP there, the eNodeB evaluates whether a low-frequency cell can provide better performance; if yes, HO PCell to that low-frequency cell and configure the original PCell as SCell.
 WBB UEs are identified by SPID or by QCI (see WBB FPD).
@@ -5588,34 +4977,34 @@
 After HO to an MBB service cell: original PCell becomes SCell; WBB-dedicated cells can be SCells; MBB service cells cannot be SCells; eNodeB will not remove SCells based on A2; DL data is scheduled only in SCells whenever possible (if all SCell config fails, UE may use the MBB PCell).</t>
         </is>
       </c>
-      <c r="B182" s="8" t="n"/>
-      <c r="C182" s="8" t="n"/>
-      <c r="D182" s="8" t="n"/>
-      <c r="E182" s="8" t="n"/>
-      <c r="F182" s="8" t="n"/>
-      <c r="G182" s="8" t="n"/>
-      <c r="H182" s="8" t="n"/>
-      <c r="I182" s="8" t="n"/>
-      <c r="J182" s="8" t="n"/>
-    </row>
-    <row r="183" ht="20" customHeight="1">
-      <c r="A183" s="17" t="inlineStr">
+      <c r="B164" s="8" t="n"/>
+      <c r="C164" s="8" t="n"/>
+      <c r="D164" s="8" t="n"/>
+      <c r="E164" s="8" t="n"/>
+      <c r="F164" s="8" t="n"/>
+      <c r="G164" s="8" t="n"/>
+      <c r="H164" s="8" t="n"/>
+      <c r="I164" s="8" t="n"/>
+      <c r="J164" s="8" t="n"/>
+    </row>
+    <row r="165" ht="20" customHeight="1">
+      <c r="A165" s="17" t="inlineStr">
         <is>
           <t>J2.  WBB A2 threshold  (Table 5-1)  +  A5 Thresh1/Thresh2  (Tables 5-2 / 5-3)</t>
         </is>
       </c>
-      <c r="B183" s="6" t="n"/>
-      <c r="C183" s="6" t="n"/>
-      <c r="D183" s="6" t="n"/>
-      <c r="E183" s="6" t="n"/>
-      <c r="F183" s="6" t="n"/>
-      <c r="G183" s="6" t="n"/>
-      <c r="H183" s="6" t="n"/>
-      <c r="I183" s="6" t="n"/>
-      <c r="J183" s="6" t="n"/>
-    </row>
-    <row r="184" ht="90" customHeight="1">
-      <c r="A184" s="18" t="inlineStr">
+      <c r="B165" s="6" t="n"/>
+      <c r="C165" s="6" t="n"/>
+      <c r="D165" s="6" t="n"/>
+      <c r="E165" s="6" t="n"/>
+      <c r="F165" s="6" t="n"/>
+      <c r="G165" s="6" t="n"/>
+      <c r="H165" s="6" t="n"/>
+      <c r="I165" s="6" t="n"/>
+      <c r="J165" s="6" t="n"/>
+    </row>
+    <row r="166" ht="90" customHeight="1">
+      <c r="A166" s="18" t="inlineStr">
         <is>
           <t>3GPP / Huawei condition:
 A2 (SPID WBB) = InterFreqHoA2ThdRsrp + SpidCfg.InterFreqHoA2RsrpThdFactor + WbbMultiCarrierCoordA2Ofs
@@ -5626,18 +5015,18 @@
     Max{ PccFreqCfg.PccA4RsrpThd ,  InterFreqHoA2ThdRsrp + WbbMultiCarrierCoordA2Ofs + 2 }</t>
         </is>
       </c>
-      <c r="B184" s="19" t="n"/>
-      <c r="C184" s="19" t="n"/>
-      <c r="D184" s="19" t="n"/>
-      <c r="E184" s="19" t="n"/>
-      <c r="F184" s="19" t="n"/>
-      <c r="G184" s="19" t="n"/>
-      <c r="H184" s="19" t="n"/>
-      <c r="I184" s="19" t="n"/>
-      <c r="J184" s="19" t="n"/>
-    </row>
-    <row r="185" ht="90" customHeight="1">
-      <c r="A185" s="20" t="inlineStr">
+      <c r="B166" s="19" t="n"/>
+      <c r="C166" s="19" t="n"/>
+      <c r="D166" s="19" t="n"/>
+      <c r="E166" s="19" t="n"/>
+      <c r="F166" s="19" t="n"/>
+      <c r="G166" s="19" t="n"/>
+      <c r="H166" s="19" t="n"/>
+      <c r="I166" s="19" t="n"/>
+      <c r="J166" s="19" t="n"/>
+    </row>
+    <row r="167" ht="90" customHeight="1">
+      <c r="A167" s="20" t="inlineStr">
         <is>
           <t>Worked example (sample values from the document or typical live-network settings):
 Doc MML: WbbMultiCarrierCoordA2Ofs = 2. Assume InterFreqHoA2ThdRsrp = −105 dBm, PccA4RsrpThd = −105 dBm, QCI-identified WBB UE, adaptive, RSRP.
@@ -5646,68 +5035,68 @@
 Result: PCell RSRP must stay below A2 (−103) throughout TTT; neighbor must exceed A5 Thresh2 (−101) with Thresh1 always true at realistic RSRP. If the A5 target is an MBB service cell that cannot aggregate with any current serving cell, eNodeB does not HO.</t>
         </is>
       </c>
-      <c r="B185" s="21" t="n"/>
-      <c r="C185" s="21" t="n"/>
-      <c r="D185" s="21" t="n"/>
-      <c r="E185" s="21" t="n"/>
-      <c r="F185" s="21" t="n"/>
-      <c r="G185" s="21" t="n"/>
-      <c r="H185" s="21" t="n"/>
-      <c r="I185" s="21" t="n"/>
-      <c r="J185" s="21" t="n"/>
-    </row>
-    <row r="186" ht="20" customHeight="1">
-      <c r="A186" s="10" t="inlineStr">
+      <c r="B167" s="21" t="n"/>
+      <c r="C167" s="21" t="n"/>
+      <c r="D167" s="21" t="n"/>
+      <c r="E167" s="21" t="n"/>
+      <c r="F167" s="21" t="n"/>
+      <c r="G167" s="21" t="n"/>
+      <c r="H167" s="21" t="n"/>
+      <c r="I167" s="21" t="n"/>
+      <c r="J167" s="21" t="n"/>
+    </row>
+    <row r="168" ht="20" customHeight="1">
+      <c r="A168" s="10" t="inlineStr">
         <is>
           <t>J3.  RRNs  (Ch.5.1.2)</t>
         </is>
       </c>
-      <c r="B186" s="11" t="n"/>
-      <c r="C186" s="11" t="n"/>
-      <c r="D186" s="11" t="n"/>
-      <c r="E186" s="11" t="n"/>
-      <c r="F186" s="11" t="n"/>
-      <c r="G186" s="11" t="n"/>
-      <c r="H186" s="11" t="n"/>
-      <c r="I186" s="11" t="n"/>
-      <c r="J186" s="11" t="n"/>
-    </row>
-    <row r="187" ht="64" customHeight="1">
-      <c r="A187" s="7" t="inlineStr">
+      <c r="B168" s="11" t="n"/>
+      <c r="C168" s="11" t="n"/>
+      <c r="D168" s="11" t="n"/>
+      <c r="E168" s="11" t="n"/>
+      <c r="F168" s="11" t="n"/>
+      <c r="G168" s="11" t="n"/>
+      <c r="H168" s="11" t="n"/>
+      <c r="I168" s="11" t="n"/>
+      <c r="J168" s="11" t="n"/>
+    </row>
+    <row r="169" ht="64" customHeight="1">
+      <c r="A169" s="7" t="inlineStr">
         <is>
           <t>•  Out-of-band relay CA: if RRN PCell is not an MBB service cell, MBB cells cannot be SCells. If PCell is MBB, non-MBB cells can be SCells; DL scheduled only in SCells when possible; if all SCell config fails, RRN may use the MBB cell.
 •  Enabled when MBBSERCELL is set on the low-frequency no-WBB-access cells AND WbbCaMultiCarrierCoordSw is selected.
 •  Verification (Ch.5.4.2): L.Thrp.Relay.Time.DL (1526735543) increases on low-frequency cells.</t>
         </is>
       </c>
-      <c r="B187" s="8" t="n"/>
-      <c r="C187" s="8" t="n"/>
-      <c r="D187" s="8" t="n"/>
-      <c r="E187" s="8" t="n"/>
-      <c r="F187" s="8" t="n"/>
-      <c r="G187" s="8" t="n"/>
-      <c r="H187" s="8" t="n"/>
-      <c r="I187" s="8" t="n"/>
-      <c r="J187" s="8" t="n"/>
-    </row>
-    <row r="188" ht="22" customHeight="1">
-      <c r="A188" s="5" t="inlineStr">
+      <c r="B169" s="8" t="n"/>
+      <c r="C169" s="8" t="n"/>
+      <c r="D169" s="8" t="n"/>
+      <c r="E169" s="8" t="n"/>
+      <c r="F169" s="8" t="n"/>
+      <c r="G169" s="8" t="n"/>
+      <c r="H169" s="8" t="n"/>
+      <c r="I169" s="8" t="n"/>
+      <c r="J169" s="8" t="n"/>
+    </row>
+    <row r="170" ht="22" customHeight="1">
+      <c r="A170" s="5" t="inlineStr">
         <is>
           <t>K.  Hardware, UE, MAE, verification  (Ch.4.3.3–4.4.3, 5.3.3–5.4.3)</t>
         </is>
       </c>
-      <c r="B188" s="6" t="n"/>
-      <c r="C188" s="6" t="n"/>
-      <c r="D188" s="6" t="n"/>
-      <c r="E188" s="6" t="n"/>
-      <c r="F188" s="6" t="n"/>
-      <c r="G188" s="6" t="n"/>
-      <c r="H188" s="6" t="n"/>
-      <c r="I188" s="6" t="n"/>
-      <c r="J188" s="6" t="n"/>
-    </row>
-    <row r="189" ht="110" customHeight="1">
-      <c r="A189" s="7" t="inlineStr">
+      <c r="B170" s="6" t="n"/>
+      <c r="C170" s="6" t="n"/>
+      <c r="D170" s="6" t="n"/>
+      <c r="E170" s="6" t="n"/>
+      <c r="F170" s="6" t="n"/>
+      <c r="G170" s="6" t="n"/>
+      <c r="H170" s="6" t="n"/>
+      <c r="I170" s="6" t="n"/>
+      <c r="J170" s="6" t="n"/>
+    </row>
+    <row r="171" ht="110" customHeight="1">
+      <c r="A171" s="7" t="inlineStr">
         <is>
           <t>•  SC (Ch.4): FDD 3900/5900 macro; TDD 3900/5900 macro + DBS3900/DBS5900 LampSite. LBBPc boards cannot be used. RF: no requirements.
 •  Enhancement (Ch.5): 3900/5900 macro + LampSite. TDD: cells on LBBPc cannot be used. FDD boards: no requirements. RF: no requirements.
@@ -5717,185 +5106,473 @@
 •  Huawei note (Ch.2.1): this FPD is activation guidance. Gains depend on the live scenario; contact Huawei professional service for optimal gains.</t>
         </is>
       </c>
-      <c r="B189" s="8" t="n"/>
-      <c r="C189" s="8" t="n"/>
-      <c r="D189" s="8" t="n"/>
-      <c r="E189" s="8" t="n"/>
-      <c r="F189" s="8" t="n"/>
-      <c r="G189" s="8" t="n"/>
-      <c r="H189" s="8" t="n"/>
-      <c r="I189" s="8" t="n"/>
-      <c r="J189" s="8" t="n"/>
+      <c r="B171" s="8" t="n"/>
+      <c r="C171" s="8" t="n"/>
+      <c r="D171" s="8" t="n"/>
+      <c r="E171" s="8" t="n"/>
+      <c r="F171" s="8" t="n"/>
+      <c r="G171" s="8" t="n"/>
+      <c r="H171" s="8" t="n"/>
+      <c r="I171" s="8" t="n"/>
+      <c r="J171" s="8" t="n"/>
+    </row>
+    <row r="172" ht="22" customHeight="1">
+      <c r="A172" s="35" t="inlineStr">
+        <is>
+          <t>L.  Final summary  —  meeting quick notes  (1-minute brief)</t>
+        </is>
+      </c>
+      <c r="B172" s="36" t="n"/>
+      <c r="C172" s="36" t="n"/>
+      <c r="D172" s="36" t="n"/>
+      <c r="E172" s="36" t="n"/>
+      <c r="F172" s="36" t="n"/>
+      <c r="G172" s="36" t="n"/>
+      <c r="H172" s="36" t="n"/>
+      <c r="I172" s="36" t="n"/>
+      <c r="J172" s="36" t="n"/>
+    </row>
+    <row r="173" ht="28" customHeight="1">
+      <c r="A173" s="3" t="inlineStr">
+        <is>
+          <t>Use this block in a meeting. All points are from the LTE Spectrum Coordination FPD (eRAN21.1 Issue 01).</t>
+        </is>
+      </c>
+      <c r="B173" s="4" t="n"/>
+      <c r="C173" s="4" t="n"/>
+      <c r="D173" s="4" t="n"/>
+      <c r="E173" s="4" t="n"/>
+      <c r="F173" s="4" t="n"/>
+      <c r="G173" s="4" t="n"/>
+      <c r="H173" s="4" t="n"/>
+      <c r="I173" s="4" t="n"/>
+      <c r="J173" s="4" t="n"/>
+    </row>
+    <row r="174" ht="22" customHeight="1">
+      <c r="A174" s="12" t="inlineStr">
+        <is>
+          <t>Topic</t>
+        </is>
+      </c>
+      <c r="B174" s="12" t="inlineStr">
+        <is>
+          <t>What to say</t>
+        </is>
+      </c>
+      <c r="C174" s="12" t="inlineStr"/>
+      <c r="D174" s="12" t="inlineStr"/>
+      <c r="E174" s="12" t="inlineStr"/>
+      <c r="F174" s="12" t="inlineStr"/>
+      <c r="G174" s="12" t="inlineStr"/>
+      <c r="H174" s="12" t="inlineStr"/>
+      <c r="I174" s="12" t="inlineStr"/>
+      <c r="J174" s="12" t="inlineStr"/>
+    </row>
+    <row r="175" ht="40" customHeight="1">
+      <c r="A175" s="32" t="inlineStr">
+        <is>
+          <t>What it is (10 s)</t>
+        </is>
+      </c>
+      <c r="B175" s="22" t="inlineStr">
+        <is>
+          <t>LTE Spectrum Coordination is a CA companion: when a CA UE sits at the high-band UL edge, the eNodeB HOs the PCell to a better low-band SCell and keeps the old PCell as SCell, so DL still uses both bands while UL rides the coverage layer. Feature IDs: LCOFD-131312 (FDD) / TDLCOFD-131312 (TDD). Same for FDD and TDD.</t>
+        </is>
+      </c>
+      <c r="C175" s="14" t="n"/>
+      <c r="D175" s="14" t="n"/>
+      <c r="E175" s="14" t="n"/>
+      <c r="F175" s="14" t="n"/>
+      <c r="G175" s="14" t="n"/>
+      <c r="H175" s="14" t="n"/>
+      <c r="I175" s="14" t="n"/>
+      <c r="J175" s="15" t="n"/>
+    </row>
+    <row r="176" ht="41" customHeight="1">
+      <c r="A176" s="32" t="inlineStr">
+        <is>
+          <t>Benefit (1–2 lines)</t>
+        </is>
+      </c>
+      <c r="B176" s="13" t="inlineStr">
+        <is>
+          <t>It lifts DL usage of CA UEs at the high-frequency UL coverage edge. Best when high/low gap is large. Scenario 1 (both bands already on): PUSCH MCS 0–3 &gt;10% on high band, low-minus-high UL interference &lt;5 dB, CA UE penetration &gt;25% → network User DL Average Throughput up. Scenario 2 (adding a new low band under an existing high band) → both User DL and User UL Average Throughput up.</t>
+        </is>
+      </c>
+      <c r="C176" s="14" t="n"/>
+      <c r="D176" s="14" t="n"/>
+      <c r="E176" s="14" t="n"/>
+      <c r="F176" s="14" t="n"/>
+      <c r="G176" s="14" t="n"/>
+      <c r="H176" s="14" t="n"/>
+      <c r="I176" s="14" t="n"/>
+      <c r="J176" s="15" t="n"/>
+    </row>
+    <row r="177" ht="40" customHeight="1">
+      <c r="A177" s="32" t="inlineStr">
+        <is>
+          <t>Trigger</t>
+        </is>
+      </c>
+      <c r="B177" s="22" t="inlineStr">
+        <is>
+          <t>CA UE already aggregating. UL SINR used in scheduling (initial MCS) &lt; SpectrumCoordSinrThld (doc MML −2 dB). Then a DL SCell must pass A4 AND be stronger than all its intra-freq neighbours, and must be allowed as PCell. Target pick: PCell/PCC priority → largest BW → lowest EARFCN (or DL air-interface capability first if intelligent selection is ON).</t>
+        </is>
+      </c>
+      <c r="C177" s="14" t="n"/>
+      <c r="D177" s="14" t="n"/>
+      <c r="E177" s="14" t="n"/>
+      <c r="F177" s="14" t="n"/>
+      <c r="G177" s="14" t="n"/>
+      <c r="H177" s="14" t="n"/>
+      <c r="I177" s="14" t="n"/>
+      <c r="J177" s="15" t="n"/>
+    </row>
+    <row r="178" ht="39" customHeight="1">
+      <c r="A178" s="32" t="inlineStr">
+        <is>
+          <t>Leave / after HO</t>
+        </is>
+      </c>
+      <c r="B178" s="13" t="inlineStr">
+        <is>
+          <t>After HO, original SCell = new PCell and original PCell = SCell. In adaptive CA, SCell A2 then manages the old high band (SccA2RsrpThldExtendedOfs; doc −10). Operator off: SpectrumCoordinationSwitch-0. Not a coverage HO; extra HOs raise count, can cut DRX UEs and may drop VoLTE MOS.</t>
+        </is>
+      </c>
+      <c r="C178" s="14" t="n"/>
+      <c r="D178" s="14" t="n"/>
+      <c r="E178" s="14" t="n"/>
+      <c r="F178" s="14" t="n"/>
+      <c r="G178" s="14" t="n"/>
+      <c r="H178" s="14" t="n"/>
+      <c r="I178" s="14" t="n"/>
+      <c r="J178" s="15" t="n"/>
+    </row>
+    <row r="179" ht="37" customHeight="1">
+      <c r="A179" s="32" t="inlineStr">
+        <is>
+          <t>Must-on conditions</t>
+        </is>
+      </c>
+      <c r="B179" s="22" t="inlineStr">
+        <is>
+          <t>HoAdmitSwitch OFF; HoWithSccCfgSwitch ON; SpectrumCoordinationSwitch ON. After enable also ON: CaEnhancedPreAllocSwitch, Dl2CCAckResShareSw, SccA2RmvSwitch. UE must support CA. CA already live (DL 2–8 CC).</t>
+        </is>
+      </c>
+      <c r="C179" s="14" t="n"/>
+      <c r="D179" s="14" t="n"/>
+      <c r="E179" s="14" t="n"/>
+      <c r="F179" s="14" t="n"/>
+      <c r="G179" s="14" t="n"/>
+      <c r="H179" s="14" t="n"/>
+      <c r="I179" s="14" t="n"/>
+      <c r="J179" s="15" t="n"/>
+    </row>
+    <row r="180" ht="37" customHeight="1">
+      <c r="A180" s="32" t="inlineStr">
+        <is>
+          <t>Applicable case</t>
+        </is>
+      </c>
+      <c r="B180" s="13" t="inlineStr">
+        <is>
+          <t>Multi-band CA cluster with overlapping high + low (FPD example 2600 + 850 MHz). Intra-eNodeB. Macro 3900/5900; TDD also LampSite. Not LBBPc.</t>
+        </is>
+      </c>
+      <c r="C180" s="14" t="n"/>
+      <c r="D180" s="14" t="n"/>
+      <c r="E180" s="14" t="n"/>
+      <c r="F180" s="14" t="n"/>
+      <c r="G180" s="14" t="n"/>
+      <c r="H180" s="14" t="n"/>
+      <c r="I180" s="14" t="n"/>
+      <c r="J180" s="15" t="n"/>
+    </row>
+    <row r="181" ht="40" customHeight="1">
+      <c r="A181" s="32" t="inlineStr">
+        <is>
+          <t>UL / DL CA limitation</t>
+        </is>
+      </c>
+      <c r="B181" s="22" t="inlineStr">
+        <is>
+          <t>Compatible with DL 2CC–8CC. Does NOT take effect if the UE has 2 CC in UL and 2 CC in DL (UL SCells are never SC targets). If UL is 2 CC and DL is 3–8 CC, it does take effect. This is not UL CA; it only moves which cell is PCell so UL uses the low band.</t>
+        </is>
+      </c>
+      <c r="C181" s="14" t="n"/>
+      <c r="D181" s="14" t="n"/>
+      <c r="E181" s="14" t="n"/>
+      <c r="F181" s="14" t="n"/>
+      <c r="G181" s="14" t="n"/>
+      <c r="H181" s="14" t="n"/>
+      <c r="I181" s="14" t="n"/>
+      <c r="J181" s="15" t="n"/>
+    </row>
+    <row r="182" ht="39" customHeight="1">
+      <c r="A182" s="32" t="inlineStr">
+        <is>
+          <t>GPS required?</t>
+        </is>
+      </c>
+      <c r="B182" s="13" t="inlineStr">
+        <is>
+          <t>No extra GPS requirement in this FPD. SC is an intra-eNodeB PCell change + CA SCell keep. Site sync stays whatever LTE already needs (TDD still needs the site’s existing GPS/1588/sync; SC does not add a GPS license or a new sync feature).</t>
+        </is>
+      </c>
+      <c r="C182" s="14" t="n"/>
+      <c r="D182" s="14" t="n"/>
+      <c r="E182" s="14" t="n"/>
+      <c r="F182" s="14" t="n"/>
+      <c r="G182" s="14" t="n"/>
+      <c r="H182" s="14" t="n"/>
+      <c r="I182" s="14" t="n"/>
+      <c r="J182" s="15" t="n"/>
+    </row>
+    <row r="183" ht="38" customHeight="1">
+      <c r="A183" s="32" t="inlineStr">
+        <is>
+          <t>License (if asked)</t>
+        </is>
+      </c>
+      <c r="B183" s="22" t="inlineStr">
+        <is>
+          <t>FDD LCOFD-131312 model LT1SUNPLTE00 per cell; TDD TDLCOFD-131312 model LT1SLTESPC00 per cell. Enhancement uses the same license. CA licenses still required. License shortage can block ACT CELL.</t>
+        </is>
+      </c>
+      <c r="C183" s="14" t="n"/>
+      <c r="D183" s="14" t="n"/>
+      <c r="E183" s="14" t="n"/>
+      <c r="F183" s="14" t="n"/>
+      <c r="G183" s="14" t="n"/>
+      <c r="H183" s="14" t="n"/>
+      <c r="I183" s="14" t="n"/>
+      <c r="J183" s="15" t="n"/>
+    </row>
+    <row r="184" ht="38" customHeight="1">
+      <c r="A184" s="32" t="inlineStr">
+        <is>
+          <t>How we know it is working</t>
+        </is>
+      </c>
+      <c r="B184" s="13" t="inlineStr">
+        <is>
+          <t>L.HHO.InterFreq.ULquality.Prep/Exec/Succ (1526729994 / 9996 / 9998) increase. Also watch CA PCell/SCell users and bits, CA UE DL rate, SCell add success (tied to HO success).</t>
+        </is>
+      </c>
+      <c r="C184" s="14" t="n"/>
+      <c r="D184" s="14" t="n"/>
+      <c r="E184" s="14" t="n"/>
+      <c r="F184" s="14" t="n"/>
+      <c r="G184" s="14" t="n"/>
+      <c r="H184" s="14" t="n"/>
+      <c r="I184" s="14" t="n"/>
+      <c r="J184" s="15" t="n"/>
+    </row>
+    <row r="185" ht="41" customHeight="1">
+      <c r="A185" s="32" t="inlineStr">
+        <is>
+          <t>Do not mix / watch-outs</t>
+        </is>
+      </c>
+      <c r="B185" s="22" t="inlineStr">
+        <is>
+          <t>Not DSS, not GSM/UMTS spectrum sharing, not NR UL/DL decoupling. DSS / SUL DSS cut LTE UL RBs → fewer UEs get SC. NSA: may HO PCC off an NSA anchor — deselect SPCT_COORD_INTER_FREQ_HO_SW to exempt NSA UEs. Enhancement (WBB/RRN) is a different bit (WbbCaMultiCarrierCoordSw); NSA PCC anchoring wins over it. SCC coverage-threshold adaptation kills SC carrier management. More HOs; CQI/KPI move with the new PCell quality.</t>
+        </is>
+      </c>
+      <c r="C185" s="14" t="n"/>
+      <c r="D185" s="14" t="n"/>
+      <c r="E185" s="14" t="n"/>
+      <c r="F185" s="14" t="n"/>
+      <c r="G185" s="14" t="n"/>
+      <c r="H185" s="14" t="n"/>
+      <c r="I185" s="14" t="n"/>
+      <c r="J185" s="15" t="n"/>
+    </row>
+    <row r="186" ht="38" customHeight="1">
+      <c r="A186" s="32" t="inlineStr">
+        <is>
+          <t>One-line close</t>
+        </is>
+      </c>
+      <c r="B186" s="13" t="inlineStr">
+        <is>
+          <t>Turn it on only after CA is green on a high/low pair; it does not create CA, it only swaps PCell on poor UL SINR so cell-edge CA UEs keep high-band DL.</t>
+        </is>
+      </c>
+      <c r="C186" s="14" t="n"/>
+      <c r="D186" s="14" t="n"/>
+      <c r="E186" s="14" t="n"/>
+      <c r="F186" s="14" t="n"/>
+      <c r="G186" s="14" t="n"/>
+      <c r="H186" s="14" t="n"/>
+      <c r="I186" s="14" t="n"/>
+      <c r="J186" s="15" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="167">
+  <mergeCells count="163">
     <mergeCell ref="E138:J138"/>
     <mergeCell ref="E143:J143"/>
-    <mergeCell ref="A181:J181"/>
-    <mergeCell ref="A184:J184"/>
     <mergeCell ref="G109:J109"/>
-    <mergeCell ref="E167:J167"/>
+    <mergeCell ref="A156:J156"/>
+    <mergeCell ref="A171:J171"/>
     <mergeCell ref="E149:J149"/>
     <mergeCell ref="A52:J52"/>
-    <mergeCell ref="G119:J119"/>
+    <mergeCell ref="A165:J165"/>
+    <mergeCell ref="B182:J182"/>
     <mergeCell ref="A63:J63"/>
+    <mergeCell ref="G159:J159"/>
+    <mergeCell ref="A155:J155"/>
+    <mergeCell ref="E133:J133"/>
     <mergeCell ref="G111:J111"/>
+    <mergeCell ref="B178:J178"/>
     <mergeCell ref="G72:J72"/>
-    <mergeCell ref="E169:J169"/>
     <mergeCell ref="A173:J173"/>
     <mergeCell ref="G81:J81"/>
     <mergeCell ref="G96:J96"/>
     <mergeCell ref="A34:J34"/>
+    <mergeCell ref="G161:J161"/>
+    <mergeCell ref="A157:J157"/>
     <mergeCell ref="G71:J71"/>
+    <mergeCell ref="B183:J183"/>
     <mergeCell ref="A49:J49"/>
+    <mergeCell ref="B177:J177"/>
     <mergeCell ref="A36:J36"/>
-    <mergeCell ref="E159:J159"/>
+    <mergeCell ref="E125:J125"/>
     <mergeCell ref="C46:J46"/>
-    <mergeCell ref="E164:J164"/>
-    <mergeCell ref="A174:J174"/>
-    <mergeCell ref="E145:J145"/>
+    <mergeCell ref="G160:J160"/>
     <mergeCell ref="E139:J139"/>
-    <mergeCell ref="A183:J183"/>
-    <mergeCell ref="G128:J128"/>
     <mergeCell ref="G66:J66"/>
+    <mergeCell ref="E129:J129"/>
     <mergeCell ref="E142:J142"/>
     <mergeCell ref="E24:J24"/>
-    <mergeCell ref="G121:J121"/>
     <mergeCell ref="A3:J3"/>
     <mergeCell ref="G74:J74"/>
     <mergeCell ref="A55:J55"/>
     <mergeCell ref="G68:J68"/>
+    <mergeCell ref="B180:J180"/>
     <mergeCell ref="G108:J108"/>
+    <mergeCell ref="E131:J131"/>
     <mergeCell ref="E140:J140"/>
-    <mergeCell ref="E171:J171"/>
     <mergeCell ref="G114:J114"/>
     <mergeCell ref="E153:J153"/>
-    <mergeCell ref="A175:J175"/>
-    <mergeCell ref="G123:J123"/>
     <mergeCell ref="A5:J5"/>
     <mergeCell ref="A32:J32"/>
     <mergeCell ref="G110:J110"/>
-    <mergeCell ref="E155:J155"/>
     <mergeCell ref="E137:J137"/>
     <mergeCell ref="G113:J113"/>
     <mergeCell ref="G91:J91"/>
+    <mergeCell ref="B179:J179"/>
     <mergeCell ref="A29:J29"/>
     <mergeCell ref="A4:J4"/>
     <mergeCell ref="G85:J85"/>
     <mergeCell ref="A38:J38"/>
     <mergeCell ref="G94:J94"/>
-    <mergeCell ref="E157:J157"/>
-    <mergeCell ref="E166:J166"/>
+    <mergeCell ref="A170:J170"/>
     <mergeCell ref="G75:J75"/>
     <mergeCell ref="G84:J84"/>
     <mergeCell ref="A31:J31"/>
     <mergeCell ref="A58:J58"/>
+    <mergeCell ref="B186:J186"/>
     <mergeCell ref="A40:J40"/>
     <mergeCell ref="G77:J77"/>
-    <mergeCell ref="A186:J186"/>
-    <mergeCell ref="E168:J168"/>
     <mergeCell ref="G86:J86"/>
     <mergeCell ref="A82:J82"/>
-    <mergeCell ref="G178:J178"/>
     <mergeCell ref="A60:J60"/>
     <mergeCell ref="G67:J67"/>
     <mergeCell ref="E136:J136"/>
     <mergeCell ref="G70:J70"/>
     <mergeCell ref="G97:J97"/>
-    <mergeCell ref="G125:J125"/>
     <mergeCell ref="A172:J172"/>
-    <mergeCell ref="A187:J187"/>
     <mergeCell ref="G112:J112"/>
-    <mergeCell ref="G127:J127"/>
-    <mergeCell ref="A189:J189"/>
+    <mergeCell ref="E122:J122"/>
+    <mergeCell ref="B185:J185"/>
+    <mergeCell ref="E127:J127"/>
     <mergeCell ref="E23:J23"/>
     <mergeCell ref="A50:J50"/>
-    <mergeCell ref="G177:J177"/>
+    <mergeCell ref="B184:J184"/>
     <mergeCell ref="A2:J2"/>
+    <mergeCell ref="B176:J176"/>
     <mergeCell ref="G104:J104"/>
     <mergeCell ref="A42:J42"/>
     <mergeCell ref="E147:J147"/>
     <mergeCell ref="A47:J47"/>
-    <mergeCell ref="E156:J156"/>
-    <mergeCell ref="E170:J170"/>
     <mergeCell ref="G88:J88"/>
+    <mergeCell ref="E128:J128"/>
     <mergeCell ref="A62:J62"/>
-    <mergeCell ref="G129:J129"/>
+    <mergeCell ref="A144:J144"/>
     <mergeCell ref="A20:J20"/>
     <mergeCell ref="G76:J76"/>
     <mergeCell ref="G90:J90"/>
-    <mergeCell ref="A134:J134"/>
     <mergeCell ref="A28:J28"/>
     <mergeCell ref="G99:J99"/>
     <mergeCell ref="E148:J148"/>
-    <mergeCell ref="G131:J131"/>
+    <mergeCell ref="A167:J167"/>
     <mergeCell ref="A30:J30"/>
-    <mergeCell ref="E154:J154"/>
     <mergeCell ref="A59:J59"/>
     <mergeCell ref="G115:J115"/>
-    <mergeCell ref="G130:J130"/>
-    <mergeCell ref="A182:J182"/>
+    <mergeCell ref="E119:J119"/>
     <mergeCell ref="A64:J64"/>
-    <mergeCell ref="G117:J117"/>
+    <mergeCell ref="A169:J169"/>
     <mergeCell ref="A51:J51"/>
     <mergeCell ref="E25:J25"/>
-    <mergeCell ref="G179:J179"/>
     <mergeCell ref="A61:J61"/>
-    <mergeCell ref="G126:J126"/>
-    <mergeCell ref="G132:J132"/>
-    <mergeCell ref="G122:J122"/>
     <mergeCell ref="A162:J162"/>
     <mergeCell ref="E146:J146"/>
-    <mergeCell ref="G116:J116"/>
     <mergeCell ref="A54:J54"/>
+    <mergeCell ref="E121:J121"/>
     <mergeCell ref="G103:J103"/>
     <mergeCell ref="A41:J41"/>
+    <mergeCell ref="E130:J130"/>
     <mergeCell ref="E151:J151"/>
-    <mergeCell ref="E160:J160"/>
+    <mergeCell ref="A164:J164"/>
     <mergeCell ref="G78:J78"/>
-    <mergeCell ref="G118:J118"/>
     <mergeCell ref="A56:J56"/>
     <mergeCell ref="A27:J27"/>
     <mergeCell ref="G87:J87"/>
+    <mergeCell ref="E123:J123"/>
     <mergeCell ref="E150:J150"/>
+    <mergeCell ref="A154:J154"/>
+    <mergeCell ref="E132:J132"/>
+    <mergeCell ref="A163:J163"/>
     <mergeCell ref="A101:J101"/>
     <mergeCell ref="G80:J80"/>
     <mergeCell ref="G95:J95"/>
     <mergeCell ref="A33:J33"/>
     <mergeCell ref="G89:J89"/>
+    <mergeCell ref="A116:J116"/>
     <mergeCell ref="E152:J152"/>
-    <mergeCell ref="E161:J161"/>
     <mergeCell ref="G79:J79"/>
-    <mergeCell ref="A188:J188"/>
     <mergeCell ref="G73:J73"/>
     <mergeCell ref="A100:J100"/>
     <mergeCell ref="A53:J53"/>
+    <mergeCell ref="E118:J118"/>
     <mergeCell ref="A35:J35"/>
-    <mergeCell ref="A180:J180"/>
-    <mergeCell ref="E158:J158"/>
+    <mergeCell ref="B181:J181"/>
+    <mergeCell ref="B175:J175"/>
     <mergeCell ref="C45:J45"/>
     <mergeCell ref="G106:J106"/>
     <mergeCell ref="G105:J105"/>
     <mergeCell ref="A39:J39"/>
+    <mergeCell ref="A166:J166"/>
     <mergeCell ref="C44:J44"/>
     <mergeCell ref="A48:J48"/>
-    <mergeCell ref="E144:J144"/>
-    <mergeCell ref="G120:J120"/>
+    <mergeCell ref="E124:J124"/>
     <mergeCell ref="G98:J98"/>
+    <mergeCell ref="E120:J120"/>
     <mergeCell ref="G107:J107"/>
     <mergeCell ref="A1:J1"/>
+    <mergeCell ref="E134:J134"/>
+    <mergeCell ref="A168:J168"/>
     <mergeCell ref="G93:J93"/>
     <mergeCell ref="A37:J37"/>
     <mergeCell ref="G69:J69"/>
-    <mergeCell ref="E165:J165"/>
     <mergeCell ref="A21:J21"/>
     <mergeCell ref="G92:J92"/>
+    <mergeCell ref="E126:J126"/>
     <mergeCell ref="E141:J141"/>
     <mergeCell ref="A26:J26"/>
     <mergeCell ref="A57:J57"/>
-    <mergeCell ref="G124:J124"/>
-    <mergeCell ref="G133:J133"/>
-    <mergeCell ref="A185:J185"/>
+    <mergeCell ref="E135:J135"/>
   </mergeCells>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.5" header="0.25" footer="0.25"/>
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>

--- a/LTE_Spectrum_Coordination.xlsx
+++ b/LTE_Spectrum_Coordination.xlsx
@@ -5168,7 +5168,7 @@
       <c r="I174" s="12" t="inlineStr"/>
       <c r="J174" s="12" t="inlineStr"/>
     </row>
-    <row r="175" ht="40" customHeight="1">
+    <row r="175" ht="52" customHeight="1">
       <c r="A175" s="32" t="inlineStr">
         <is>
           <t>What it is (10 s)</t>
@@ -5188,7 +5188,7 @@
       <c r="I175" s="14" t="n"/>
       <c r="J175" s="15" t="n"/>
     </row>
-    <row r="176" ht="41" customHeight="1">
+    <row r="176" ht="52" customHeight="1">
       <c r="A176" s="32" t="inlineStr">
         <is>
           <t>Benefit (1–2 lines)</t>
@@ -5208,7 +5208,7 @@
       <c r="I176" s="14" t="n"/>
       <c r="J176" s="15" t="n"/>
     </row>
-    <row r="177" ht="40" customHeight="1">
+    <row r="177" ht="52" customHeight="1">
       <c r="A177" s="32" t="inlineStr">
         <is>
           <t>Trigger</t>
@@ -5228,7 +5228,7 @@
       <c r="I177" s="14" t="n"/>
       <c r="J177" s="15" t="n"/>
     </row>
-    <row r="178" ht="39" customHeight="1">
+    <row r="178" ht="52" customHeight="1">
       <c r="A178" s="32" t="inlineStr">
         <is>
           <t>Leave / after HO</t>
@@ -5248,7 +5248,7 @@
       <c r="I178" s="14" t="n"/>
       <c r="J178" s="15" t="n"/>
     </row>
-    <row r="179" ht="37" customHeight="1">
+    <row r="179" ht="52" customHeight="1">
       <c r="A179" s="32" t="inlineStr">
         <is>
           <t>Must-on conditions</t>
@@ -5268,7 +5268,7 @@
       <c r="I179" s="14" t="n"/>
       <c r="J179" s="15" t="n"/>
     </row>
-    <row r="180" ht="37" customHeight="1">
+    <row r="180" ht="52" customHeight="1">
       <c r="A180" s="32" t="inlineStr">
         <is>
           <t>Applicable case</t>
@@ -5288,7 +5288,7 @@
       <c r="I180" s="14" t="n"/>
       <c r="J180" s="15" t="n"/>
     </row>
-    <row r="181" ht="40" customHeight="1">
+    <row r="181" ht="52" customHeight="1">
       <c r="A181" s="32" t="inlineStr">
         <is>
           <t>UL / DL CA limitation</t>
@@ -5308,7 +5308,7 @@
       <c r="I181" s="14" t="n"/>
       <c r="J181" s="15" t="n"/>
     </row>
-    <row r="182" ht="39" customHeight="1">
+    <row r="182" ht="52" customHeight="1">
       <c r="A182" s="32" t="inlineStr">
         <is>
           <t>GPS required?</t>
@@ -5328,7 +5328,7 @@
       <c r="I182" s="14" t="n"/>
       <c r="J182" s="15" t="n"/>
     </row>
-    <row r="183" ht="38" customHeight="1">
+    <row r="183" ht="52" customHeight="1">
       <c r="A183" s="32" t="inlineStr">
         <is>
           <t>License (if asked)</t>
@@ -5348,7 +5348,7 @@
       <c r="I183" s="14" t="n"/>
       <c r="J183" s="15" t="n"/>
     </row>
-    <row r="184" ht="38" customHeight="1">
+    <row r="184" ht="52" customHeight="1">
       <c r="A184" s="32" t="inlineStr">
         <is>
           <t>How we know it is working</t>
@@ -5368,7 +5368,7 @@
       <c r="I184" s="14" t="n"/>
       <c r="J184" s="15" t="n"/>
     </row>
-    <row r="185" ht="41" customHeight="1">
+    <row r="185" ht="52" customHeight="1">
       <c r="A185" s="32" t="inlineStr">
         <is>
           <t>Do not mix / watch-outs</t>
@@ -5388,15 +5388,19 @@
       <c r="I185" s="14" t="n"/>
       <c r="J185" s="15" t="n"/>
     </row>
-    <row r="186" ht="38" customHeight="1">
+    <row r="186" ht="118" customHeight="1">
       <c r="A186" s="32" t="inlineStr">
         <is>
-          <t>One-line close</t>
+          <t>Plain-English close  (read this if the jargon is heavy)</t>
         </is>
       </c>
       <c r="B186" s="13" t="inlineStr">
         <is>
-          <t>Turn it on only after CA is green on a high/low pair; it does not create CA, it only swaps PCell on poor UL SINR so cell-edge CA UEs keep high-band DL.</t>
+          <t>1) First make normal Carrier Aggregation work between one high-frequency cell and one low-frequency cell (same site, overlapping coverage). If CA is not working, do not turn Spectrum Coordination on.
+2) Spectrum Coordination does not join two carriers by itself. CA already joined them. This feature only changes which of those two cells is the PCell (the cell that carries the uplink).
+3) When the UE is near the cell edge, uplink on the high band is weak (poor UL SINR). The eNodeB then makes the low-band cell the PCell so the UE transmits uplink on the low band (better coverage).
+4) The high-band cell is kept as an SCell, so downlink data can still use both bands. That is the gain: cell-edge users keep high-band download speed even when their upload cannot stay on the high band.
+5) Short version: CA = two pipes for download. Spectrum Coordination = move the upload pipe to the low band at the edge, without throwing away the high-band download pipe.</t>
         </is>
       </c>
       <c r="C186" s="14" t="n"/>

--- a/LTE_Spectrum_Coordination.xlsx
+++ b/LTE_Spectrum_Coordination.xlsx
@@ -707,7 +707,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J186"/>
+  <dimension ref="A1:J189"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -5176,7 +5176,7 @@
       </c>
       <c r="B175" s="22" t="inlineStr">
         <is>
-          <t>LTE Spectrum Coordination is a CA companion: when a CA UE sits at the high-band UL edge, the eNodeB HOs the PCell to a better low-band SCell and keeps the old PCell as SCell, so DL still uses both bands while UL rides the coverage layer. Feature IDs: LCOFD-131312 (FDD) / TDLCOFD-131312 (TDD). Same for FDD and TDD.</t>
+          <t>The UE is already in CA: PCell = high band (upload + download), SCell = low band (download extra). If upload on the high-band PCell becomes too weak, the eNodeB does an inter-frequency handover: the low-band SCell becomes the new PCell, and the old high-band PCell is immediately kept as an SCell. Feature IDs: LCOFD-131312 (FDD) / TDLCOFD-131312 (TDD). Same for FDD and TDD.</t>
         </is>
       </c>
       <c r="C175" s="14" t="n"/>
@@ -5191,12 +5191,12 @@
     <row r="176" ht="52" customHeight="1">
       <c r="A176" s="32" t="inlineStr">
         <is>
-          <t>Benefit (1–2 lines)</t>
+          <t>Q1. Is the low-band SCell already configured with this PCell?</t>
         </is>
       </c>
       <c r="B176" s="13" t="inlineStr">
         <is>
-          <t>It lifts DL usage of CA UEs at the high-frequency UL coverage edge. Best when high/low gap is large. Scenario 1 (both bands already on): PUSCH MCS 0–3 &gt;10% on high band, low-minus-high UL interference &lt;5 dB, CA UE penetration &gt;25% → network User DL Average Throughput up. Scenario 2 (adding a new low band under an existing high band) → both User DL and User UL Average Throughput up.</t>
+          <t>YES. The FPD starts from a UE already in the CA state. The eNodeB only looks at that UE’s existing downlink SCells — it does not add a new neighbor from outside CA at this step. Example in Figure 4-1: before the swap, PCell is already 2600 MHz and SCell is already 850 MHz.</t>
         </is>
       </c>
       <c r="C176" s="14" t="n"/>
@@ -5211,12 +5211,12 @@
     <row r="177" ht="52" customHeight="1">
       <c r="A177" s="32" t="inlineStr">
         <is>
-          <t>Trigger</t>
+          <t>Q2. If the UE has several SCells, which one becomes the new PCell?</t>
         </is>
       </c>
       <c r="B177" s="22" t="inlineStr">
         <is>
-          <t>CA UE already aggregating. UL SINR used in scheduling (initial MCS) &lt; SpectrumCoordSinrThld (doc MML −2 dB). Then a DL SCell must pass A4 AND be stronger than all its intra-freq neighbours, and must be allowed as PCell. Target pick: PCell/PCC priority → largest BW → lowest EARFCN (or DL air-interface capability first if intelligent selection is ON).</t>
+          <t>Only SCells that pass ALL of: (a) better uplink than the current PCell, (b) DL RSRP reaches CA event A4, (c) stronger than all intra-frequency neighbors of that SCell, (d) allowed to be a PCell. If only one SCell passes → HO to that one. If two or more pass → pick by rule: highest PCell/PCC priority, then largest bandwidth, then lowest EARFCN. If intelligent selection is ON, DL air-interface capability is used first, then the same ties. UL SCells are never chosen as the target.</t>
         </is>
       </c>
       <c r="C177" s="14" t="n"/>
@@ -5228,15 +5228,19 @@
       <c r="I177" s="14" t="n"/>
       <c r="J177" s="15" t="n"/>
     </row>
-    <row r="178" ht="52" customHeight="1">
+    <row r="178" ht="118" customHeight="1">
       <c r="A178" s="32" t="inlineStr">
         <is>
-          <t>Leave / after HO</t>
+          <t>What “DL still uses both bands, UL rides the coverage layer” means</t>
         </is>
       </c>
       <c r="B178" s="13" t="inlineStr">
         <is>
-          <t>After HO, original SCell = new PCell and original PCell = SCell. In adaptive CA, SCell A2 then manages the old high band (SccA2RsrpThldExtendedOfs; doc −10). Operator off: SpectrumCoordinationSwitch-0. Not a coverage HO; extra HOs raise count, can cut DRX UEs and may drop VoLTE MOS.</t>
+          <t>Coverage layer = low frequency (better uplink reach). Capacity layer = high frequency (more downlink speed, weaker uplink at the edge).
+In normal LTE CA without UL CA, upload (PUSCH/PUCCH) is only on the PCell. Download can use PCell + SCell.
+BEFORE swap: PCell=high band → upload is on high band (often too weak at the edge); download = high + low.
+AFTER swap: PCell=low band → upload is on low band (coverage layer, stronger); the high band is still an SCell so download is still high + low.
+So download does not lose the high band. Only the upload home cell changes. That is why cell-edge users can keep high-band download while their upload survives.</t>
         </is>
       </c>
       <c r="C178" s="14" t="n"/>
@@ -5251,12 +5255,12 @@
     <row r="179" ht="52" customHeight="1">
       <c r="A179" s="32" t="inlineStr">
         <is>
-          <t>Must-on conditions</t>
+          <t>Benefit (1–2 lines)</t>
         </is>
       </c>
       <c r="B179" s="22" t="inlineStr">
         <is>
-          <t>HoAdmitSwitch OFF; HoWithSccCfgSwitch ON; SpectrumCoordinationSwitch ON. After enable also ON: CaEnhancedPreAllocSwitch, Dl2CCAckResShareSw, SccA2RmvSwitch. UE must support CA. CA already live (DL 2–8 CC).</t>
+          <t>It lifts DL usage of CA UEs at the high-frequency UL coverage edge. Best when high/low gap is large. Scenario 1 (both bands already on): PUSCH MCS 0–3 &gt;10% on high band, low-minus-high UL interference &lt;5 dB, CA UE penetration &gt;25% → network User DL Average Throughput up. Scenario 2 (adding a new low band under an existing high band) → both User DL and User UL Average Throughput up.</t>
         </is>
       </c>
       <c r="C179" s="14" t="n"/>
@@ -5271,12 +5275,12 @@
     <row r="180" ht="52" customHeight="1">
       <c r="A180" s="32" t="inlineStr">
         <is>
-          <t>Applicable case</t>
+          <t>Trigger</t>
         </is>
       </c>
       <c r="B180" s="13" t="inlineStr">
         <is>
-          <t>Multi-band CA cluster with overlapping high + low (FPD example 2600 + 850 MHz). Intra-eNodeB. Macro 3900/5900; TDD also LampSite. Not LBBPc.</t>
+          <t>CA UE already aggregating. UL SINR used in scheduling (initial MCS) &lt; SpectrumCoordSinrThld (doc MML −2 dB). Then a DL SCell must pass A4 AND be stronger than all its intra-freq neighbours, and must be allowed as PCell. Target pick: PCell/PCC priority → largest BW → lowest EARFCN (or DL air-interface capability first if intelligent selection is ON).</t>
         </is>
       </c>
       <c r="C180" s="14" t="n"/>
@@ -5291,12 +5295,12 @@
     <row r="181" ht="52" customHeight="1">
       <c r="A181" s="32" t="inlineStr">
         <is>
-          <t>UL / DL CA limitation</t>
+          <t>Leave / after HO</t>
         </is>
       </c>
       <c r="B181" s="22" t="inlineStr">
         <is>
-          <t>Compatible with DL 2CC–8CC. Does NOT take effect if the UE has 2 CC in UL and 2 CC in DL (UL SCells are never SC targets). If UL is 2 CC and DL is 3–8 CC, it does take effect. This is not UL CA; it only moves which cell is PCell so UL uses the low band.</t>
+          <t>After HO, original SCell = new PCell and original PCell = SCell. In adaptive CA, SCell A2 then manages the old high band (SccA2RsrpThldExtendedOfs; doc −10). Operator off: SpectrumCoordinationSwitch-0. Not a coverage HO; extra HOs raise count, can cut DRX UEs and may drop VoLTE MOS.</t>
         </is>
       </c>
       <c r="C181" s="14" t="n"/>
@@ -5311,12 +5315,12 @@
     <row r="182" ht="52" customHeight="1">
       <c r="A182" s="32" t="inlineStr">
         <is>
-          <t>GPS required?</t>
+          <t>Must-on conditions</t>
         </is>
       </c>
       <c r="B182" s="13" t="inlineStr">
         <is>
-          <t>No extra GPS requirement in this FPD. SC is an intra-eNodeB PCell change + CA SCell keep. Site sync stays whatever LTE already needs (TDD still needs the site’s existing GPS/1588/sync; SC does not add a GPS license or a new sync feature).</t>
+          <t>HoAdmitSwitch OFF; HoWithSccCfgSwitch ON; SpectrumCoordinationSwitch ON. After enable also ON: CaEnhancedPreAllocSwitch, Dl2CCAckResShareSw, SccA2RmvSwitch. UE must support CA. CA already live (DL 2–8 CC).</t>
         </is>
       </c>
       <c r="C182" s="14" t="n"/>
@@ -5331,12 +5335,12 @@
     <row r="183" ht="52" customHeight="1">
       <c r="A183" s="32" t="inlineStr">
         <is>
-          <t>License (if asked)</t>
+          <t>Applicable case</t>
         </is>
       </c>
       <c r="B183" s="22" t="inlineStr">
         <is>
-          <t>FDD LCOFD-131312 model LT1SUNPLTE00 per cell; TDD TDLCOFD-131312 model LT1SLTESPC00 per cell. Enhancement uses the same license. CA licenses still required. License shortage can block ACT CELL.</t>
+          <t>Multi-band CA cluster with overlapping high + low (FPD example 2600 + 850 MHz). Intra-eNodeB. Macro 3900/5900; TDD also LampSite. Not LBBPc.</t>
         </is>
       </c>
       <c r="C183" s="14" t="n"/>
@@ -5351,12 +5355,12 @@
     <row r="184" ht="52" customHeight="1">
       <c r="A184" s="32" t="inlineStr">
         <is>
-          <t>How we know it is working</t>
+          <t>UL / DL CA limitation</t>
         </is>
       </c>
       <c r="B184" s="13" t="inlineStr">
         <is>
-          <t>L.HHO.InterFreq.ULquality.Prep/Exec/Succ (1526729994 / 9996 / 9998) increase. Also watch CA PCell/SCell users and bits, CA UE DL rate, SCell add success (tied to HO success).</t>
+          <t>Compatible with DL 2CC–8CC. Does NOT take effect if the UE has 2 CC in UL and 2 CC in DL (UL SCells are never SC targets). If UL is 2 CC and DL is 3–8 CC, it does take effect. This is not UL CA; it only moves which cell is PCell so UL uses the low band.</t>
         </is>
       </c>
       <c r="C184" s="14" t="n"/>
@@ -5371,12 +5375,12 @@
     <row r="185" ht="52" customHeight="1">
       <c r="A185" s="32" t="inlineStr">
         <is>
-          <t>Do not mix / watch-outs</t>
+          <t>GPS required?</t>
         </is>
       </c>
       <c r="B185" s="22" t="inlineStr">
         <is>
-          <t>Not DSS, not GSM/UMTS spectrum sharing, not NR UL/DL decoupling. DSS / SUL DSS cut LTE UL RBs → fewer UEs get SC. NSA: may HO PCC off an NSA anchor — deselect SPCT_COORD_INTER_FREQ_HO_SW to exempt NSA UEs. Enhancement (WBB/RRN) is a different bit (WbbCaMultiCarrierCoordSw); NSA PCC anchoring wins over it. SCC coverage-threshold adaptation kills SC carrier management. More HOs; CQI/KPI move with the new PCell quality.</t>
+          <t>No extra GPS requirement in this FPD. SC is an intra-eNodeB PCell change + CA SCell keep. Site sync stays whatever LTE already needs (TDD still needs the site’s existing GPS/1588/sync; SC does not add a GPS license or a new sync feature).</t>
         </is>
       </c>
       <c r="C185" s="14" t="n"/>
@@ -5388,19 +5392,15 @@
       <c r="I185" s="14" t="n"/>
       <c r="J185" s="15" t="n"/>
     </row>
-    <row r="186" ht="118" customHeight="1">
+    <row r="186" ht="52" customHeight="1">
       <c r="A186" s="32" t="inlineStr">
         <is>
-          <t>Plain-English close  (read this if the jargon is heavy)</t>
+          <t>License (if asked)</t>
         </is>
       </c>
       <c r="B186" s="13" t="inlineStr">
         <is>
-          <t>1) First make normal Carrier Aggregation work between one high-frequency cell and one low-frequency cell (same site, overlapping coverage). If CA is not working, do not turn Spectrum Coordination on.
-2) Spectrum Coordination does not join two carriers by itself. CA already joined them. This feature only changes which of those two cells is the PCell (the cell that carries the uplink).
-3) When the UE is near the cell edge, uplink on the high band is weak (poor UL SINR). The eNodeB then makes the low-band cell the PCell so the UE transmits uplink on the low band (better coverage).
-4) The high-band cell is kept as an SCell, so downlink data can still use both bands. That is the gain: cell-edge users keep high-band download speed even when their upload cannot stay on the high band.
-5) Short version: CA = two pipes for download. Spectrum Coordination = move the upload pipe to the low band at the edge, without throwing away the high-band download pipe.</t>
+          <t>FDD LCOFD-131312 model LT1SUNPLTE00 per cell; TDD TDLCOFD-131312 model LT1SLTESPC00 per cell. Enhancement uses the same license. CA licenses still required. License shortage can block ACT CELL.</t>
         </is>
       </c>
       <c r="C186" s="14" t="n"/>
@@ -5412,8 +5412,72 @@
       <c r="I186" s="14" t="n"/>
       <c r="J186" s="15" t="n"/>
     </row>
+    <row r="187" ht="52" customHeight="1">
+      <c r="A187" s="32" t="inlineStr">
+        <is>
+          <t>How we know it is working</t>
+        </is>
+      </c>
+      <c r="B187" s="22" t="inlineStr">
+        <is>
+          <t>L.HHO.InterFreq.ULquality.Prep/Exec/Succ (1526729994 / 9996 / 9998) increase. Also watch CA PCell/SCell users and bits, CA UE DL rate, SCell add success (tied to HO success).</t>
+        </is>
+      </c>
+      <c r="C187" s="14" t="n"/>
+      <c r="D187" s="14" t="n"/>
+      <c r="E187" s="14" t="n"/>
+      <c r="F187" s="14" t="n"/>
+      <c r="G187" s="14" t="n"/>
+      <c r="H187" s="14" t="n"/>
+      <c r="I187" s="14" t="n"/>
+      <c r="J187" s="15" t="n"/>
+    </row>
+    <row r="188" ht="52" customHeight="1">
+      <c r="A188" s="32" t="inlineStr">
+        <is>
+          <t>Do not mix / watch-outs</t>
+        </is>
+      </c>
+      <c r="B188" s="13" t="inlineStr">
+        <is>
+          <t>Not DSS, not GSM/UMTS spectrum sharing, not NR UL/DL decoupling. DSS / SUL DSS cut LTE UL RBs → fewer UEs get SC. NSA: may HO PCC off an NSA anchor — deselect SPCT_COORD_INTER_FREQ_HO_SW to exempt NSA UEs. Enhancement (WBB/RRN) is a different bit (WbbCaMultiCarrierCoordSw); NSA PCC anchoring wins over it. SCC coverage-threshold adaptation kills SC carrier management. More HOs; CQI/KPI move with the new PCell quality.</t>
+        </is>
+      </c>
+      <c r="C188" s="14" t="n"/>
+      <c r="D188" s="14" t="n"/>
+      <c r="E188" s="14" t="n"/>
+      <c r="F188" s="14" t="n"/>
+      <c r="G188" s="14" t="n"/>
+      <c r="H188" s="14" t="n"/>
+      <c r="I188" s="14" t="n"/>
+      <c r="J188" s="15" t="n"/>
+    </row>
+    <row r="189" ht="118" customHeight="1">
+      <c r="A189" s="32" t="inlineStr">
+        <is>
+          <t>Plain-English close  (read this if the jargon is heavy)</t>
+        </is>
+      </c>
+      <c r="B189" s="22" t="inlineStr">
+        <is>
+          <t>1) First make normal Carrier Aggregation work between one high-frequency cell and one low-frequency cell (same site, overlapping coverage). If CA is not working, do not turn Spectrum Coordination on.
+2) Spectrum Coordination does not join two carriers by itself. CA already joined them. This feature only changes which of those two cells is the PCell (the cell that carries the uplink).
+3) When the UE is near the cell edge, uplink on the high band is weak (poor UL SINR). The eNodeB then makes the low-band cell the PCell so the UE transmits uplink on the low band (better coverage).
+4) The high-band cell is kept as an SCell, so downlink data can still use both bands. That is the gain: cell-edge users keep high-band download speed even when their upload cannot stay on the high band.
+5) Short version: CA = two pipes for download. Spectrum Coordination = move the upload pipe to the low band at the edge, without throwing away the high-band download pipe.</t>
+        </is>
+      </c>
+      <c r="C189" s="14" t="n"/>
+      <c r="D189" s="14" t="n"/>
+      <c r="E189" s="14" t="n"/>
+      <c r="F189" s="14" t="n"/>
+      <c r="G189" s="14" t="n"/>
+      <c r="H189" s="14" t="n"/>
+      <c r="I189" s="14" t="n"/>
+      <c r="J189" s="15" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="163">
+  <mergeCells count="166">
     <mergeCell ref="E138:J138"/>
     <mergeCell ref="E143:J143"/>
     <mergeCell ref="G109:J109"/>
@@ -5515,13 +5579,16 @@
     <mergeCell ref="A59:J59"/>
     <mergeCell ref="G115:J115"/>
     <mergeCell ref="E119:J119"/>
+    <mergeCell ref="B187:J187"/>
     <mergeCell ref="A64:J64"/>
     <mergeCell ref="A169:J169"/>
     <mergeCell ref="A51:J51"/>
     <mergeCell ref="E25:J25"/>
     <mergeCell ref="A61:J61"/>
+    <mergeCell ref="B189:J189"/>
     <mergeCell ref="A162:J162"/>
     <mergeCell ref="E146:J146"/>
+    <mergeCell ref="B188:J188"/>
     <mergeCell ref="A54:J54"/>
     <mergeCell ref="E121:J121"/>
     <mergeCell ref="G103:J103"/>

--- a/LTE_Spectrum_Coordination.xlsx
+++ b/LTE_Spectrum_Coordination.xlsx
@@ -703,11 +703,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="001F4E79"/>
+    <tabColor rgb="000D7377"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J189"/>
+  <dimension ref="A1:J190"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1075,7 +1075,7 @@
     <row r="33" ht="28" customHeight="1">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>Trigger is uplink SINR used in scheduling (initial MCS selection), compared with CaMgtCfg.SpectrumCoordSinrThld.  Doc optimization MML sets SpectrumCoordSinrThld = −2 on every original PCell.  This is NOT CA event A1–A6 as the trigger (A4/A2 are used afterwards to pick the target SCell and to manage SCells).</t>
+          <t>Trigger is uplink SINR used in scheduling (initial MCS selection), compared with CaMgtCfg.SpectrumCoordSinrThld.  Doc optimization MML sets SpectrumCoordSinrThld = −2 on every original PCell.  This is NOT CA event A1–A6 as the trigger. After the SINR trigger, target SCell suitability uses PCellA4RsrpThd/PccA4RsrpThd; post-HO SCell leave uses CarrAggrA2ThdRsrp + SccA2Offset [+ SccA2RsrpThldExtendedOfs].</t>
         </is>
       </c>
       <c r="B33" s="4" t="n"/>
@@ -1160,10 +1160,10 @@
       <c r="I37" s="11" t="n"/>
       <c r="J37" s="11" t="n"/>
     </row>
-    <row r="38" ht="130" customHeight="1">
+    <row r="38" ht="155" customHeight="1">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t>•  Downlink signal strength of that SCell reaches the RSRP threshold for event A4  AND  is higher than all of its intra-frequency neighboring cells. If either fails, the SCell is not a target.
+          <t>•  Downlink RSRP of that SCell reaches CaGroupCell.PCellA4RsrpThd (group) or PccFreqCfg.PccA4RsrpThd (adaptive)  AND  is higher than all of its intra-frequency neighboring cells. If either fails, the SCell is not a target. This is NOT CaMgtCfg.CarrAggrA4ThdRsrp (that is CA SCell-add A4).
 •  Recommendation (Ch.4.1): CaGroupCell.PCellA4RsrpThd (group) or PccFreqCfg.PccA4RsrpThd (adaptive)  &gt;  InterFreqHoGroup.InterFreqHoA4ThdRsrp, to prevent a decrease in handover success rate.
 •  The SCell must also meet PCell conditions (see Carrier Aggregation FPD — this workbook Step1).
 •  If no downlink SCell meets the conditions: eNodeB does not initiate an inter-frequency handover.
@@ -1185,7 +1185,7 @@
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="17" t="inlineStr">
         <is>
-          <t>B2 worked example  —  is this SCell a legal SC target?  (A4 + strongest intra-freq)</t>
+          <t>B2 worked example  —  is this SCell a legal SC target?  (PCellA4RsrpThd/PccA4RsrpThd + strongest intra-freq)</t>
         </is>
       </c>
       <c r="B39" s="6" t="n"/>
@@ -1198,13 +1198,13 @@
       <c r="I39" s="6" t="n"/>
       <c r="J39" s="6" t="n"/>
     </row>
-    <row r="40" ht="76" customHeight="1">
+    <row r="40" ht="80" customHeight="1">
       <c r="A40" s="18" t="inlineStr">
         <is>
           <t>3GPP / Huawei condition:
-SCell is suitable iff  (SCell RSRP reaches CA event A4)  AND  (SCell RSRP &gt; every intra-frequency neighbor of that SCell).
-CA A4 entering (this workbook / CA FPD Ch.4.3):  Mn + Ofn + Ocn − Hys  &gt;  Thresh
-Thresh = CarrAggrA4ThdRsrp + SCellA4Offset/SccA4Offset  (offsets 0 in the CA FPD MML examples).</t>
+SCell is suitable iff  (SCell RSRP reaches CaGroupCell.PCellA4RsrpThd [group] or PccFreqCfg.PccA4RsrpThd [adaptive])  AND  (SCell RSRP &gt; every intra-frequency neighbor of that SCell).
+Keep PCellA4RsrpThd/PccA4RsrpThd &gt; InterFreqHoGroup.InterFreqHoA4ThdRsrp so SC HO does not steal coverage HO.
+CA SCell-add A4 (used later for carrier management) is separate: CaMgtCfg.CarrAggrA4ThdRsrp + CaGroupSCellCfg.SCellA4Offset (group) or SccFreqCfg.SccA4Offset (adaptive).</t>
         </is>
       </c>
       <c r="B40" s="19" t="n"/>
@@ -1261,12 +1261,12 @@
       </c>
       <c r="B43" s="12" t="inlineStr">
         <is>
-          <t>Intelligent selection OFF (CaSmartSelectionSwitch)</t>
+          <t>CaSmartSelectionSwitch OFF</t>
         </is>
       </c>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>Intelligent selection ON</t>
+          <t>CaSmartSelectionSwitch ON</t>
         </is>
       </c>
       <c r="D43" s="12" t="inlineStr"/>
@@ -1277,7 +1277,7 @@
       <c r="I43" s="12" t="inlineStr"/>
       <c r="J43" s="12" t="inlineStr"/>
     </row>
-    <row r="44" ht="40" customHeight="1">
+    <row r="44" ht="56" customHeight="1">
       <c r="A44" s="13" t="inlineStr">
         <is>
           <t>1</t>
@@ -1285,12 +1285,12 @@
       </c>
       <c r="B44" s="13" t="inlineStr">
         <is>
-          <t>Highest PCell priority (CaGroupCell.PreferredPCellPriority) or PCC priority (PccFreqCfg.PreferredPccPriority)</t>
+          <t>Highest CaGroupCell.PreferredPCellPriority (group) or PccFreqCfg.PreferredPccPriority (adaptive)</t>
         </is>
       </c>
       <c r="C44" s="13" t="inlineStr">
         <is>
-          <t>Highest downlink air interface capability (see CA FPD)</t>
+          <t>Highest DL air interface capability (CA FPD Ch.12). CaMgtCfg.MinDlAvgToBeScheduledUeNum=0 → P×SF×SE−G; else (P×SF×SE−G)/N. P=L.ChMeas.PRB.DL.Avail, SF=CellMLB.CellCapacityScaleFactor, G=GBR BW, SE=spectral efficiency, N=active UEs (floor=MinDlAvgToBeScheduledUeNum)</t>
         </is>
       </c>
       <c r="D44" s="14" t="n"/>
@@ -1301,7 +1301,7 @@
       <c r="I44" s="14" t="n"/>
       <c r="J44" s="15" t="n"/>
     </row>
-    <row r="45" ht="40" customHeight="1">
+    <row r="45" ht="56" customHeight="1">
       <c r="A45" s="16" t="inlineStr">
         <is>
           <t>2</t>
@@ -1309,12 +1309,12 @@
       </c>
       <c r="B45" s="16" t="inlineStr">
         <is>
-          <t>If still tied: largest bandwidth</t>
+          <t>If still tied: largest cell bandwidth</t>
         </is>
       </c>
       <c r="C45" s="16" t="inlineStr">
         <is>
-          <t>If still tied: highest PCell / PCC priority (same MOs as left)</t>
+          <t>If still tied: highest PreferredPCellPriority / PreferredPccPriority</t>
         </is>
       </c>
       <c r="D45" s="14" t="n"/>
@@ -1325,7 +1325,7 @@
       <c r="I45" s="14" t="n"/>
       <c r="J45" s="15" t="n"/>
     </row>
-    <row r="46" ht="40" customHeight="1">
+    <row r="46" ht="56" customHeight="1">
       <c r="A46" s="13" t="inlineStr">
         <is>
           <t>3</t>
@@ -1333,12 +1333,12 @@
       </c>
       <c r="B46" s="13" t="inlineStr">
         <is>
-          <t>If still tied: lowest center frequency</t>
+          <t>If still tied: lowest center frequency (EARFCN)</t>
         </is>
       </c>
       <c r="C46" s="13" t="inlineStr">
         <is>
-          <t>If still tied: larger bandwidth; then lowest center frequency</t>
+          <t>If still tied: larger bandwidth, then lowest EARFCN</t>
         </is>
       </c>
       <c r="D46" s="14" t="n"/>
@@ -1368,8 +1368,8 @@
     <row r="48" ht="88" customHeight="1">
       <c r="A48" s="20" t="inlineStr">
         <is>
-          <t>Doc 3CC optimization MML uses three downlink EARFCNs 123 / 567 / 890 as PCC/SCC pairs. Sample (intelligent selection OFF):
-UE PCell = high-frequency cell on EARFCN 890, UL SINR = −3 dB &lt; −2 dB → SC starts. Two DL SCells both pass A4+strongest:
+          <t>Doc 3CC optimization MML uses three downlink EARFCNs 123 / 567 / 890 as PCC/SCC pairs. Sample (ENodeBAlgoSwitch.CaAlgoSwitch / CaSmartSelectionSwitch OFF):
+UE PCell = high-frequency cell on EARFCN 890, UL SINR = −3 dB &lt; −2 dB → SC starts. Two DL SCells both pass PCellA4RsrpThd/PccA4RsrpThd + strongest:
   Cell A  EARFCN 123, PreferredPccPriority=2, BW=10 MHz
   Cell B  EARFCN 567, PreferredPccPriority=2, BW=20 MHz
 Same PCC priority → pick largest bandwidth → Cell B. After HO: PCell = Cell B, original 890-cell becomes SCell. If both had BW=20 MHz, pick the lower EARFCN (123).</t>
@@ -1452,7 +1452,7 @@
     <row r="53" ht="20" customHeight="1">
       <c r="A53" s="17" t="inlineStr">
         <is>
-          <t>C2.  SccA2RsrpThldExtendedOfs ≠ 0  and intelligent selection ON  (Ch.4.1 steps i–iv)</t>
+          <t>C2.  SccA2RsrpThldExtendedOfs ≠ 0  and CaSmartSelectionSwitch ON  (Ch.4.1 steps i–iv)</t>
         </is>
       </c>
       <c r="B53" s="6" t="n"/>
@@ -1475,7 +1475,7 @@
 If RSRP meets the new condition → remove SCell (end).
 If not → delete previous A2 cfg; deliver new A2 cfg + A1 cfg for this SCell.
     A1 threshold  =  CarrAggrA4ThdRsrp + SccA4Offset
-Before further A2/A1, intelligent selection may pick a better SCell.
+Before further A2/A1, CaSmartSelectionSwitch may pick a better SCell using the Ch.12 DL air interface capability formula (MinDlAvgToBeScheduledUeNum).
 Further A2 containing this SCell → remove it.  A1 containing this SCell → release new A2, restore previous A2 (threshold back to CarrAggrA2ThdRsrp + SccA2Offset).</t>
         </is>
       </c>
@@ -1497,7 +1497,7 @@
 First A2 thresh = −115 dBm. New A2 thresh = −115 + 0 + (−10) = −125 dBm.
 SCell RSRP in the report = −118 dBm.
 −118 meets first A2 (below −115) but does NOT meet new A2 (need to be below −125).
-Result: SCell is NOT removed on the first A2. eNodeB switches to the extended A2 + A1 pair (A1 thresh = −105 dBm) and intelligent selection may replace the SCell. If a later A2 still contains this SCell, it is removed.</t>
+Result: SCell is NOT removed on the first A2. eNodeB switches to the extended A2 + A1 pair (A1 thresh = CarrAggrA4ThdRsrp + SccA4Offset = −105 dBm) and CaSmartSelectionSwitch may replace the SCell. If a later A2 still contains this SCell, it is removed.</t>
         </is>
       </c>
       <c r="B55" s="21" t="n"/>
@@ -1513,7 +1513,7 @@
     <row r="56" ht="20" customHeight="1">
       <c r="A56" s="10" t="inlineStr">
         <is>
-          <t>C3.  SccA2RsrpThldExtendedOfs ≠ 0  and intelligent selection OFF</t>
+          <t>C3.  SccA2RsrpThldExtendedOfs ≠ 0  and CaSmartSelectionSwitch OFF</t>
         </is>
       </c>
       <c r="B56" s="11" t="n"/>
@@ -2804,7 +2804,7 @@
       </c>
       <c r="F94" s="33" t="inlineStr">
         <is>
-          <t>First tie-break among multiple SC target SCells when intelligent selection is OFF (and second tie-break when ON).</t>
+          <t>First tie-break among multiple SC target SCells when CaSmartSelectionSwitch is OFF (and second tie-break when ON).</t>
         </is>
       </c>
       <c r="G94" s="33" t="inlineStr">
@@ -2816,7 +2816,7 @@
       <c r="I94" s="14" t="n"/>
       <c r="J94" s="15" t="n"/>
     </row>
-    <row r="95" ht="40" customHeight="1">
+    <row r="95" ht="64" customHeight="1">
       <c r="A95" s="31" t="n">
         <v>12</v>
       </c>
@@ -2842,7 +2842,7 @@
       </c>
       <c r="F95" s="33" t="inlineStr">
         <is>
-          <t>Intelligent selection of serving cell combinations. Changes B3 selection order and C2 vs C3 A2 handling.</t>
+          <t>ENodeBAlgoSwitch.CaAlgoSwitch bit CaSmartSelectionSwitch. ON: first pick among SC targets is highest DL air interface capability (CaMgtCfg.MinDlAvgToBeScheduledUeNum formula). OFF: first pick is PreferredPCellPriority/PreferredPccPriority. Also changes C2 vs C3 A2 handling.</t>
         </is>
       </c>
       <c r="G95" s="33" t="inlineStr">
@@ -5168,7 +5168,7 @@
       <c r="I174" s="12" t="inlineStr"/>
       <c r="J174" s="12" t="inlineStr"/>
     </row>
-    <row r="175" ht="52" customHeight="1">
+    <row r="175" ht="82" customHeight="1">
       <c r="A175" s="32" t="inlineStr">
         <is>
           <t>What it is (10 s)</t>
@@ -5188,7 +5188,7 @@
       <c r="I175" s="14" t="n"/>
       <c r="J175" s="15" t="n"/>
     </row>
-    <row r="176" ht="52" customHeight="1">
+    <row r="176" ht="72" customHeight="1">
       <c r="A176" s="32" t="inlineStr">
         <is>
           <t>Q1. Is the low-band SCell already configured with this PCell?</t>
@@ -5208,7 +5208,7 @@
       <c r="I176" s="14" t="n"/>
       <c r="J176" s="15" t="n"/>
     </row>
-    <row r="177" ht="52" customHeight="1">
+    <row r="177" ht="116" customHeight="1">
       <c r="A177" s="32" t="inlineStr">
         <is>
           <t>Q2. If the UE has several SCells, which one becomes the new PCell?</t>
@@ -5216,7 +5216,8 @@
       </c>
       <c r="B177" s="22" t="inlineStr">
         <is>
-          <t>Only SCells that pass ALL of: (a) better uplink than the current PCell, (b) DL RSRP reaches CA event A4, (c) stronger than all intra-frequency neighbors of that SCell, (d) allowed to be a PCell. If only one SCell passes → HO to that one. If two or more pass → pick by rule: highest PCell/PCC priority, then largest bandwidth, then lowest EARFCN. If intelligent selection is ON, DL air-interface capability is used first, then the same ties. UL SCells are never chosen as the target.</t>
+          <t>Only existing DL SCells that pass ALL of: (a) better uplink than the current PCell; (b) DL RSRP reaches CaGroupCell.PCellA4RsrpThd (group) or PccFreqCfg.PccA4RsrpThd (adaptive) — keep this &gt; InterFreqHoGroup.InterFreqHoA4ThdRsrp; do not confuse with CA SCell-add CaMgtCfg.CarrAggrA4ThdRsrp; (c) stronger than all intra-frequency neighbors of that SCell; (d) allowed to be a PCell. UL SCells are never the target (CaMgtCfg.CellCaAlgoSwitch / CaUl2CCSwitch UEs with UL2CC+DL2CC are excluded).
+One candidate → HO to it. Several candidates → see next row for the pick order.</t>
         </is>
       </c>
       <c r="C177" s="14" t="n"/>
@@ -5228,19 +5229,17 @@
       <c r="I177" s="14" t="n"/>
       <c r="J177" s="15" t="n"/>
     </row>
-    <row r="178" ht="118" customHeight="1">
+    <row r="178" ht="140" customHeight="1">
       <c r="A178" s="32" t="inlineStr">
         <is>
-          <t>What “DL still uses both bands, UL rides the coverage layer” means</t>
+          <t>How the eNodeB picks among several legal SCells</t>
         </is>
       </c>
       <c r="B178" s="13" t="inlineStr">
         <is>
-          <t>Coverage layer = low frequency (better uplink reach). Capacity layer = high frequency (more downlink speed, weaker uplink at the edge).
-In normal LTE CA without UL CA, upload (PUSCH/PUCCH) is only on the PCell. Download can use PCell + SCell.
-BEFORE swap: PCell=high band → upload is on high band (often too weak at the edge); download = high + low.
-AFTER swap: PCell=low band → upload is on low band (coverage layer, stronger); the high band is still an SCell so download is still high + low.
-So download does not lose the high band. Only the upload home cell changes. That is why cell-edge users can keep high-band download while their upload survives.</t>
+          <t>Switch: ENodeBAlgoSwitch.CaAlgoSwitch → CaSmartSelectionSwitch.
+OFF: 1) highest CaGroupCell.PreferredPCellPriority (group) or PccFreqCfg.PreferredPccPriority (adaptive)  2) largest cell bandwidth  3) lowest center frequency (EARFCN).
+ON: 1) highest downlink air interface capability of the cell, from CA FPD Ch.12: if CaMgtCfg.MinDlAvgToBeScheduledUeNum=0 then P×SF×SE−G, else (P×SF×SE−G)/N. P = L.ChMeas.PRB.DL.Avail; SF = CellMLB.CellCapacityScaleFactor; G = GBR bandwidth in the cell; SE = cell spectral efficiency; N = active UEs (floor = MinDlAvgToBeScheduledUeNum).  2) same PreferredPCellPriority / PreferredPccPriority  3) larger bandwidth  4) lowest EARFCN.</t>
         </is>
       </c>
       <c r="C178" s="14" t="n"/>
@@ -5252,15 +5251,19 @@
       <c r="I178" s="14" t="n"/>
       <c r="J178" s="15" t="n"/>
     </row>
-    <row r="179" ht="52" customHeight="1">
+    <row r="179" ht="168" customHeight="1">
       <c r="A179" s="32" t="inlineStr">
         <is>
-          <t>Benefit (1–2 lines)</t>
+          <t>What “DL still uses both bands, UL rides the coverage layer” means</t>
         </is>
       </c>
       <c r="B179" s="22" t="inlineStr">
         <is>
-          <t>It lifts DL usage of CA UEs at the high-frequency UL coverage edge. Best when high/low gap is large. Scenario 1 (both bands already on): PUSCH MCS 0–3 &gt;10% on high band, low-minus-high UL interference &lt;5 dB, CA UE penetration &gt;25% → network User DL Average Throughput up. Scenario 2 (adding a new low band under an existing high band) → both User DL and User UL Average Throughput up.</t>
+          <t>Coverage layer = low frequency (better uplink reach). Capacity layer = high frequency (more downlink speed, weaker uplink at the edge).
+In normal LTE CA without UL CA, upload (PUSCH/PUCCH) is only on the PCell. Download can use PCell + SCell.
+BEFORE swap: PCell=high band → upload is on high band (often too weak at the edge); download = high + low.
+AFTER swap: PCell=low band → upload is on low band (coverage layer, stronger); the high band is still an SCell so download is still high + low.
+So download does not lose the high band. Only the upload home cell changes. That is why cell-edge users can keep high-band download while their upload survives.</t>
         </is>
       </c>
       <c r="C179" s="14" t="n"/>
@@ -5272,15 +5275,15 @@
       <c r="I179" s="14" t="n"/>
       <c r="J179" s="15" t="n"/>
     </row>
-    <row r="180" ht="52" customHeight="1">
+    <row r="180" ht="82" customHeight="1">
       <c r="A180" s="32" t="inlineStr">
         <is>
-          <t>Trigger</t>
+          <t>Benefit (1–2 lines)</t>
         </is>
       </c>
       <c r="B180" s="13" t="inlineStr">
         <is>
-          <t>CA UE already aggregating. UL SINR used in scheduling (initial MCS) &lt; SpectrumCoordSinrThld (doc MML −2 dB). Then a DL SCell must pass A4 AND be stronger than all its intra-freq neighbours, and must be allowed as PCell. Target pick: PCell/PCC priority → largest BW → lowest EARFCN (or DL air-interface capability first if intelligent selection is ON).</t>
+          <t>It lifts DL usage of CA UEs at the high-frequency UL coverage edge. Best when high/low gap is large. Scenario 1 (both bands already on): PUSCH MCS 0–3 &gt;10% on high band, low-minus-high UL interference &lt;5 dB, CA UE penetration &gt;25% → network User DL Average Throughput up. Scenario 2 (adding a new low band under an existing high band) → both User DL and User UL Average Throughput up.</t>
         </is>
       </c>
       <c r="C180" s="14" t="n"/>
@@ -5292,15 +5295,15 @@
       <c r="I180" s="14" t="n"/>
       <c r="J180" s="15" t="n"/>
     </row>
-    <row r="181" ht="52" customHeight="1">
+    <row r="181" ht="122" customHeight="1">
       <c r="A181" s="32" t="inlineStr">
         <is>
-          <t>Leave / after HO</t>
+          <t>Trigger</t>
         </is>
       </c>
       <c r="B181" s="22" t="inlineStr">
         <is>
-          <t>After HO, original SCell = new PCell and original PCell = SCell. In adaptive CA, SCell A2 then manages the old high band (SccA2RsrpThldExtendedOfs; doc −10). Operator off: SpectrumCoordinationSwitch-0. Not a coverage HO; extra HOs raise count, can cut DRX UEs and may drop VoLTE MOS.</t>
+          <t>CA UE already aggregating. UL SINR used in scheduling (initial MCS) &lt; CaMgtCfg.SpectrumCoordSinrThld (doc MML −2 dB). Then a DL SCell must reach CaGroupCell.PCellA4RsrpThd (group) or PccFreqCfg.PccA4RsrpThd (adaptive), AND be stronger than all intra-freq neighbours, AND be allowed as PCell. Recommend PCellA4RsrpThd/PccA4RsrpThd &gt; InterFreqHoGroup.InterFreqHoA4ThdRsrp. Target pick: if ENodeBAlgoSwitch.CaAlgoSwitch / CaSmartSelectionSwitch OFF → CaGroupCell.PreferredPCellPriority or PccFreqCfg.PreferredPccPriority → largest BW → lowest EARFCN. If CaSmartSelectionSwitch ON → highest DL air interface capability first (CaMgtCfg.MinDlAvgToBeScheduledUeNum=0 → P×SF×SE−G else (P×SF×SE−G)/N; P=L.ChMeas.PRB.DL.Avail, SF=CellMLB.CellCapacityScaleFactor), then the same ties.</t>
         </is>
       </c>
       <c r="C181" s="14" t="n"/>
@@ -5312,15 +5315,15 @@
       <c r="I181" s="14" t="n"/>
       <c r="J181" s="15" t="n"/>
     </row>
-    <row r="182" ht="52" customHeight="1">
+    <row r="182" ht="72" customHeight="1">
       <c r="A182" s="32" t="inlineStr">
         <is>
-          <t>Must-on conditions</t>
+          <t>Leave / after HO</t>
         </is>
       </c>
       <c r="B182" s="13" t="inlineStr">
         <is>
-          <t>HoAdmitSwitch OFF; HoWithSccCfgSwitch ON; SpectrumCoordinationSwitch ON. After enable also ON: CaEnhancedPreAllocSwitch, Dl2CCAckResShareSw, SccA2RmvSwitch. UE must support CA. CA already live (DL 2–8 CC).</t>
+          <t>After HO, original SCell = new PCell and original PCell = SCell. In adaptive CA, SCell A2 then manages the old high band (SccA2RsrpThldExtendedOfs; doc −10). Operator off: SpectrumCoordinationSwitch-0. Not a coverage HO; extra HOs raise count, can cut DRX UEs and may drop VoLTE MOS.</t>
         </is>
       </c>
       <c r="C182" s="14" t="n"/>
@@ -5332,15 +5335,15 @@
       <c r="I182" s="14" t="n"/>
       <c r="J182" s="15" t="n"/>
     </row>
-    <row r="183" ht="52" customHeight="1">
+    <row r="183" ht="62" customHeight="1">
       <c r="A183" s="32" t="inlineStr">
         <is>
-          <t>Applicable case</t>
+          <t>Must-on conditions</t>
         </is>
       </c>
       <c r="B183" s="22" t="inlineStr">
         <is>
-          <t>Multi-band CA cluster with overlapping high + low (FPD example 2600 + 850 MHz). Intra-eNodeB. Macro 3900/5900; TDD also LampSite. Not LBBPc.</t>
+          <t>HoAdmitSwitch OFF; HoWithSccCfgSwitch ON; SpectrumCoordinationSwitch ON. After enable also ON: CaEnhancedPreAllocSwitch, Dl2CCAckResShareSw, SccA2RmvSwitch. UE must support CA. CA already live (DL 2–8 CC).</t>
         </is>
       </c>
       <c r="C183" s="14" t="n"/>
@@ -5355,12 +5358,12 @@
     <row r="184" ht="52" customHeight="1">
       <c r="A184" s="32" t="inlineStr">
         <is>
-          <t>UL / DL CA limitation</t>
+          <t>Applicable case</t>
         </is>
       </c>
       <c r="B184" s="13" t="inlineStr">
         <is>
-          <t>Compatible with DL 2CC–8CC. Does NOT take effect if the UE has 2 CC in UL and 2 CC in DL (UL SCells are never SC targets). If UL is 2 CC and DL is 3–8 CC, it does take effect. This is not UL CA; it only moves which cell is PCell so UL uses the low band.</t>
+          <t>Multi-band CA cluster with overlapping high + low (FPD example 2600 + 850 MHz). Intra-eNodeB. Macro 3900/5900; TDD also LampSite. Not LBBPc.</t>
         </is>
       </c>
       <c r="C184" s="14" t="n"/>
@@ -5372,15 +5375,15 @@
       <c r="I184" s="14" t="n"/>
       <c r="J184" s="15" t="n"/>
     </row>
-    <row r="185" ht="52" customHeight="1">
+    <row r="185" ht="62" customHeight="1">
       <c r="A185" s="32" t="inlineStr">
         <is>
-          <t>GPS required?</t>
+          <t>UL / DL CA limitation</t>
         </is>
       </c>
       <c r="B185" s="22" t="inlineStr">
         <is>
-          <t>No extra GPS requirement in this FPD. SC is an intra-eNodeB PCell change + CA SCell keep. Site sync stays whatever LTE already needs (TDD still needs the site’s existing GPS/1588/sync; SC does not add a GPS license or a new sync feature).</t>
+          <t>Compatible with DL 2CC–8CC. Does NOT take effect if the UE has 2 CC in UL and 2 CC in DL (UL SCells are never SC targets). If UL is 2 CC and DL is 3–8 CC, it does take effect. This is not UL CA; it only moves which cell is PCell so UL uses the low band.</t>
         </is>
       </c>
       <c r="C185" s="14" t="n"/>
@@ -5392,15 +5395,15 @@
       <c r="I185" s="14" t="n"/>
       <c r="J185" s="15" t="n"/>
     </row>
-    <row r="186" ht="52" customHeight="1">
+    <row r="186" ht="62" customHeight="1">
       <c r="A186" s="32" t="inlineStr">
         <is>
-          <t>License (if asked)</t>
+          <t>GPS required?</t>
         </is>
       </c>
       <c r="B186" s="13" t="inlineStr">
         <is>
-          <t>FDD LCOFD-131312 model LT1SUNPLTE00 per cell; TDD TDLCOFD-131312 model LT1SLTESPC00 per cell. Enhancement uses the same license. CA licenses still required. License shortage can block ACT CELL.</t>
+          <t>No extra GPS requirement in this FPD. SC is an intra-eNodeB PCell change + CA SCell keep. Site sync stays whatever LTE already needs (TDD still needs the site’s existing GPS/1588/sync; SC does not add a GPS license or a new sync feature).</t>
         </is>
       </c>
       <c r="C186" s="14" t="n"/>
@@ -5412,15 +5415,15 @@
       <c r="I186" s="14" t="n"/>
       <c r="J186" s="15" t="n"/>
     </row>
-    <row r="187" ht="52" customHeight="1">
+    <row r="187" ht="62" customHeight="1">
       <c r="A187" s="32" t="inlineStr">
         <is>
-          <t>How we know it is working</t>
+          <t>License (if asked)</t>
         </is>
       </c>
       <c r="B187" s="22" t="inlineStr">
         <is>
-          <t>L.HHO.InterFreq.ULquality.Prep/Exec/Succ (1526729994 / 9996 / 9998) increase. Also watch CA PCell/SCell users and bits, CA UE DL rate, SCell add success (tied to HO success).</t>
+          <t>FDD LCOFD-131312 model LT1SUNPLTE00 per cell; TDD TDLCOFD-131312 model LT1SLTESPC00 per cell. Enhancement uses the same license. CA licenses still required. License shortage can block ACT CELL.</t>
         </is>
       </c>
       <c r="C187" s="14" t="n"/>
@@ -5435,12 +5438,12 @@
     <row r="188" ht="52" customHeight="1">
       <c r="A188" s="32" t="inlineStr">
         <is>
-          <t>Do not mix / watch-outs</t>
+          <t>How we know it is working</t>
         </is>
       </c>
       <c r="B188" s="13" t="inlineStr">
         <is>
-          <t>Not DSS, not GSM/UMTS spectrum sharing, not NR UL/DL decoupling. DSS / SUL DSS cut LTE UL RBs → fewer UEs get SC. NSA: may HO PCC off an NSA anchor — deselect SPCT_COORD_INTER_FREQ_HO_SW to exempt NSA UEs. Enhancement (WBB/RRN) is a different bit (WbbCaMultiCarrierCoordSw); NSA PCC anchoring wins over it. SCC coverage-threshold adaptation kills SC carrier management. More HOs; CQI/KPI move with the new PCell quality.</t>
+          <t>L.HHO.InterFreq.ULquality.Prep/Exec/Succ (1526729994 / 9996 / 9998) increase. Also watch CA PCell/SCell users and bits, CA UE DL rate, SCell add success (tied to HO success).</t>
         </is>
       </c>
       <c r="C188" s="14" t="n"/>
@@ -5452,19 +5455,15 @@
       <c r="I188" s="14" t="n"/>
       <c r="J188" s="15" t="n"/>
     </row>
-    <row r="189" ht="118" customHeight="1">
+    <row r="189" ht="82" customHeight="1">
       <c r="A189" s="32" t="inlineStr">
         <is>
-          <t>Plain-English close  (read this if the jargon is heavy)</t>
+          <t>Do not mix / watch-outs</t>
         </is>
       </c>
       <c r="B189" s="22" t="inlineStr">
         <is>
-          <t>1) First make normal Carrier Aggregation work between one high-frequency cell and one low-frequency cell (same site, overlapping coverage). If CA is not working, do not turn Spectrum Coordination on.
-2) Spectrum Coordination does not join two carriers by itself. CA already joined them. This feature only changes which of those two cells is the PCell (the cell that carries the uplink).
-3) When the UE is near the cell edge, uplink on the high band is weak (poor UL SINR). The eNodeB then makes the low-band cell the PCell so the UE transmits uplink on the low band (better coverage).
-4) The high-band cell is kept as an SCell, so downlink data can still use both bands. That is the gain: cell-edge users keep high-band download speed even when their upload cannot stay on the high band.
-5) Short version: CA = two pipes for download. Spectrum Coordination = move the upload pipe to the low band at the edge, without throwing away the high-band download pipe.</t>
+          <t>Not DSS, not GSM/UMTS spectrum sharing, not NR UL/DL decoupling. DSS / SUL DSS cut LTE UL RBs → fewer UEs get SC. NSA: may HO PCC off an NSA anchor — deselect SPCT_COORD_INTER_FREQ_HO_SW to exempt NSA UEs. Enhancement (WBB/RRN) is a different bit (WbbCaMultiCarrierCoordSw); NSA PCC anchoring wins over it. SCC coverage-threshold adaptation kills SC carrier management. More HOs; CQI/KPI move with the new PCell quality.</t>
         </is>
       </c>
       <c r="C189" s="14" t="n"/>
@@ -5476,8 +5475,32 @@
       <c r="I189" s="14" t="n"/>
       <c r="J189" s="15" t="n"/>
     </row>
+    <row r="190" ht="180" customHeight="1">
+      <c r="A190" s="32" t="inlineStr">
+        <is>
+          <t>Plain-English close  (read this if the jargon is heavy)</t>
+        </is>
+      </c>
+      <c r="B190" s="13" t="inlineStr">
+        <is>
+          <t>1) First make normal Carrier Aggregation work between one high-frequency cell and one low-frequency cell (same site, overlapping coverage). If CA is not working, do not turn Spectrum Coordination on.
+2) Spectrum Coordination does not join two carriers by itself. CA already joined them. This feature only changes which of those two cells is the PCell (the cell that carries the uplink).
+3) When the UE is near the cell edge, uplink on the high band is weak (poor UL SINR). The eNodeB then makes the low-band cell the PCell so the UE transmits uplink on the low band (better coverage).
+4) The high-band cell is kept as an SCell, so downlink data can still use both bands. That is the gain: cell-edge users keep high-band download speed even when their upload cannot stay on the high band.
+5) Short version: CA = two pipes for download. Spectrum Coordination = move the upload pipe to the low band at the edge, without throwing away the high-band download pipe.</t>
+        </is>
+      </c>
+      <c r="C190" s="14" t="n"/>
+      <c r="D190" s="14" t="n"/>
+      <c r="E190" s="14" t="n"/>
+      <c r="F190" s="14" t="n"/>
+      <c r="G190" s="14" t="n"/>
+      <c r="H190" s="14" t="n"/>
+      <c r="I190" s="14" t="n"/>
+      <c r="J190" s="15" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="166">
+  <mergeCells count="167">
     <mergeCell ref="E138:J138"/>
     <mergeCell ref="E143:J143"/>
     <mergeCell ref="G109:J109"/>
@@ -5597,6 +5620,7 @@
     <mergeCell ref="E151:J151"/>
     <mergeCell ref="A164:J164"/>
     <mergeCell ref="G78:J78"/>
+    <mergeCell ref="B190:J190"/>
     <mergeCell ref="A56:J56"/>
     <mergeCell ref="A27:J27"/>
     <mergeCell ref="G87:J87"/>
